--- a/data/flat/mlb.xlsx
+++ b/data/flat/mlb.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR218" headerRowCount="1">
-  <autoFilter ref="A1:CR218"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS218" headerRowCount="1">
+  <autoFilter ref="A1:CS218"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR218"/>
+  <dimension ref="A1:CS218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1905,6 +1912,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2203,6 +2211,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2501,6 +2510,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2811,6 +2821,7 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3121,6 +3132,7 @@
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
       <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3431,6 +3443,7 @@
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
       <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3729,6 +3742,7 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
       <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -4027,6 +4041,7 @@
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
       <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4325,6 +4340,7 @@
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
       <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4623,6 +4639,7 @@
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
       <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4921,6 +4938,7 @@
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
       <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -5231,6 +5249,7 @@
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
       <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5541,6 +5560,7 @@
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
       <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5851,6 +5871,7 @@
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
       <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -6149,6 +6170,7 @@
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
       <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6447,6 +6469,7 @@
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
       <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6745,6 +6768,7 @@
       <c r="CP18" s="24" t="n"/>
       <c r="CQ18" s="24" t="n"/>
       <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -7043,6 +7067,7 @@
       <c r="CP19" s="24" t="n"/>
       <c r="CQ19" s="24" t="n"/>
       <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
@@ -7341,6 +7366,7 @@
       <c r="CP20" s="24" t="n"/>
       <c r="CQ20" s="24" t="n"/>
       <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -7651,6 +7677,7 @@
       <c r="CP21" s="24" t="n"/>
       <c r="CQ21" s="24" t="n"/>
       <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
@@ -7961,6 +7988,7 @@
       <c r="CP22" s="24" t="n"/>
       <c r="CQ22" s="24" t="n"/>
       <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
@@ -8271,6 +8299,7 @@
       <c r="CP23" s="24" t="n"/>
       <c r="CQ23" s="24" t="n"/>
       <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
@@ -8569,6 +8598,7 @@
       <c r="CP24" s="24" t="n"/>
       <c r="CQ24" s="24" t="n"/>
       <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
@@ -8867,6 +8897,7 @@
       <c r="CP25" s="24" t="n"/>
       <c r="CQ25" s="24" t="n"/>
       <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
@@ -9165,6 +9196,7 @@
       <c r="CP26" s="24" t="n"/>
       <c r="CQ26" s="24" t="n"/>
       <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
@@ -9463,6 +9495,7 @@
       <c r="CP27" s="24" t="n"/>
       <c r="CQ27" s="24" t="n"/>
       <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
@@ -9761,6 +9794,7 @@
       <c r="CP28" s="24" t="n"/>
       <c r="CQ28" s="24" t="n"/>
       <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
@@ -10071,6 +10105,7 @@
       <c r="CP29" s="24" t="n"/>
       <c r="CQ29" s="24" t="n"/>
       <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="n"/>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
@@ -10369,6 +10404,7 @@
       <c r="CP30" s="24" t="n"/>
       <c r="CQ30" s="24" t="n"/>
       <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="n"/>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
@@ -10667,6 +10703,7 @@
       <c r="CP31" s="24" t="n"/>
       <c r="CQ31" s="24" t="n"/>
       <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="n"/>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
@@ -10977,6 +11014,7 @@
       <c r="CP32" s="24" t="n"/>
       <c r="CQ32" s="24" t="n"/>
       <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="n"/>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
@@ -11287,6 +11325,7 @@
       <c r="CP33" s="24" t="n"/>
       <c r="CQ33" s="24" t="n"/>
       <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
@@ -11597,6 +11636,7 @@
       <c r="CP34" s="24" t="n"/>
       <c r="CQ34" s="24" t="n"/>
       <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
@@ -11907,6 +11947,7 @@
       <c r="CP35" s="24" t="n"/>
       <c r="CQ35" s="24" t="n"/>
       <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
@@ -12217,6 +12258,7 @@
       <c r="CP36" s="24" t="n"/>
       <c r="CQ36" s="24" t="n"/>
       <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
@@ -12527,6 +12569,7 @@
       <c r="CP37" s="24" t="n"/>
       <c r="CQ37" s="24" t="n"/>
       <c r="CR37" s="24" t="n"/>
+      <c r="CS37" s="24" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
@@ -12837,6 +12880,7 @@
       <c r="CP38" s="24" t="n"/>
       <c r="CQ38" s="24" t="n"/>
       <c r="CR38" s="24" t="n"/>
+      <c r="CS38" s="24" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
@@ -13135,6 +13179,7 @@
       <c r="CP39" s="24" t="n"/>
       <c r="CQ39" s="24" t="n"/>
       <c r="CR39" s="24" t="n"/>
+      <c r="CS39" s="24" t="n"/>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
@@ -13433,6 +13478,7 @@
       <c r="CP40" s="24" t="n"/>
       <c r="CQ40" s="24" t="n"/>
       <c r="CR40" s="24" t="n"/>
+      <c r="CS40" s="24" t="n"/>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
@@ -13731,6 +13777,7 @@
       <c r="CP41" s="24" t="n"/>
       <c r="CQ41" s="24" t="n"/>
       <c r="CR41" s="24" t="n"/>
+      <c r="CS41" s="24" t="n"/>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
@@ -14029,6 +14076,7 @@
       <c r="CP42" s="24" t="n"/>
       <c r="CQ42" s="24" t="n"/>
       <c r="CR42" s="24" t="n"/>
+      <c r="CS42" s="24" t="n"/>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
@@ -14327,6 +14375,7 @@
       <c r="CP43" s="24" t="n"/>
       <c r="CQ43" s="24" t="n"/>
       <c r="CR43" s="24" t="n"/>
+      <c r="CS43" s="24" t="n"/>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
@@ -14625,6 +14674,7 @@
       <c r="CP44" s="24" t="n"/>
       <c r="CQ44" s="24" t="n"/>
       <c r="CR44" s="24" t="n"/>
+      <c r="CS44" s="24" t="n"/>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
@@ -14923,6 +14973,7 @@
       <c r="CP45" s="24" t="n"/>
       <c r="CQ45" s="24" t="n"/>
       <c r="CR45" s="24" t="n"/>
+      <c r="CS45" s="24" t="n"/>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
@@ -15221,6 +15272,7 @@
       <c r="CP46" s="24" t="n"/>
       <c r="CQ46" s="24" t="n"/>
       <c r="CR46" s="24" t="n"/>
+      <c r="CS46" s="24" t="n"/>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
@@ -15519,6 +15571,7 @@
       <c r="CP47" s="24" t="n"/>
       <c r="CQ47" s="24" t="n"/>
       <c r="CR47" s="24" t="n"/>
+      <c r="CS47" s="24" t="n"/>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
@@ -15817,6 +15870,7 @@
       <c r="CP48" s="24" t="n"/>
       <c r="CQ48" s="24" t="n"/>
       <c r="CR48" s="24" t="n"/>
+      <c r="CS48" s="24" t="n"/>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
@@ -16115,6 +16169,7 @@
       <c r="CP49" s="24" t="n"/>
       <c r="CQ49" s="24" t="n"/>
       <c r="CR49" s="24" t="n"/>
+      <c r="CS49" s="24" t="n"/>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
@@ -16413,6 +16468,7 @@
       <c r="CP50" s="24" t="n"/>
       <c r="CQ50" s="24" t="n"/>
       <c r="CR50" s="24" t="n"/>
+      <c r="CS50" s="24" t="n"/>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
@@ -16711,6 +16767,7 @@
       <c r="CP51" s="24" t="n"/>
       <c r="CQ51" s="24" t="n"/>
       <c r="CR51" s="24" t="n"/>
+      <c r="CS51" s="24" t="n"/>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
@@ -17009,6 +17066,7 @@
       <c r="CP52" s="24" t="n"/>
       <c r="CQ52" s="24" t="n"/>
       <c r="CR52" s="24" t="n"/>
+      <c r="CS52" s="24" t="n"/>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
@@ -17319,6 +17377,7 @@
       <c r="CP53" s="24" t="n"/>
       <c r="CQ53" s="24" t="n"/>
       <c r="CR53" s="24" t="n"/>
+      <c r="CS53" s="24" t="n"/>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
@@ -17629,6 +17688,7 @@
       <c r="CP54" s="24" t="n"/>
       <c r="CQ54" s="24" t="n"/>
       <c r="CR54" s="24" t="n"/>
+      <c r="CS54" s="24" t="n"/>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
@@ -17939,6 +17999,7 @@
       <c r="CP55" s="24" t="n"/>
       <c r="CQ55" s="24" t="n"/>
       <c r="CR55" s="24" t="n"/>
+      <c r="CS55" s="24" t="n"/>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
@@ -18249,6 +18310,7 @@
       <c r="CP56" s="24" t="n"/>
       <c r="CQ56" s="24" t="n"/>
       <c r="CR56" s="24" t="n"/>
+      <c r="CS56" s="24" t="n"/>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
@@ -18559,6 +18621,7 @@
       <c r="CP57" s="24" t="n"/>
       <c r="CQ57" s="24" t="n"/>
       <c r="CR57" s="24" t="n"/>
+      <c r="CS57" s="24" t="n"/>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
@@ -18869,6 +18932,7 @@
       <c r="CP58" s="24" t="n"/>
       <c r="CQ58" s="24" t="n"/>
       <c r="CR58" s="24" t="n"/>
+      <c r="CS58" s="24" t="n"/>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
@@ -19179,6 +19243,7 @@
       <c r="CP59" s="24" t="n"/>
       <c r="CQ59" s="24" t="n"/>
       <c r="CR59" s="24" t="n"/>
+      <c r="CS59" s="24" t="n"/>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
@@ -19477,6 +19542,7 @@
       <c r="CP60" s="24" t="n"/>
       <c r="CQ60" s="24" t="n"/>
       <c r="CR60" s="24" t="n"/>
+      <c r="CS60" s="24" t="n"/>
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
@@ -19775,6 +19841,7 @@
       <c r="CP61" s="24" t="n"/>
       <c r="CQ61" s="24" t="n"/>
       <c r="CR61" s="24" t="n"/>
+      <c r="CS61" s="24" t="n"/>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
@@ -20073,6 +20140,7 @@
       <c r="CP62" s="24" t="n"/>
       <c r="CQ62" s="24" t="n"/>
       <c r="CR62" s="24" t="n"/>
+      <c r="CS62" s="24" t="n"/>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
@@ -20371,6 +20439,7 @@
       <c r="CP63" s="24" t="n"/>
       <c r="CQ63" s="24" t="n"/>
       <c r="CR63" s="24" t="n"/>
+      <c r="CS63" s="24" t="n"/>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
@@ -20669,6 +20738,7 @@
       <c r="CP64" s="24" t="n"/>
       <c r="CQ64" s="24" t="n"/>
       <c r="CR64" s="24" t="n"/>
+      <c r="CS64" s="24" t="n"/>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
@@ -20967,6 +21037,7 @@
       <c r="CP65" s="24" t="n"/>
       <c r="CQ65" s="24" t="n"/>
       <c r="CR65" s="24" t="n"/>
+      <c r="CS65" s="24" t="n"/>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
@@ -21265,6 +21336,7 @@
       <c r="CP66" s="24" t="n"/>
       <c r="CQ66" s="24" t="n"/>
       <c r="CR66" s="24" t="n"/>
+      <c r="CS66" s="24" t="n"/>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
@@ -21563,6 +21635,7 @@
       <c r="CP67" s="24" t="n"/>
       <c r="CQ67" s="24" t="n"/>
       <c r="CR67" s="24" t="n"/>
+      <c r="CS67" s="24" t="n"/>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
@@ -21861,6 +21934,7 @@
       <c r="CP68" s="24" t="n"/>
       <c r="CQ68" s="24" t="n"/>
       <c r="CR68" s="24" t="n"/>
+      <c r="CS68" s="24" t="n"/>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
@@ -22159,6 +22233,7 @@
       <c r="CP69" s="24" t="n"/>
       <c r="CQ69" s="24" t="n"/>
       <c r="CR69" s="24" t="n"/>
+      <c r="CS69" s="24" t="n"/>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
@@ -22457,6 +22532,7 @@
       <c r="CP70" s="24" t="n"/>
       <c r="CQ70" s="24" t="n"/>
       <c r="CR70" s="24" t="n"/>
+      <c r="CS70" s="24" t="n"/>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
@@ -22755,6 +22831,7 @@
       <c r="CP71" s="24" t="n"/>
       <c r="CQ71" s="24" t="n"/>
       <c r="CR71" s="24" t="n"/>
+      <c r="CS71" s="24" t="n"/>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
@@ -23053,6 +23130,7 @@
       <c r="CP72" s="24" t="n"/>
       <c r="CQ72" s="24" t="n"/>
       <c r="CR72" s="24" t="n"/>
+      <c r="CS72" s="24" t="n"/>
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
@@ -23351,6 +23429,7 @@
       <c r="CP73" s="24" t="n"/>
       <c r="CQ73" s="24" t="n"/>
       <c r="CR73" s="24" t="n"/>
+      <c r="CS73" s="24" t="n"/>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
@@ -23661,6 +23740,7 @@
       <c r="CP74" s="24" t="n"/>
       <c r="CQ74" s="24" t="n"/>
       <c r="CR74" s="24" t="n"/>
+      <c r="CS74" s="24" t="n"/>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
@@ -23971,6 +24051,7 @@
       <c r="CP75" s="24" t="n"/>
       <c r="CQ75" s="24" t="n"/>
       <c r="CR75" s="24" t="n"/>
+      <c r="CS75" s="24" t="n"/>
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
@@ -24281,6 +24362,7 @@
       <c r="CP76" s="24" t="n"/>
       <c r="CQ76" s="24" t="n"/>
       <c r="CR76" s="24" t="n"/>
+      <c r="CS76" s="24" t="n"/>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
@@ -24591,6 +24673,7 @@
       <c r="CP77" s="24" t="n"/>
       <c r="CQ77" s="24" t="n"/>
       <c r="CR77" s="24" t="n"/>
+      <c r="CS77" s="24" t="n"/>
     </row>
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="24" t="inlineStr">
@@ -24889,6 +24972,7 @@
       <c r="CP78" s="24" t="n"/>
       <c r="CQ78" s="24" t="n"/>
       <c r="CR78" s="24" t="n"/>
+      <c r="CS78" s="24" t="n"/>
     </row>
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
@@ -25187,6 +25271,7 @@
       <c r="CP79" s="24" t="n"/>
       <c r="CQ79" s="24" t="n"/>
       <c r="CR79" s="24" t="n"/>
+      <c r="CS79" s="24" t="n"/>
     </row>
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="24" t="inlineStr">
@@ -25485,6 +25570,7 @@
       <c r="CP80" s="24" t="n"/>
       <c r="CQ80" s="24" t="n"/>
       <c r="CR80" s="24" t="n"/>
+      <c r="CS80" s="24" t="n"/>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
@@ -25783,6 +25869,7 @@
       <c r="CP81" s="24" t="n"/>
       <c r="CQ81" s="24" t="n"/>
       <c r="CR81" s="24" t="n"/>
+      <c r="CS81" s="24" t="n"/>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
@@ -26081,6 +26168,7 @@
       <c r="CP82" s="24" t="n"/>
       <c r="CQ82" s="24" t="n"/>
       <c r="CR82" s="24" t="n"/>
+      <c r="CS82" s="24" t="n"/>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="24" t="inlineStr">
@@ -26379,6 +26467,7 @@
       <c r="CP83" s="24" t="n"/>
       <c r="CQ83" s="24" t="n"/>
       <c r="CR83" s="24" t="n"/>
+      <c r="CS83" s="24" t="n"/>
     </row>
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="24" t="inlineStr">
@@ -26677,6 +26766,7 @@
       <c r="CP84" s="24" t="n"/>
       <c r="CQ84" s="24" t="n"/>
       <c r="CR84" s="24" t="n"/>
+      <c r="CS84" s="24" t="n"/>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="24" t="inlineStr">
@@ -26975,6 +27065,7 @@
       <c r="CP85" s="24" t="n"/>
       <c r="CQ85" s="24" t="n"/>
       <c r="CR85" s="24" t="n"/>
+      <c r="CS85" s="24" t="n"/>
     </row>
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="24" t="inlineStr">
@@ -27285,6 +27376,7 @@
       <c r="CP86" s="24" t="n"/>
       <c r="CQ86" s="24" t="n"/>
       <c r="CR86" s="24" t="n"/>
+      <c r="CS86" s="24" t="n"/>
     </row>
     <row r="87" ht="36" customHeight="1">
       <c r="A87" s="24" t="inlineStr">
@@ -27595,6 +27687,7 @@
       <c r="CP87" s="24" t="n"/>
       <c r="CQ87" s="24" t="n"/>
       <c r="CR87" s="24" t="n"/>
+      <c r="CS87" s="24" t="n"/>
     </row>
     <row r="88" ht="36" customHeight="1">
       <c r="A88" s="24" t="inlineStr">
@@ -27905,6 +27998,7 @@
       <c r="CP88" s="24" t="n"/>
       <c r="CQ88" s="24" t="n"/>
       <c r="CR88" s="24" t="n"/>
+      <c r="CS88" s="24" t="n"/>
     </row>
     <row r="89" ht="36" customHeight="1">
       <c r="A89" s="24" t="inlineStr">
@@ -28215,6 +28309,7 @@
       <c r="CP89" s="24" t="n"/>
       <c r="CQ89" s="24" t="n"/>
       <c r="CR89" s="24" t="n"/>
+      <c r="CS89" s="24" t="n"/>
     </row>
     <row r="90" ht="36" customHeight="1">
       <c r="A90" s="24" t="inlineStr">
@@ -28525,6 +28620,7 @@
       <c r="CP90" s="24" t="n"/>
       <c r="CQ90" s="24" t="n"/>
       <c r="CR90" s="24" t="n"/>
+      <c r="CS90" s="24" t="n"/>
     </row>
     <row r="91" ht="36" customHeight="1">
       <c r="A91" s="24" t="inlineStr">
@@ -28835,6 +28931,7 @@
       <c r="CP91" s="24" t="n"/>
       <c r="CQ91" s="24" t="n"/>
       <c r="CR91" s="24" t="n"/>
+      <c r="CS91" s="24" t="n"/>
     </row>
     <row r="92" ht="36" customHeight="1">
       <c r="A92" s="24" t="inlineStr">
@@ -29133,6 +29230,7 @@
       <c r="CP92" s="24" t="n"/>
       <c r="CQ92" s="24" t="n"/>
       <c r="CR92" s="24" t="n"/>
+      <c r="CS92" s="24" t="n"/>
     </row>
     <row r="93" ht="36" customHeight="1">
       <c r="A93" s="24" t="inlineStr">
@@ -29431,6 +29529,7 @@
       <c r="CP93" s="24" t="n"/>
       <c r="CQ93" s="24" t="n"/>
       <c r="CR93" s="24" t="n"/>
+      <c r="CS93" s="24" t="n"/>
     </row>
     <row r="94" ht="36" customHeight="1">
       <c r="A94" s="24" t="inlineStr">
@@ -29729,6 +29828,7 @@
       <c r="CP94" s="24" t="n"/>
       <c r="CQ94" s="24" t="n"/>
       <c r="CR94" s="24" t="n"/>
+      <c r="CS94" s="24" t="n"/>
     </row>
     <row r="95" ht="36" customHeight="1">
       <c r="A95" s="24" t="inlineStr">
@@ -30027,6 +30127,7 @@
       <c r="CP95" s="24" t="n"/>
       <c r="CQ95" s="24" t="n"/>
       <c r="CR95" s="24" t="n"/>
+      <c r="CS95" s="24" t="n"/>
     </row>
     <row r="96" ht="36" customHeight="1">
       <c r="A96" s="24" t="inlineStr">
@@ -30325,6 +30426,7 @@
       <c r="CP96" s="24" t="n"/>
       <c r="CQ96" s="24" t="n"/>
       <c r="CR96" s="24" t="n"/>
+      <c r="CS96" s="24" t="n"/>
     </row>
     <row r="97" ht="36" customHeight="1">
       <c r="A97" s="24" t="inlineStr">
@@ -30623,6 +30725,7 @@
       <c r="CP97" s="24" t="n"/>
       <c r="CQ97" s="24" t="n"/>
       <c r="CR97" s="24" t="n"/>
+      <c r="CS97" s="24" t="n"/>
     </row>
     <row r="98" ht="36" customHeight="1">
       <c r="A98" s="24" t="inlineStr">
@@ -30921,6 +31024,7 @@
       <c r="CP98" s="24" t="n"/>
       <c r="CQ98" s="24" t="n"/>
       <c r="CR98" s="24" t="n"/>
+      <c r="CS98" s="24" t="n"/>
     </row>
     <row r="99" ht="36" customHeight="1">
       <c r="A99" s="24" t="inlineStr">
@@ -31219,6 +31323,7 @@
       <c r="CP99" s="24" t="n"/>
       <c r="CQ99" s="24" t="n"/>
       <c r="CR99" s="24" t="n"/>
+      <c r="CS99" s="24" t="n"/>
     </row>
     <row r="100" ht="36" customHeight="1">
       <c r="A100" s="24" t="inlineStr">
@@ -31517,6 +31622,7 @@
       <c r="CP100" s="24" t="n"/>
       <c r="CQ100" s="24" t="n"/>
       <c r="CR100" s="24" t="n"/>
+      <c r="CS100" s="24" t="n"/>
     </row>
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="24" t="inlineStr">
@@ -31815,6 +31921,7 @@
       <c r="CP101" s="24" t="n"/>
       <c r="CQ101" s="24" t="n"/>
       <c r="CR101" s="24" t="n"/>
+      <c r="CS101" s="24" t="n"/>
     </row>
     <row r="102" ht="36" customHeight="1">
       <c r="A102" s="24" t="inlineStr">
@@ -32113,6 +32220,7 @@
       <c r="CP102" s="24" t="n"/>
       <c r="CQ102" s="24" t="n"/>
       <c r="CR102" s="24" t="n"/>
+      <c r="CS102" s="24" t="n"/>
     </row>
     <row r="103" ht="36" customHeight="1">
       <c r="A103" s="24" t="inlineStr">
@@ -32411,6 +32519,7 @@
       <c r="CP103" s="24" t="n"/>
       <c r="CQ103" s="24" t="n"/>
       <c r="CR103" s="24" t="n"/>
+      <c r="CS103" s="24" t="n"/>
     </row>
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="24" t="inlineStr">
@@ -32721,6 +32830,7 @@
       <c r="CP104" s="24" t="n"/>
       <c r="CQ104" s="24" t="n"/>
       <c r="CR104" s="24" t="n"/>
+      <c r="CS104" s="24" t="n"/>
     </row>
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="24" t="inlineStr">
@@ -33031,6 +33141,7 @@
       <c r="CP105" s="24" t="n"/>
       <c r="CQ105" s="24" t="n"/>
       <c r="CR105" s="24" t="n"/>
+      <c r="CS105" s="24" t="n"/>
     </row>
     <row r="106" ht="36" customHeight="1">
       <c r="A106" s="24" t="inlineStr">
@@ -33341,6 +33452,7 @@
       <c r="CP106" s="24" t="n"/>
       <c r="CQ106" s="24" t="n"/>
       <c r="CR106" s="24" t="n"/>
+      <c r="CS106" s="24" t="n"/>
     </row>
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="24" t="inlineStr">
@@ -33651,6 +33763,7 @@
       <c r="CP107" s="24" t="n"/>
       <c r="CQ107" s="24" t="n"/>
       <c r="CR107" s="24" t="n"/>
+      <c r="CS107" s="24" t="n"/>
     </row>
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="24" t="inlineStr">
@@ -33961,6 +34074,7 @@
       <c r="CP108" s="24" t="n"/>
       <c r="CQ108" s="24" t="n"/>
       <c r="CR108" s="24" t="n"/>
+      <c r="CS108" s="24" t="n"/>
     </row>
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="24" t="inlineStr">
@@ -34259,6 +34373,7 @@
       <c r="CP109" s="24" t="n"/>
       <c r="CQ109" s="24" t="n"/>
       <c r="CR109" s="24" t="n"/>
+      <c r="CS109" s="24" t="n"/>
     </row>
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="24" t="inlineStr">
@@ -34557,6 +34672,7 @@
       <c r="CP110" s="24" t="n"/>
       <c r="CQ110" s="24" t="n"/>
       <c r="CR110" s="24" t="n"/>
+      <c r="CS110" s="24" t="n"/>
     </row>
     <row r="111" ht="36" customHeight="1">
       <c r="A111" s="24" t="inlineStr">
@@ -34855,6 +34971,7 @@
       <c r="CP111" s="24" t="n"/>
       <c r="CQ111" s="24" t="n"/>
       <c r="CR111" s="24" t="n"/>
+      <c r="CS111" s="24" t="n"/>
     </row>
     <row r="112" ht="36" customHeight="1">
       <c r="A112" s="24" t="inlineStr">
@@ -35153,6 +35270,7 @@
       <c r="CP112" s="24" t="n"/>
       <c r="CQ112" s="24" t="n"/>
       <c r="CR112" s="24" t="n"/>
+      <c r="CS112" s="24" t="n"/>
     </row>
     <row r="113" ht="36" customHeight="1">
       <c r="A113" s="24" t="inlineStr">
@@ -35451,6 +35569,7 @@
       <c r="CP113" s="24" t="n"/>
       <c r="CQ113" s="24" t="n"/>
       <c r="CR113" s="24" t="n"/>
+      <c r="CS113" s="24" t="n"/>
     </row>
     <row r="114" ht="36" customHeight="1">
       <c r="A114" s="24" t="inlineStr">
@@ -35749,6 +35868,7 @@
       <c r="CP114" s="24" t="n"/>
       <c r="CQ114" s="24" t="n"/>
       <c r="CR114" s="24" t="n"/>
+      <c r="CS114" s="24" t="n"/>
     </row>
     <row r="115" ht="36" customHeight="1">
       <c r="A115" s="24" t="inlineStr">
@@ -36047,6 +36167,7 @@
       <c r="CP115" s="24" t="n"/>
       <c r="CQ115" s="24" t="n"/>
       <c r="CR115" s="24" t="n"/>
+      <c r="CS115" s="24" t="n"/>
     </row>
     <row r="116" ht="36" customHeight="1">
       <c r="A116" s="24" t="inlineStr">
@@ -36345,6 +36466,7 @@
       <c r="CP116" s="24" t="n"/>
       <c r="CQ116" s="24" t="n"/>
       <c r="CR116" s="24" t="n"/>
+      <c r="CS116" s="24" t="n"/>
     </row>
     <row r="117" ht="36" customHeight="1">
       <c r="A117" s="24" t="inlineStr">
@@ -36643,6 +36765,7 @@
       <c r="CP117" s="24" t="n"/>
       <c r="CQ117" s="24" t="n"/>
       <c r="CR117" s="24" t="n"/>
+      <c r="CS117" s="24" t="n"/>
     </row>
     <row r="118" ht="36" customHeight="1">
       <c r="A118" s="24" t="inlineStr">
@@ -36941,6 +37064,7 @@
       <c r="CP118" s="24" t="n"/>
       <c r="CQ118" s="24" t="n"/>
       <c r="CR118" s="24" t="n"/>
+      <c r="CS118" s="24" t="n"/>
     </row>
     <row r="119" ht="36" customHeight="1">
       <c r="A119" s="24" t="inlineStr">
@@ -37249,12 +37373,13 @@
       <c r="CN119" s="24" t="n"/>
       <c r="CO119" s="24" t="n"/>
       <c r="CP119" s="24" t="n"/>
-      <c r="CQ119" s="24" t="inlineStr">
+      <c r="CQ119" s="24" t="n"/>
+      <c r="CR119" s="24" t="inlineStr">
         <is>
           <t>0.510159</t>
         </is>
       </c>
-      <c r="CR119" s="24" t="inlineStr">
+      <c r="CS119" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -37567,12 +37692,13 @@
       <c r="CN120" s="24" t="n"/>
       <c r="CO120" s="24" t="n"/>
       <c r="CP120" s="24" t="n"/>
-      <c r="CQ120" s="24" t="inlineStr">
+      <c r="CQ120" s="24" t="n"/>
+      <c r="CR120" s="24" t="inlineStr">
         <is>
           <t>0.600464</t>
         </is>
       </c>
-      <c r="CR120" s="24" t="inlineStr">
+      <c r="CS120" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -37885,12 +38011,13 @@
       <c r="CN121" s="24" t="n"/>
       <c r="CO121" s="24" t="n"/>
       <c r="CP121" s="24" t="n"/>
-      <c r="CQ121" s="24" t="inlineStr">
+      <c r="CQ121" s="24" t="n"/>
+      <c r="CR121" s="24" t="inlineStr">
         <is>
           <t>0.536276</t>
         </is>
       </c>
-      <c r="CR121" s="24" t="inlineStr">
+      <c r="CS121" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -38192,7 +38319,8 @@
       <c r="CO122" s="24" t="n"/>
       <c r="CP122" s="24" t="n"/>
       <c r="CQ122" s="24" t="n"/>
-      <c r="CR122" s="24" t="inlineStr">
+      <c r="CR122" s="24" t="n"/>
+      <c r="CS122" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -38494,7 +38622,8 @@
       <c r="CO123" s="24" t="n"/>
       <c r="CP123" s="24" t="n"/>
       <c r="CQ123" s="24" t="n"/>
-      <c r="CR123" s="24" t="inlineStr">
+      <c r="CR123" s="24" t="n"/>
+      <c r="CS123" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -38796,7 +38925,8 @@
       <c r="CO124" s="24" t="n"/>
       <c r="CP124" s="24" t="n"/>
       <c r="CQ124" s="24" t="n"/>
-      <c r="CR124" s="24" t="inlineStr">
+      <c r="CR124" s="24" t="n"/>
+      <c r="CS124" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -39098,7 +39228,8 @@
       <c r="CO125" s="24" t="n"/>
       <c r="CP125" s="24" t="n"/>
       <c r="CQ125" s="24" t="n"/>
-      <c r="CR125" s="24" t="inlineStr">
+      <c r="CR125" s="24" t="n"/>
+      <c r="CS125" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -39400,7 +39531,8 @@
       <c r="CO126" s="24" t="n"/>
       <c r="CP126" s="24" t="n"/>
       <c r="CQ126" s="24" t="n"/>
-      <c r="CR126" s="24" t="inlineStr">
+      <c r="CR126" s="24" t="n"/>
+      <c r="CS126" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -39702,7 +39834,8 @@
       <c r="CO127" s="24" t="n"/>
       <c r="CP127" s="24" t="n"/>
       <c r="CQ127" s="24" t="n"/>
-      <c r="CR127" s="24" t="inlineStr">
+      <c r="CR127" s="24" t="n"/>
+      <c r="CS127" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -40015,12 +40148,13 @@
       <c r="CN128" s="24" t="n"/>
       <c r="CO128" s="24" t="n"/>
       <c r="CP128" s="24" t="n"/>
-      <c r="CQ128" s="24" t="inlineStr">
+      <c r="CQ128" s="24" t="n"/>
+      <c r="CR128" s="24" t="inlineStr">
         <is>
           <t>0.541975</t>
         </is>
       </c>
-      <c r="CR128" s="24" t="inlineStr">
+      <c r="CS128" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -40333,12 +40467,13 @@
       <c r="CN129" s="24" t="n"/>
       <c r="CO129" s="24" t="n"/>
       <c r="CP129" s="24" t="n"/>
-      <c r="CQ129" s="24" t="inlineStr">
+      <c r="CQ129" s="24" t="n"/>
+      <c r="CR129" s="24" t="inlineStr">
         <is>
           <t>0.565508</t>
         </is>
       </c>
-      <c r="CR129" s="24" t="inlineStr">
+      <c r="CS129" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -40651,12 +40786,13 @@
       <c r="CN130" s="24" t="n"/>
       <c r="CO130" s="24" t="n"/>
       <c r="CP130" s="24" t="n"/>
-      <c r="CQ130" s="24" t="inlineStr">
+      <c r="CQ130" s="24" t="n"/>
+      <c r="CR130" s="24" t="inlineStr">
         <is>
           <t>0.519289</t>
         </is>
       </c>
-      <c r="CR130" s="24" t="inlineStr">
+      <c r="CS130" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -40969,12 +41105,13 @@
       <c r="CN131" s="24" t="n"/>
       <c r="CO131" s="24" t="n"/>
       <c r="CP131" s="24" t="n"/>
-      <c r="CQ131" s="24" t="inlineStr">
+      <c r="CQ131" s="24" t="n"/>
+      <c r="CR131" s="24" t="inlineStr">
         <is>
           <t>0.518519</t>
         </is>
       </c>
-      <c r="CR131" s="24" t="inlineStr">
+      <c r="CS131" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -41287,12 +41424,13 @@
       <c r="CN132" s="24" t="n"/>
       <c r="CO132" s="24" t="n"/>
       <c r="CP132" s="24" t="n"/>
-      <c r="CQ132" s="24" t="inlineStr">
+      <c r="CQ132" s="24" t="n"/>
+      <c r="CR132" s="24" t="inlineStr">
         <is>
           <t>0.538187</t>
         </is>
       </c>
-      <c r="CR132" s="24" t="inlineStr">
+      <c r="CS132" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -41605,12 +41743,13 @@
       <c r="CN133" s="24" t="n"/>
       <c r="CO133" s="24" t="n"/>
       <c r="CP133" s="24" t="n"/>
-      <c r="CQ133" s="24" t="inlineStr">
+      <c r="CQ133" s="24" t="n"/>
+      <c r="CR133" s="24" t="inlineStr">
         <is>
           <t>0.549522</t>
         </is>
       </c>
-      <c r="CR133" s="24" t="inlineStr">
+      <c r="CS133" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -41912,7 +42051,8 @@
       <c r="CO134" s="24" t="n"/>
       <c r="CP134" s="24" t="n"/>
       <c r="CQ134" s="24" t="n"/>
-      <c r="CR134" s="24" t="inlineStr">
+      <c r="CR134" s="24" t="n"/>
+      <c r="CS134" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -42214,7 +42354,8 @@
       <c r="CO135" s="24" t="n"/>
       <c r="CP135" s="24" t="n"/>
       <c r="CQ135" s="24" t="n"/>
-      <c r="CR135" s="24" t="inlineStr">
+      <c r="CR135" s="24" t="n"/>
+      <c r="CS135" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -42516,7 +42657,8 @@
       <c r="CO136" s="24" t="n"/>
       <c r="CP136" s="24" t="n"/>
       <c r="CQ136" s="24" t="n"/>
-      <c r="CR136" s="24" t="inlineStr">
+      <c r="CR136" s="24" t="n"/>
+      <c r="CS136" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -42818,7 +42960,8 @@
       <c r="CO137" s="24" t="n"/>
       <c r="CP137" s="24" t="n"/>
       <c r="CQ137" s="24" t="n"/>
-      <c r="CR137" s="24" t="inlineStr">
+      <c r="CR137" s="24" t="n"/>
+      <c r="CS137" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -43131,12 +43274,13 @@
       <c r="CN138" s="24" t="n"/>
       <c r="CO138" s="24" t="n"/>
       <c r="CP138" s="24" t="n"/>
-      <c r="CQ138" s="24" t="inlineStr">
+      <c r="CQ138" s="24" t="n"/>
+      <c r="CR138" s="24" t="inlineStr">
         <is>
           <t>0.60003</t>
         </is>
       </c>
-      <c r="CR138" s="24" t="inlineStr">
+      <c r="CS138" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -43449,12 +43593,13 @@
       <c r="CN139" s="24" t="n"/>
       <c r="CO139" s="24" t="n"/>
       <c r="CP139" s="24" t="n"/>
-      <c r="CQ139" s="24" t="inlineStr">
+      <c r="CQ139" s="24" t="n"/>
+      <c r="CR139" s="24" t="inlineStr">
         <is>
           <t>0.625602</t>
         </is>
       </c>
-      <c r="CR139" s="24" t="inlineStr">
+      <c r="CS139" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -43756,7 +43901,8 @@
       <c r="CO140" s="24" t="n"/>
       <c r="CP140" s="24" t="n"/>
       <c r="CQ140" s="24" t="n"/>
-      <c r="CR140" s="24" t="inlineStr">
+      <c r="CR140" s="24" t="n"/>
+      <c r="CS140" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -44058,7 +44204,8 @@
       <c r="CO141" s="24" t="n"/>
       <c r="CP141" s="24" t="n"/>
       <c r="CQ141" s="24" t="n"/>
-      <c r="CR141" s="24" t="inlineStr">
+      <c r="CR141" s="24" t="n"/>
+      <c r="CS141" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -44360,7 +44507,8 @@
       <c r="CO142" s="24" t="n"/>
       <c r="CP142" s="24" t="n"/>
       <c r="CQ142" s="24" t="n"/>
-      <c r="CR142" s="24" t="inlineStr">
+      <c r="CR142" s="24" t="n"/>
+      <c r="CS142" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -44662,7 +44810,8 @@
       <c r="CO143" s="24" t="n"/>
       <c r="CP143" s="24" t="n"/>
       <c r="CQ143" s="24" t="n"/>
-      <c r="CR143" s="24" t="inlineStr">
+      <c r="CR143" s="24" t="n"/>
+      <c r="CS143" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -44975,12 +45124,13 @@
       <c r="CN144" s="24" t="n"/>
       <c r="CO144" s="24" t="n"/>
       <c r="CP144" s="24" t="n"/>
-      <c r="CQ144" s="24" t="inlineStr">
+      <c r="CQ144" s="24" t="n"/>
+      <c r="CR144" s="24" t="inlineStr">
         <is>
           <t>0.559378</t>
         </is>
       </c>
-      <c r="CR144" s="24" t="inlineStr">
+      <c r="CS144" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -45293,12 +45443,13 @@
       <c r="CN145" s="24" t="n"/>
       <c r="CO145" s="24" t="n"/>
       <c r="CP145" s="24" t="n"/>
-      <c r="CQ145" s="24" t="inlineStr">
+      <c r="CQ145" s="24" t="n"/>
+      <c r="CR145" s="24" t="inlineStr">
         <is>
           <t>0.596425</t>
         </is>
       </c>
-      <c r="CR145" s="24" t="inlineStr">
+      <c r="CS145" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -45611,12 +45762,13 @@
       <c r="CN146" s="24" t="n"/>
       <c r="CO146" s="24" t="n"/>
       <c r="CP146" s="24" t="n"/>
-      <c r="CQ146" s="24" t="inlineStr">
+      <c r="CQ146" s="24" t="n"/>
+      <c r="CR146" s="24" t="inlineStr">
         <is>
           <t>0.589226</t>
         </is>
       </c>
-      <c r="CR146" s="24" t="inlineStr">
+      <c r="CS146" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -45918,7 +46070,8 @@
       <c r="CO147" s="24" t="n"/>
       <c r="CP147" s="24" t="n"/>
       <c r="CQ147" s="24" t="n"/>
-      <c r="CR147" s="24" t="inlineStr">
+      <c r="CR147" s="24" t="n"/>
+      <c r="CS147" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -46220,7 +46373,8 @@
       <c r="CO148" s="24" t="n"/>
       <c r="CP148" s="24" t="n"/>
       <c r="CQ148" s="24" t="n"/>
-      <c r="CR148" s="24" t="inlineStr">
+      <c r="CR148" s="24" t="n"/>
+      <c r="CS148" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -46522,7 +46676,8 @@
       <c r="CO149" s="24" t="n"/>
       <c r="CP149" s="24" t="n"/>
       <c r="CQ149" s="24" t="n"/>
-      <c r="CR149" s="24" t="inlineStr">
+      <c r="CR149" s="24" t="n"/>
+      <c r="CS149" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -46824,7 +46979,8 @@
       <c r="CO150" s="24" t="n"/>
       <c r="CP150" s="24" t="n"/>
       <c r="CQ150" s="24" t="n"/>
-      <c r="CR150" s="24" t="inlineStr">
+      <c r="CR150" s="24" t="n"/>
+      <c r="CS150" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -47126,7 +47282,8 @@
       <c r="CO151" s="24" t="n"/>
       <c r="CP151" s="24" t="n"/>
       <c r="CQ151" s="24" t="n"/>
-      <c r="CR151" s="24" t="inlineStr">
+      <c r="CR151" s="24" t="n"/>
+      <c r="CS151" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -47428,7 +47585,8 @@
       <c r="CO152" s="24" t="n"/>
       <c r="CP152" s="24" t="n"/>
       <c r="CQ152" s="24" t="n"/>
-      <c r="CR152" s="24" t="inlineStr">
+      <c r="CR152" s="24" t="n"/>
+      <c r="CS152" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -47741,12 +47899,13 @@
       <c r="CN153" s="24" t="n"/>
       <c r="CO153" s="24" t="n"/>
       <c r="CP153" s="24" t="n"/>
-      <c r="CQ153" s="24" t="inlineStr">
+      <c r="CQ153" s="24" t="n"/>
+      <c r="CR153" s="24" t="inlineStr">
         <is>
           <t>0.559308</t>
         </is>
       </c>
-      <c r="CR153" s="24" t="inlineStr">
+      <c r="CS153" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -48048,7 +48207,8 @@
       <c r="CO154" s="24" t="n"/>
       <c r="CP154" s="24" t="n"/>
       <c r="CQ154" s="24" t="n"/>
-      <c r="CR154" s="24" t="inlineStr">
+      <c r="CR154" s="24" t="n"/>
+      <c r="CS154" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -48350,7 +48510,8 @@
       <c r="CO155" s="24" t="n"/>
       <c r="CP155" s="24" t="n"/>
       <c r="CQ155" s="24" t="n"/>
-      <c r="CR155" s="24" t="inlineStr">
+      <c r="CR155" s="24" t="n"/>
+      <c r="CS155" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -48663,12 +48824,13 @@
       <c r="CN156" s="24" t="n"/>
       <c r="CO156" s="24" t="n"/>
       <c r="CP156" s="24" t="n"/>
-      <c r="CQ156" s="24" t="inlineStr">
+      <c r="CQ156" s="24" t="n"/>
+      <c r="CR156" s="24" t="inlineStr">
         <is>
           <t>0.580684</t>
         </is>
       </c>
-      <c r="CR156" s="24" t="inlineStr">
+      <c r="CS156" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -48970,7 +49132,8 @@
       <c r="CO157" s="24" t="n"/>
       <c r="CP157" s="24" t="n"/>
       <c r="CQ157" s="24" t="n"/>
-      <c r="CR157" s="24" t="inlineStr">
+      <c r="CR157" s="24" t="n"/>
+      <c r="CS157" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -49272,7 +49435,8 @@
       <c r="CO158" s="24" t="n"/>
       <c r="CP158" s="24" t="n"/>
       <c r="CQ158" s="24" t="n"/>
-      <c r="CR158" s="24" t="inlineStr">
+      <c r="CR158" s="24" t="n"/>
+      <c r="CS158" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -49585,12 +49749,13 @@
       <c r="CN159" s="24" t="n"/>
       <c r="CO159" s="24" t="n"/>
       <c r="CP159" s="24" t="n"/>
-      <c r="CQ159" s="24" t="inlineStr">
+      <c r="CQ159" s="24" t="n"/>
+      <c r="CR159" s="24" t="inlineStr">
         <is>
           <t>0.587948</t>
         </is>
       </c>
-      <c r="CR159" s="24" t="inlineStr">
+      <c r="CS159" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -49903,12 +50068,13 @@
       <c r="CN160" s="24" t="n"/>
       <c r="CO160" s="24" t="n"/>
       <c r="CP160" s="24" t="n"/>
-      <c r="CQ160" s="24" t="inlineStr">
+      <c r="CQ160" s="24" t="n"/>
+      <c r="CR160" s="24" t="inlineStr">
         <is>
           <t>0.606371</t>
         </is>
       </c>
-      <c r="CR160" s="24" t="inlineStr">
+      <c r="CS160" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -50221,12 +50387,13 @@
       <c r="CN161" s="24" t="n"/>
       <c r="CO161" s="24" t="n"/>
       <c r="CP161" s="24" t="n"/>
-      <c r="CQ161" s="24" t="inlineStr">
+      <c r="CQ161" s="24" t="n"/>
+      <c r="CR161" s="24" t="inlineStr">
         <is>
           <t>0.582299</t>
         </is>
       </c>
-      <c r="CR161" s="24" t="inlineStr">
+      <c r="CS161" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -50539,12 +50706,13 @@
       <c r="CN162" s="24" t="n"/>
       <c r="CO162" s="24" t="n"/>
       <c r="CP162" s="24" t="n"/>
-      <c r="CQ162" s="24" t="inlineStr">
+      <c r="CQ162" s="24" t="n"/>
+      <c r="CR162" s="24" t="inlineStr">
         <is>
           <t>0.507802</t>
         </is>
       </c>
-      <c r="CR162" s="24" t="inlineStr">
+      <c r="CS162" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -50857,12 +51025,13 @@
       <c r="CN163" s="24" t="n"/>
       <c r="CO163" s="24" t="n"/>
       <c r="CP163" s="24" t="n"/>
-      <c r="CQ163" s="24" t="inlineStr">
+      <c r="CQ163" s="24" t="n"/>
+      <c r="CR163" s="24" t="inlineStr">
         <is>
           <t>0.535416</t>
         </is>
       </c>
-      <c r="CR163" s="24" t="inlineStr">
+      <c r="CS163" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -51175,12 +51344,13 @@
       <c r="CN164" s="24" t="n"/>
       <c r="CO164" s="24" t="n"/>
       <c r="CP164" s="24" t="n"/>
-      <c r="CQ164" s="24" t="inlineStr">
+      <c r="CQ164" s="24" t="n"/>
+      <c r="CR164" s="24" t="inlineStr">
         <is>
           <t>0.648206</t>
         </is>
       </c>
-      <c r="CR164" s="24" t="inlineStr">
+      <c r="CS164" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -51493,12 +51663,13 @@
       <c r="CN165" s="24" t="n"/>
       <c r="CO165" s="24" t="n"/>
       <c r="CP165" s="24" t="n"/>
-      <c r="CQ165" s="24" t="inlineStr">
+      <c r="CQ165" s="24" t="n"/>
+      <c r="CR165" s="24" t="inlineStr">
         <is>
           <t>0.502816</t>
         </is>
       </c>
-      <c r="CR165" s="24" t="inlineStr">
+      <c r="CS165" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -51800,7 +51971,8 @@
       <c r="CO166" s="24" t="n"/>
       <c r="CP166" s="24" t="n"/>
       <c r="CQ166" s="24" t="n"/>
-      <c r="CR166" s="24" t="inlineStr">
+      <c r="CR166" s="24" t="n"/>
+      <c r="CS166" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -52102,7 +52274,8 @@
       <c r="CO167" s="24" t="n"/>
       <c r="CP167" s="24" t="n"/>
       <c r="CQ167" s="24" t="n"/>
-      <c r="CR167" s="24" t="inlineStr">
+      <c r="CR167" s="24" t="n"/>
+      <c r="CS167" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -52404,7 +52577,8 @@
       <c r="CO168" s="24" t="n"/>
       <c r="CP168" s="24" t="n"/>
       <c r="CQ168" s="24" t="n"/>
-      <c r="CR168" s="24" t="inlineStr">
+      <c r="CR168" s="24" t="n"/>
+      <c r="CS168" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -52706,7 +52880,8 @@
       <c r="CO169" s="24" t="n"/>
       <c r="CP169" s="24" t="n"/>
       <c r="CQ169" s="24" t="n"/>
-      <c r="CR169" s="24" t="inlineStr">
+      <c r="CR169" s="24" t="n"/>
+      <c r="CS169" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -53008,7 +53183,8 @@
       <c r="CO170" s="24" t="n"/>
       <c r="CP170" s="24" t="n"/>
       <c r="CQ170" s="24" t="n"/>
-      <c r="CR170" s="24" t="inlineStr">
+      <c r="CR170" s="24" t="n"/>
+      <c r="CS170" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -53310,7 +53486,8 @@
       <c r="CO171" s="24" t="n"/>
       <c r="CP171" s="24" t="n"/>
       <c r="CQ171" s="24" t="n"/>
-      <c r="CR171" s="24" t="inlineStr">
+      <c r="CR171" s="24" t="n"/>
+      <c r="CS171" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -53612,7 +53789,8 @@
       <c r="CO172" s="24" t="n"/>
       <c r="CP172" s="24" t="n"/>
       <c r="CQ172" s="24" t="n"/>
-      <c r="CR172" s="24" t="inlineStr">
+      <c r="CR172" s="24" t="n"/>
+      <c r="CS172" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -53914,7 +54092,8 @@
       <c r="CO173" s="24" t="n"/>
       <c r="CP173" s="24" t="n"/>
       <c r="CQ173" s="24" t="n"/>
-      <c r="CR173" s="24" t="inlineStr">
+      <c r="CR173" s="24" t="n"/>
+      <c r="CS173" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -54216,7 +54395,8 @@
       <c r="CO174" s="24" t="n"/>
       <c r="CP174" s="24" t="n"/>
       <c r="CQ174" s="24" t="n"/>
-      <c r="CR174" s="24" t="inlineStr">
+      <c r="CR174" s="24" t="n"/>
+      <c r="CS174" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -54518,7 +54698,8 @@
       <c r="CO175" s="24" t="n"/>
       <c r="CP175" s="24" t="n"/>
       <c r="CQ175" s="24" t="n"/>
-      <c r="CR175" s="24" t="inlineStr">
+      <c r="CR175" s="24" t="n"/>
+      <c r="CS175" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -54820,7 +55001,8 @@
       <c r="CO176" s="24" t="n"/>
       <c r="CP176" s="24" t="n"/>
       <c r="CQ176" s="24" t="n"/>
-      <c r="CR176" s="24" t="inlineStr">
+      <c r="CR176" s="24" t="n"/>
+      <c r="CS176" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -55122,7 +55304,8 @@
       <c r="CO177" s="24" t="n"/>
       <c r="CP177" s="24" t="n"/>
       <c r="CQ177" s="24" t="n"/>
-      <c r="CR177" s="24" t="inlineStr">
+      <c r="CR177" s="24" t="n"/>
+      <c r="CS177" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -55424,7 +55607,8 @@
       <c r="CO178" s="24" t="n"/>
       <c r="CP178" s="24" t="n"/>
       <c r="CQ178" s="24" t="n"/>
-      <c r="CR178" s="24" t="inlineStr">
+      <c r="CR178" s="24" t="n"/>
+      <c r="CS178" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -55726,7 +55910,8 @@
       <c r="CO179" s="24" t="n"/>
       <c r="CP179" s="24" t="n"/>
       <c r="CQ179" s="24" t="n"/>
-      <c r="CR179" s="24" t="inlineStr">
+      <c r="CR179" s="24" t="n"/>
+      <c r="CS179" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -55735,12 +55920,12 @@
     <row r="180" ht="36" customHeight="1">
       <c r="A180" s="24" t="inlineStr">
         <is>
-          <t>faeced7e487c461c</t>
+          <t>1a5cc2105a3f4fb3</t>
         </is>
       </c>
       <c r="B180" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C180" s="24" t="inlineStr">
@@ -55794,21 +55979,21 @@
         <v>0.555556</v>
       </c>
       <c r="O180" s="28" t="n">
-        <v>0.538033</v>
+        <v>0.542811</v>
       </c>
       <c r="P180" s="28" t="n"/>
       <c r="Q180" s="28" t="n">
-        <v>-0.017523</v>
+        <v>-0.012745</v>
       </c>
       <c r="R180" s="26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S180" s="29" t="n">
         <v>0</v>
       </c>
       <c r="T180" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U180" s="24" t="inlineStr">
@@ -55827,7 +56012,7 @@
       <c r="AD180" s="24" t="n"/>
       <c r="AE180" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6242; executable ask 0.5550 (aec-mlb-ath-cin-2026-08-04); model edge vs ask -0.0170.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.5550 (aec-mlb-ath-cin-2026-08-04); model edge vs ask -0.0122.</t>
         </is>
       </c>
       <c r="AF180" s="31" t="inlineStr">
@@ -55911,7 +56096,7 @@
       </c>
       <c r="BA180" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB180" s="24" t="inlineStr">
@@ -55921,17 +56106,17 @@
       </c>
       <c r="BC180" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD180" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE180" s="24" t="inlineStr">
         <is>
-          <t>3c0db2a442210ede</t>
+          <t>b94b2f1337120d9f</t>
         </is>
       </c>
       <c r="BF180" s="24" t="inlineStr">
@@ -55941,12 +56126,12 @@
       </c>
       <c r="BG180" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH180" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:19.498539Z</t>
+          <t>2026-08-04T14:23:06.428271Z</t>
         </is>
       </c>
       <c r="BI180" s="24" t="inlineStr">
@@ -55998,14 +56183,10 @@
       </c>
       <c r="CF180" s="24" t="inlineStr">
         <is>
-          <t>1.017</t>
-        </is>
-      </c>
-      <c r="CG180" s="24" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
+          <t>1.0173</t>
+        </is>
+      </c>
+      <c r="CG180" s="24" t="n"/>
       <c r="CH180" s="24" t="n"/>
       <c r="CI180" s="24" t="n"/>
       <c r="CJ180" s="24" t="inlineStr">
@@ -56016,19 +56197,24 @@
       <c r="CK180" s="24" t="n"/>
       <c r="CL180" s="24" t="inlineStr">
         <is>
-          <t>-0.747682</t>
-        </is>
-      </c>
-      <c r="CM180" s="24" t="n"/>
+          <t>-0.787719</t>
+        </is>
+      </c>
+      <c r="CM180" s="24" t="inlineStr">
+        <is>
+          <t>-1.7902</t>
+        </is>
+      </c>
       <c r="CN180" s="24" t="n"/>
       <c r="CO180" s="24" t="n"/>
       <c r="CP180" s="24" t="n"/>
-      <c r="CQ180" s="24" t="inlineStr">
-        <is>
-          <t>0.538033</t>
-        </is>
-      </c>
+      <c r="CQ180" s="24" t="n"/>
       <c r="CR180" s="24" t="inlineStr">
+        <is>
+          <t>0.542811</t>
+        </is>
+      </c>
+      <c r="CS180" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -56037,12 +56223,12 @@
     <row r="181" ht="36" customHeight="1">
       <c r="A181" s="24" t="inlineStr">
         <is>
-          <t>b6a5c4c4abfe4631</t>
+          <t>c1a6d7ad109a4af5</t>
         </is>
       </c>
       <c r="B181" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C181" s="24" t="inlineStr">
@@ -56087,30 +56273,30 @@
         </is>
       </c>
       <c r="L181" s="26" t="n">
-        <v>-144</v>
+        <v>-141</v>
       </c>
       <c r="M181" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.70922</v>
       </c>
       <c r="N181" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.585062</v>
       </c>
       <c r="O181" s="28" t="n">
-        <v>0.5663899999999999</v>
+        <v>0.583155</v>
       </c>
       <c r="P181" s="28" t="n"/>
       <c r="Q181" s="28" t="n">
-        <v>-0.023774</v>
+        <v>-0.001907</v>
       </c>
       <c r="R181" s="26" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="S181" s="29" t="n">
         <v>0</v>
       </c>
       <c r="T181" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U181" s="24" t="inlineStr">
@@ -56129,7 +56315,7 @@
       <c r="AD181" s="24" t="n"/>
       <c r="AE181" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6242; executable ask 0.5900 (aec-mlb-nym-cle-2026-08-04); model edge vs ask -0.0236.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.5850 (aec-mlb-nym-cle-2026-08-04); model edge vs ask -0.0018.</t>
         </is>
       </c>
       <c r="AF181" s="31" t="inlineStr">
@@ -56213,7 +56399,7 @@
       </c>
       <c r="BA181" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB181" s="24" t="inlineStr">
@@ -56223,17 +56409,17 @@
       </c>
       <c r="BC181" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD181" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE181" s="24" t="inlineStr">
         <is>
-          <t>f82bfe398cfb233d</t>
+          <t>0b49cd84a0231454</t>
         </is>
       </c>
       <c r="BF181" s="24" t="inlineStr">
@@ -56243,12 +56429,12 @@
       </c>
       <c r="BG181" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH181" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:18.856760Z</t>
+          <t>2026-08-04T14:23:05.946346Z</t>
         </is>
       </c>
       <c r="BI181" s="24" t="inlineStr">
@@ -56258,16 +56444,16 @@
       </c>
       <c r="BJ181" s="25" t="n"/>
       <c r="BK181" s="26" t="n">
-        <v>-144</v>
+        <v>-141</v>
       </c>
       <c r="BL181" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.70922</v>
       </c>
       <c r="BM181" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.585062</v>
       </c>
       <c r="BN181" s="28" t="n">
-        <v>0.5870649999999999</v>
+        <v>0.58209</v>
       </c>
       <c r="BO181" s="28" t="n"/>
       <c r="BP181" s="25" t="n"/>
@@ -56300,14 +56486,10 @@
       </c>
       <c r="CF181" s="24" t="inlineStr">
         <is>
-          <t>1.008</t>
-        </is>
-      </c>
-      <c r="CG181" s="24" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
+          <t>1.0079</t>
+        </is>
+      </c>
+      <c r="CG181" s="24" t="n"/>
       <c r="CH181" s="24" t="n"/>
       <c r="CI181" s="24" t="n"/>
       <c r="CJ181" s="24" t="inlineStr">
@@ -56318,19 +56500,24 @@
       <c r="CK181" s="24" t="n"/>
       <c r="CL181" s="24" t="inlineStr">
         <is>
-          <t>-0.572333</t>
-        </is>
-      </c>
-      <c r="CM181" s="24" t="n"/>
+          <t>0.097105</t>
+        </is>
+      </c>
+      <c r="CM181" s="24" t="inlineStr">
+        <is>
+          <t>-2.2045</t>
+        </is>
+      </c>
       <c r="CN181" s="24" t="n"/>
       <c r="CO181" s="24" t="n"/>
       <c r="CP181" s="24" t="n"/>
-      <c r="CQ181" s="24" t="inlineStr">
-        <is>
-          <t>0.56639</t>
-        </is>
-      </c>
+      <c r="CQ181" s="24" t="n"/>
       <c r="CR181" s="24" t="inlineStr">
+        <is>
+          <t>0.583155</t>
+        </is>
+      </c>
+      <c r="CS181" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -56339,12 +56526,12 @@
     <row r="182" ht="36" customHeight="1">
       <c r="A182" s="24" t="inlineStr">
         <is>
-          <t>507c9beb6b254693</t>
+          <t>f1cde61691e84d8a</t>
         </is>
       </c>
       <c r="B182" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C182" s="24" t="inlineStr">
@@ -56389,20 +56576,20 @@
         </is>
       </c>
       <c r="L182" s="26" t="n">
-        <v>-233</v>
+        <v>-257</v>
       </c>
       <c r="M182" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.389105</v>
       </c>
       <c r="N182" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.719888</v>
       </c>
       <c r="O182" s="28" t="n">
-        <v>0.585456</v>
+        <v>0.576615</v>
       </c>
       <c r="P182" s="28" t="n"/>
       <c r="Q182" s="28" t="n">
-        <v>-0.114244</v>
+        <v>-0.143273</v>
       </c>
       <c r="R182" s="26" t="n">
         <v>0</v>
@@ -56412,7 +56599,7 @@
       </c>
       <c r="T182" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U182" s="24" t="inlineStr">
@@ -56431,7 +56618,7 @@
       <c r="AD182" s="24" t="n"/>
       <c r="AE182" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6242; executable ask 0.7000 (aec-mlb-wsh-phi-2026-08-04); model edge vs ask -0.1145.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.7200 (aec-mlb-wsh-phi-2026-08-04); model edge vs ask -0.1434. NOTE: NO_CALL_STARTER_ERA_GAP_INSUFFICIENT_HISTORY unavailable for this game — defaulted to neutral, other features used normally.</t>
         </is>
       </c>
       <c r="AF182" s="31" t="inlineStr">
@@ -56515,7 +56702,7 @@
       </c>
       <c r="BA182" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB182" s="24" t="inlineStr">
@@ -56525,17 +56712,17 @@
       </c>
       <c r="BC182" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD182" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE182" s="24" t="inlineStr">
         <is>
-          <t>093993194689ed4e</t>
+          <t>9ee0310cde0f84fa</t>
         </is>
       </c>
       <c r="BF182" s="24" t="inlineStr">
@@ -56545,12 +56732,12 @@
       </c>
       <c r="BG182" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH182" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:19.941279Z</t>
+          <t>2026-08-04T14:23:07.075526Z</t>
         </is>
       </c>
       <c r="BI182" s="24" t="inlineStr">
@@ -56560,16 +56747,16 @@
       </c>
       <c r="BJ182" s="25" t="n"/>
       <c r="BK182" s="26" t="n">
-        <v>-233</v>
+        <v>-257</v>
       </c>
       <c r="BL182" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.389105</v>
       </c>
       <c r="BM182" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.719888</v>
       </c>
       <c r="BN182" s="28" t="n">
-        <v>0.6965170000000001</v>
+        <v>0.716418</v>
       </c>
       <c r="BO182" s="28" t="n"/>
       <c r="BP182" s="25" t="n"/>
@@ -56602,16 +56789,16 @@
       </c>
       <c r="CF182" s="24" t="inlineStr">
         <is>
-          <t>1.0116</t>
-        </is>
-      </c>
-      <c r="CG182" s="24" t="inlineStr">
-        <is>
-          <t>-2.4</t>
-        </is>
-      </c>
+          <t>1.012</t>
+        </is>
+      </c>
+      <c r="CG182" s="24" t="n"/>
       <c r="CH182" s="24" t="n"/>
-      <c r="CI182" s="24" t="n"/>
+      <c r="CI182" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_STARTER_ERA_GAP_INSUFFICIENT_HISTORY</t>
+        </is>
+      </c>
       <c r="CJ182" s="24" t="inlineStr">
         <is>
           <t>1.204538</t>
@@ -56620,19 +56807,24 @@
       <c r="CK182" s="24" t="n"/>
       <c r="CL182" s="24" t="inlineStr">
         <is>
-          <t>-0.198438</t>
-        </is>
-      </c>
-      <c r="CM182" s="24" t="n"/>
+          <t>-0.545196</t>
+        </is>
+      </c>
+      <c r="CM182" s="24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="CN182" s="24" t="n"/>
       <c r="CO182" s="24" t="n"/>
       <c r="CP182" s="24" t="n"/>
-      <c r="CQ182" s="24" t="inlineStr">
-        <is>
-          <t>0.585456</t>
-        </is>
-      </c>
+      <c r="CQ182" s="24" t="n"/>
       <c r="CR182" s="24" t="inlineStr">
+        <is>
+          <t>0.576615</t>
+        </is>
+      </c>
+      <c r="CS182" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -56641,12 +56833,12 @@
     <row r="183" ht="36" customHeight="1">
       <c r="A183" s="24" t="inlineStr">
         <is>
-          <t>092ca773d1d447c7</t>
+          <t>bc9a48e2ce834581</t>
         </is>
       </c>
       <c r="B183" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C183" s="24" t="inlineStr">
@@ -56691,30 +56883,30 @@
         </is>
       </c>
       <c r="L183" s="26" t="n">
-        <v>-156</v>
+        <v>-182</v>
       </c>
       <c r="M183" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.549451</v>
       </c>
       <c r="N183" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.64539</v>
       </c>
       <c r="O183" s="28" t="n">
-        <v>0.585641</v>
+        <v>0.606778</v>
       </c>
       <c r="P183" s="28" t="n"/>
       <c r="Q183" s="28" t="n">
-        <v>-0.023734</v>
+        <v>-0.038612</v>
       </c>
       <c r="R183" s="26" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="S183" s="29" t="n">
         <v>0</v>
       </c>
       <c r="T183" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U183" s="24" t="inlineStr">
@@ -56733,7 +56925,7 @@
       <c r="AD183" s="24" t="n"/>
       <c r="AE183" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6242; executable ask 0.6100 (aec-mlb-stl-nyy-2026-08-04); model edge vs ask -0.0244.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.6450 (aec-mlb-stl-nyy-2026-08-04); model edge vs ask -0.0382.</t>
         </is>
       </c>
       <c r="AF183" s="31" t="inlineStr">
@@ -56817,7 +57009,7 @@
       </c>
       <c r="BA183" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB183" s="24" t="inlineStr">
@@ -56827,17 +57019,17 @@
       </c>
       <c r="BC183" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD183" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE183" s="24" t="inlineStr">
         <is>
-          <t>288f404cbb2ac94a</t>
+          <t>63ce416cd671aa81</t>
         </is>
       </c>
       <c r="BF183" s="24" t="inlineStr">
@@ -56847,12 +57039,12 @@
       </c>
       <c r="BG183" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH183" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:20.462463Z</t>
+          <t>2026-08-04T14:23:07.959215Z</t>
         </is>
       </c>
       <c r="BI183" s="24" t="inlineStr">
@@ -56862,16 +57054,16 @@
       </c>
       <c r="BJ183" s="25" t="n"/>
       <c r="BK183" s="26" t="n">
-        <v>-156</v>
+        <v>-182</v>
       </c>
       <c r="BL183" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.549451</v>
       </c>
       <c r="BM183" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.64539</v>
       </c>
       <c r="BN183" s="28" t="n">
-        <v>0.606965</v>
+        <v>0.641791</v>
       </c>
       <c r="BO183" s="28" t="n"/>
       <c r="BP183" s="25" t="n"/>
@@ -56904,14 +57096,10 @@
       </c>
       <c r="CF183" s="24" t="inlineStr">
         <is>
-          <t>1.0066</t>
-        </is>
-      </c>
-      <c r="CG183" s="24" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
+          <t>1.0058</t>
+        </is>
+      </c>
+      <c r="CG183" s="24" t="n"/>
       <c r="CH183" s="24" t="n"/>
       <c r="CI183" s="24" t="n"/>
       <c r="CJ183" s="24" t="inlineStr">
@@ -56922,19 +57110,24 @@
       <c r="CK183" s="24" t="n"/>
       <c r="CL183" s="24" t="inlineStr">
         <is>
-          <t>-0.250122</t>
-        </is>
-      </c>
-      <c r="CM183" s="24" t="n"/>
+          <t>0.083592</t>
+        </is>
+      </c>
+      <c r="CM183" s="24" t="inlineStr">
+        <is>
+          <t>-3.0458</t>
+        </is>
+      </c>
       <c r="CN183" s="24" t="n"/>
       <c r="CO183" s="24" t="n"/>
       <c r="CP183" s="24" t="n"/>
-      <c r="CQ183" s="24" t="inlineStr">
-        <is>
-          <t>0.585641</t>
-        </is>
-      </c>
+      <c r="CQ183" s="24" t="n"/>
       <c r="CR183" s="24" t="inlineStr">
+        <is>
+          <t>0.606778</t>
+        </is>
+      </c>
+      <c r="CS183" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -56943,12 +57136,12 @@
     <row r="184" ht="36" customHeight="1">
       <c r="A184" s="24" t="inlineStr">
         <is>
-          <t>68a2bac009354e3a</t>
+          <t>d701108b8a024b3e</t>
         </is>
       </c>
       <c r="B184" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C184" s="24" t="inlineStr">
@@ -56993,30 +57186,30 @@
         </is>
       </c>
       <c r="L184" s="26" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="M184" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.8</v>
       </c>
       <c r="N184" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.555556</v>
       </c>
       <c r="O184" s="28" t="n">
-        <v>0.589466</v>
+        <v>0.574715</v>
       </c>
       <c r="P184" s="28" t="n"/>
       <c r="Q184" s="28" t="n">
-        <v>0.039916</v>
+        <v>0.019159</v>
       </c>
       <c r="R184" s="26" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="S184" s="29" t="n">
         <v>0</v>
       </c>
       <c r="T184" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U184" s="24" t="inlineStr">
@@ -57035,7 +57228,7 @@
       <c r="AD184" s="24" t="n"/>
       <c r="AE184" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6242; executable ask 0.5500 (aec-mlb-cws-bos-2026-08-04); model edge vs ask +0.0395.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.5550 (aec-mlb-cws-bos-2026-08-04); model edge vs ask +0.0197.</t>
         </is>
       </c>
       <c r="AF184" s="31" t="inlineStr">
@@ -57119,7 +57312,7 @@
       </c>
       <c r="BA184" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB184" s="24" t="inlineStr">
@@ -57129,17 +57322,17 @@
       </c>
       <c r="BC184" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD184" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE184" s="24" t="inlineStr">
         <is>
-          <t>067d8daffda52912</t>
+          <t>8e5d770c4943ab65</t>
         </is>
       </c>
       <c r="BF184" s="24" t="inlineStr">
@@ -57149,12 +57342,12 @@
       </c>
       <c r="BG184" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH184" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:20.885688Z</t>
+          <t>2026-08-04T14:23:08.559833Z</t>
         </is>
       </c>
       <c r="BI184" s="24" t="inlineStr">
@@ -57164,16 +57357,16 @@
       </c>
       <c r="BJ184" s="25" t="n"/>
       <c r="BK184" s="26" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="BL184" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.8</v>
       </c>
       <c r="BM184" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.555556</v>
       </c>
       <c r="BN184" s="28" t="n">
-        <v>0.547264</v>
+        <v>0.552239</v>
       </c>
       <c r="BO184" s="28" t="n"/>
       <c r="BP184" s="25" t="n"/>
@@ -57206,14 +57399,10 @@
       </c>
       <c r="CF184" s="24" t="inlineStr">
         <is>
-          <t>1.0098</t>
-        </is>
-      </c>
-      <c r="CG184" s="24" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
+          <t>1.0097</t>
+        </is>
+      </c>
+      <c r="CG184" s="24" t="n"/>
       <c r="CH184" s="24" t="n"/>
       <c r="CI184" s="24" t="n"/>
       <c r="CJ184" s="24" t="inlineStr">
@@ -57224,19 +57413,24 @@
       <c r="CK184" s="24" t="n"/>
       <c r="CL184" s="24" t="inlineStr">
         <is>
-          <t>-0.091891</t>
-        </is>
-      </c>
-      <c r="CM184" s="24" t="n"/>
+          <t>-0.002488</t>
+        </is>
+      </c>
+      <c r="CM184" s="24" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
       <c r="CN184" s="24" t="n"/>
       <c r="CO184" s="24" t="n"/>
       <c r="CP184" s="24" t="n"/>
-      <c r="CQ184" s="24" t="inlineStr">
-        <is>
-          <t>0.589466</t>
-        </is>
-      </c>
+      <c r="CQ184" s="24" t="n"/>
       <c r="CR184" s="24" t="inlineStr">
+        <is>
+          <t>0.574715</t>
+        </is>
+      </c>
+      <c r="CS184" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -57245,12 +57439,12 @@
     <row r="185" ht="36" customHeight="1">
       <c r="A185" s="24" t="inlineStr">
         <is>
-          <t>d8dbd5f2b0ce46a9</t>
+          <t>d073109f6f8f4d71</t>
         </is>
       </c>
       <c r="B185" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C185" s="24" t="inlineStr">
@@ -57295,30 +57489,30 @@
         </is>
       </c>
       <c r="L185" s="26" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="M185" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.724638</v>
       </c>
       <c r="N185" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.579832</v>
       </c>
       <c r="O185" s="28" t="n">
-        <v>0.589535</v>
+        <v>0.592828</v>
       </c>
       <c r="P185" s="28" t="n"/>
       <c r="Q185" s="28" t="n">
-        <v>0.01872</v>
+        <v>0.012996</v>
       </c>
       <c r="R185" s="26" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="S185" s="29" t="n">
         <v>0</v>
       </c>
       <c r="T185" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U185" s="24" t="inlineStr">
@@ -57337,7 +57531,7 @@
       <c r="AD185" s="24" t="n"/>
       <c r="AE185" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6242; executable ask 0.5700 (aec-mlb-mia-atl-2026-08-04); model edge vs ask +0.0195.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.5800 (aec-mlb-mia-atl-2026-08-04); model edge vs ask +0.0128.</t>
         </is>
       </c>
       <c r="AF185" s="31" t="inlineStr">
@@ -57421,7 +57615,7 @@
       </c>
       <c r="BA185" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB185" s="24" t="inlineStr">
@@ -57431,17 +57625,17 @@
       </c>
       <c r="BC185" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD185" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE185" s="24" t="inlineStr">
         <is>
-          <t>dbeb91f17a9268bb</t>
+          <t>3a98c46b1feb5dff</t>
         </is>
       </c>
       <c r="BF185" s="24" t="inlineStr">
@@ -57451,12 +57645,12 @@
       </c>
       <c r="BG185" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH185" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:21.412725Z</t>
+          <t>2026-08-04T14:23:09.398190Z</t>
         </is>
       </c>
       <c r="BI185" s="24" t="inlineStr">
@@ -57466,16 +57660,16 @@
       </c>
       <c r="BJ185" s="25" t="n"/>
       <c r="BK185" s="26" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="BL185" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.724638</v>
       </c>
       <c r="BM185" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.579832</v>
       </c>
       <c r="BN185" s="28" t="n">
-        <v>0.567164</v>
+        <v>0.577114</v>
       </c>
       <c r="BO185" s="28" t="n"/>
       <c r="BP185" s="25" t="n"/>
@@ -57508,14 +57702,10 @@
       </c>
       <c r="CF185" s="24" t="inlineStr">
         <is>
-          <t>1.0152</t>
-        </is>
-      </c>
-      <c r="CG185" s="24" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+          <t>1.0123</t>
+        </is>
+      </c>
+      <c r="CG185" s="24" t="n"/>
       <c r="CH185" s="24" t="n"/>
       <c r="CI185" s="24" t="n"/>
       <c r="CJ185" s="24" t="inlineStr">
@@ -57526,19 +57716,24 @@
       <c r="CK185" s="24" t="n"/>
       <c r="CL185" s="24" t="inlineStr">
         <is>
-          <t>-0.187292</t>
-        </is>
-      </c>
-      <c r="CM185" s="24" t="n"/>
+          <t>-0.037443</t>
+        </is>
+      </c>
+      <c r="CM185" s="24" t="inlineStr">
+        <is>
+          <t>-0.8666</t>
+        </is>
+      </c>
       <c r="CN185" s="24" t="n"/>
       <c r="CO185" s="24" t="n"/>
       <c r="CP185" s="24" t="n"/>
-      <c r="CQ185" s="24" t="inlineStr">
-        <is>
-          <t>0.589535</t>
-        </is>
-      </c>
+      <c r="CQ185" s="24" t="n"/>
       <c r="CR185" s="24" t="inlineStr">
+        <is>
+          <t>0.592828</t>
+        </is>
+      </c>
+      <c r="CS185" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -57547,12 +57742,12 @@
     <row r="186" ht="36" customHeight="1">
       <c r="A186" s="24" t="inlineStr">
         <is>
-          <t>d80d81a05ae0486d</t>
+          <t>f2921bd8bbf74694</t>
         </is>
       </c>
       <c r="B186" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C186" s="24" t="inlineStr">
@@ -57606,21 +57801,21 @@
         <v>0.425532</v>
       </c>
       <c r="O186" s="28" t="n">
-        <v>0.540201</v>
+        <v>0.548577</v>
       </c>
       <c r="P186" s="28" t="n"/>
       <c r="Q186" s="28" t="n">
-        <v>0.114669</v>
+        <v>0.123045</v>
       </c>
       <c r="R186" s="26" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="S186" s="29" t="n">
         <v>0</v>
       </c>
       <c r="T186" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U186" s="24" t="inlineStr">
@@ -57639,7 +57834,7 @@
       <c r="AD186" s="24" t="n"/>
       <c r="AE186" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6242; executable ask 0.4250 (aec-mlb-min-kc-2026-08-04); model edge vs ask +0.1152.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.4250 (aec-mlb-min-kc-2026-08-04); model edge vs ask +0.1236. NOTE: NO_CALL_STARTER_ERA_GAP_INSUFFICIENT_HISTORY unavailable for this game — defaulted to neutral, other features used normally.</t>
         </is>
       </c>
       <c r="AF186" s="31" t="inlineStr">
@@ -57723,7 +57918,7 @@
       </c>
       <c r="BA186" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB186" s="24" t="inlineStr">
@@ -57733,17 +57928,17 @@
       </c>
       <c r="BC186" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD186" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE186" s="24" t="inlineStr">
         <is>
-          <t>c38b45d4af23d8e9</t>
+          <t>8502bc8bb5e15229</t>
         </is>
       </c>
       <c r="BF186" s="24" t="inlineStr">
@@ -57753,12 +57948,12 @@
       </c>
       <c r="BG186" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH186" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:22.244590Z</t>
+          <t>2026-08-04T14:23:10.651606Z</t>
         </is>
       </c>
       <c r="BI186" s="24" t="inlineStr">
@@ -57810,16 +58005,16 @@
       </c>
       <c r="CF186" s="24" t="inlineStr">
         <is>
-          <t>1.0236</t>
-        </is>
-      </c>
-      <c r="CG186" s="24" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
+          <t>1.0234</t>
+        </is>
+      </c>
+      <c r="CG186" s="24" t="n"/>
       <c r="CH186" s="24" t="n"/>
-      <c r="CI186" s="24" t="n"/>
+      <c r="CI186" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_STARTER_ERA_GAP_INSUFFICIENT_HISTORY</t>
+        </is>
+      </c>
       <c r="CJ186" s="24" t="inlineStr">
         <is>
           <t>-0.736554</t>
@@ -57828,19 +58023,24 @@
       <c r="CK186" s="24" t="n"/>
       <c r="CL186" s="24" t="inlineStr">
         <is>
-          <t>0.543475</t>
-        </is>
-      </c>
-      <c r="CM186" s="24" t="n"/>
+          <t>0.623137</t>
+        </is>
+      </c>
+      <c r="CM186" s="24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="CN186" s="24" t="n"/>
       <c r="CO186" s="24" t="n"/>
       <c r="CP186" s="24" t="n"/>
-      <c r="CQ186" s="24" t="inlineStr">
-        <is>
-          <t>0.540201</t>
-        </is>
-      </c>
+      <c r="CQ186" s="24" t="n"/>
       <c r="CR186" s="24" t="inlineStr">
+        <is>
+          <t>0.548577</t>
+        </is>
+      </c>
+      <c r="CS186" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -57849,12 +58049,12 @@
     <row r="187" ht="36" customHeight="1">
       <c r="A187" s="24" t="inlineStr">
         <is>
-          <t>dc88f6d7b08d444e</t>
+          <t>7fdae9c916fa43d7</t>
         </is>
       </c>
       <c r="B187" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C187" s="24" t="inlineStr">
@@ -57908,21 +58108,21 @@
         <v>0.6</v>
       </c>
       <c r="O187" s="28" t="n">
-        <v>0.605446</v>
+        <v>0.602762</v>
       </c>
       <c r="P187" s="28" t="n"/>
       <c r="Q187" s="28" t="n">
-        <v>0.005446</v>
+        <v>0.002762</v>
       </c>
       <c r="R187" s="26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S187" s="29" t="n">
         <v>0</v>
       </c>
       <c r="T187" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U187" s="24" t="inlineStr">
@@ -57941,7 +58141,7 @@
       <c r="AD187" s="24" t="n"/>
       <c r="AE187" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6242; executable ask 0.6000 (aec-mlb-pit-mil-2026-08-04); model edge vs ask +0.0054.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.6000 (aec-mlb-pit-mil-2026-08-04); model edge vs ask +0.0028.</t>
         </is>
       </c>
       <c r="AF187" s="31" t="inlineStr">
@@ -58025,7 +58225,7 @@
       </c>
       <c r="BA187" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB187" s="24" t="inlineStr">
@@ -58035,17 +58235,17 @@
       </c>
       <c r="BC187" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD187" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE187" s="24" t="inlineStr">
         <is>
-          <t>2f5664ed9b7f4a0c</t>
+          <t>13e97fbe35b98e79</t>
         </is>
       </c>
       <c r="BF187" s="24" t="inlineStr">
@@ -58055,12 +58255,12 @@
       </c>
       <c r="BG187" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH187" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:21.899733Z</t>
+          <t>2026-08-04T14:23:10.125761Z</t>
         </is>
       </c>
       <c r="BI187" s="24" t="inlineStr">
@@ -58115,11 +58315,7 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="CG187" s="24" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
+      <c r="CG187" s="24" t="n"/>
       <c r="CH187" s="24" t="n"/>
       <c r="CI187" s="24" t="n"/>
       <c r="CJ187" s="24" t="inlineStr">
@@ -58130,19 +58326,24 @@
       <c r="CK187" s="24" t="n"/>
       <c r="CL187" s="24" t="inlineStr">
         <is>
-          <t>-0.042309</t>
-        </is>
-      </c>
-      <c r="CM187" s="24" t="n"/>
+          <t>-0.007808</t>
+        </is>
+      </c>
+      <c r="CM187" s="24" t="inlineStr">
+        <is>
+          <t>0.1044</t>
+        </is>
+      </c>
       <c r="CN187" s="24" t="n"/>
       <c r="CO187" s="24" t="n"/>
       <c r="CP187" s="24" t="n"/>
-      <c r="CQ187" s="24" t="inlineStr">
-        <is>
-          <t>0.605446</t>
-        </is>
-      </c>
+      <c r="CQ187" s="24" t="n"/>
       <c r="CR187" s="24" t="inlineStr">
+        <is>
+          <t>0.602762</t>
+        </is>
+      </c>
+      <c r="CS187" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -58151,12 +58352,12 @@
     <row r="188" ht="36" customHeight="1">
       <c r="A188" s="24" t="inlineStr">
         <is>
-          <t>3d4df7aa619046a1</t>
+          <t>e177601115ad47a6</t>
         </is>
       </c>
       <c r="B188" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C188" s="24" t="inlineStr">
@@ -58201,30 +58402,30 @@
         </is>
       </c>
       <c r="L188" s="26" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="M188" s="27" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N188" s="28" t="n">
-        <v>0.35461</v>
+        <v>0.344828</v>
       </c>
       <c r="O188" s="28" t="n">
-        <v>0.509325</v>
+        <v>0.521495</v>
       </c>
       <c r="P188" s="28" t="n"/>
       <c r="Q188" s="28" t="n">
-        <v>0.154715</v>
+        <v>0.176667</v>
       </c>
       <c r="R188" s="26" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S188" s="29" t="n">
         <v>0</v>
       </c>
       <c r="T188" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U188" s="24" t="inlineStr">
@@ -58243,7 +58444,7 @@
       <c r="AD188" s="24" t="n"/>
       <c r="AE188" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6242; executable ask 0.3550 (aec-mlb-lad-chc-2026-08-04); model edge vs ask +0.1543.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.3450 (aec-mlb-lad-chc-2026-08-04); model edge vs ask +0.1765.</t>
         </is>
       </c>
       <c r="AF188" s="31" t="inlineStr">
@@ -58327,7 +58528,7 @@
       </c>
       <c r="BA188" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB188" s="24" t="inlineStr">
@@ -58337,17 +58538,17 @@
       </c>
       <c r="BC188" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD188" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE188" s="24" t="inlineStr">
         <is>
-          <t>f68ee4f138d232dd</t>
+          <t>60a3d5d3de62be38</t>
         </is>
       </c>
       <c r="BF188" s="24" t="inlineStr">
@@ -58357,12 +58558,12 @@
       </c>
       <c r="BG188" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH188" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:22.695517Z</t>
+          <t>2026-08-04T14:23:11.051384Z</t>
         </is>
       </c>
       <c r="BI188" s="24" t="inlineStr">
@@ -58372,16 +58573,16 @@
       </c>
       <c r="BJ188" s="25" t="n"/>
       <c r="BK188" s="26" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="BL188" s="27" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BM188" s="28" t="n">
-        <v>0.35461</v>
+        <v>0.344828</v>
       </c>
       <c r="BN188" s="28" t="n">
-        <v>0.353234</v>
+        <v>0.343284</v>
       </c>
       <c r="BO188" s="28" t="n"/>
       <c r="BP188" s="25" t="n"/>
@@ -58414,14 +58615,10 @@
       </c>
       <c r="CF188" s="24" t="inlineStr">
         <is>
-          <t>1.0048</t>
-        </is>
-      </c>
-      <c r="CG188" s="24" t="inlineStr">
-        <is>
-          <t>-3.8</t>
-        </is>
-      </c>
+          <t>1.0043</t>
+        </is>
+      </c>
+      <c r="CG188" s="24" t="n"/>
       <c r="CH188" s="24" t="n"/>
       <c r="CI188" s="24" t="n"/>
       <c r="CJ188" s="24" t="inlineStr">
@@ -58432,19 +58629,24 @@
       <c r="CK188" s="24" t="n"/>
       <c r="CL188" s="24" t="inlineStr">
         <is>
-          <t>0.220703</t>
-        </is>
-      </c>
-      <c r="CM188" s="24" t="n"/>
+          <t>-0.041774</t>
+        </is>
+      </c>
+      <c r="CM188" s="24" t="inlineStr">
+        <is>
+          <t>-0.0904</t>
+        </is>
+      </c>
       <c r="CN188" s="24" t="n"/>
       <c r="CO188" s="24" t="n"/>
       <c r="CP188" s="24" t="n"/>
-      <c r="CQ188" s="24" t="inlineStr">
-        <is>
-          <t>0.509325</t>
-        </is>
-      </c>
+      <c r="CQ188" s="24" t="n"/>
       <c r="CR188" s="24" t="inlineStr">
+        <is>
+          <t>0.521495</t>
+        </is>
+      </c>
+      <c r="CS188" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -58453,12 +58655,12 @@
     <row r="189" ht="36" customHeight="1">
       <c r="A189" s="24" t="inlineStr">
         <is>
-          <t>1a4697435d7640b6</t>
+          <t>a3e6c72bd24d462c</t>
         </is>
       </c>
       <c r="B189" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C189" s="24" t="inlineStr">
@@ -58512,11 +58714,11 @@
         <v>0.64539</v>
       </c>
       <c r="O189" s="28" t="n">
-        <v>0.584674</v>
+        <v>0.598469</v>
       </c>
       <c r="P189" s="28" t="n"/>
       <c r="Q189" s="28" t="n">
-        <v>-0.060716</v>
+        <v>-0.046921</v>
       </c>
       <c r="R189" s="26" t="n">
         <v>0</v>
@@ -58526,7 +58728,7 @@
       </c>
       <c r="T189" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U189" s="24" t="inlineStr">
@@ -58545,7 +58747,7 @@
       <c r="AD189" s="24" t="n"/>
       <c r="AE189" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6242; executable ask 0.6450 (aec-mlb-sf-tex-2026-08-04); model edge vs ask -0.0603.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.6450 (aec-mlb-sf-tex-2026-08-04); model edge vs ask -0.0465.</t>
         </is>
       </c>
       <c r="AF189" s="31" t="inlineStr">
@@ -58629,7 +58831,7 @@
       </c>
       <c r="BA189" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB189" s="24" t="inlineStr">
@@ -58639,17 +58841,17 @@
       </c>
       <c r="BC189" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD189" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE189" s="24" t="inlineStr">
         <is>
-          <t>2e6e6abc0bc66052</t>
+          <t>99e74cbbb81a6f38</t>
         </is>
       </c>
       <c r="BF189" s="24" t="inlineStr">
@@ -58659,12 +58861,12 @@
       </c>
       <c r="BG189" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH189" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:23.300225Z</t>
+          <t>2026-08-04T14:23:34.287233Z</t>
         </is>
       </c>
       <c r="BI189" s="24" t="inlineStr">
@@ -58719,11 +58921,7 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="CG189" s="24" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
+      <c r="CG189" s="24" t="n"/>
       <c r="CH189" s="24" t="n"/>
       <c r="CI189" s="24" t="n"/>
       <c r="CJ189" s="24" t="inlineStr">
@@ -58734,19 +58932,24 @@
       <c r="CK189" s="24" t="n"/>
       <c r="CL189" s="24" t="inlineStr">
         <is>
-          <t>0.603262</t>
-        </is>
-      </c>
-      <c r="CM189" s="24" t="n"/>
+          <t>0.625111</t>
+        </is>
+      </c>
+      <c r="CM189" s="24" t="inlineStr">
+        <is>
+          <t>-2.7307</t>
+        </is>
+      </c>
       <c r="CN189" s="24" t="n"/>
       <c r="CO189" s="24" t="n"/>
       <c r="CP189" s="24" t="n"/>
-      <c r="CQ189" s="24" t="inlineStr">
-        <is>
-          <t>0.584674</t>
-        </is>
-      </c>
+      <c r="CQ189" s="24" t="n"/>
       <c r="CR189" s="24" t="inlineStr">
+        <is>
+          <t>0.598469</t>
+        </is>
+      </c>
+      <c r="CS189" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -58755,12 +58958,12 @@
     <row r="190" ht="36" customHeight="1">
       <c r="A190" s="24" t="inlineStr">
         <is>
-          <t>cdbc9b914bd047b9</t>
+          <t>ec97d79ce0804090</t>
         </is>
       </c>
       <c r="B190" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C190" s="24" t="inlineStr">
@@ -58814,21 +59017,21 @@
         <v>0.54955</v>
       </c>
       <c r="O190" s="28" t="n">
-        <v>0.542548</v>
+        <v>0.533882</v>
       </c>
       <c r="P190" s="28" t="n"/>
       <c r="Q190" s="28" t="n">
-        <v>-0.007002</v>
+        <v>-0.015668</v>
       </c>
       <c r="R190" s="26" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="S190" s="29" t="n">
         <v>0</v>
       </c>
       <c r="T190" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U190" s="24" t="inlineStr">
@@ -58847,7 +59050,7 @@
       <c r="AD190" s="24" t="n"/>
       <c r="AE190" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6242; executable ask 0.5500 (aec-mlb-tor-hou-2026-08-04); model edge vs ask -0.0075.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.5500 (aec-mlb-tor-hou-2026-08-04); model edge vs ask -0.0161.</t>
         </is>
       </c>
       <c r="AF190" s="31" t="inlineStr">
@@ -58931,7 +59134,7 @@
       </c>
       <c r="BA190" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB190" s="24" t="inlineStr">
@@ -58941,17 +59144,17 @@
       </c>
       <c r="BC190" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD190" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE190" s="24" t="inlineStr">
         <is>
-          <t>fb9456890e2413ab</t>
+          <t>9031aa134a98c176</t>
         </is>
       </c>
       <c r="BF190" s="24" t="inlineStr">
@@ -58961,12 +59164,12 @@
       </c>
       <c r="BG190" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH190" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:23.770086Z</t>
+          <t>2026-08-04T14:23:12.528117Z</t>
         </is>
       </c>
       <c r="BI190" s="24" t="inlineStr">
@@ -59021,11 +59224,7 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="CG190" s="24" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
+      <c r="CG190" s="24" t="n"/>
       <c r="CH190" s="24" t="n"/>
       <c r="CI190" s="24" t="n"/>
       <c r="CJ190" s="24" t="inlineStr">
@@ -59036,19 +59235,24 @@
       <c r="CK190" s="24" t="n"/>
       <c r="CL190" s="24" t="inlineStr">
         <is>
-          <t>-0.112375</t>
-        </is>
-      </c>
-      <c r="CM190" s="24" t="n"/>
+          <t>0.015906</t>
+        </is>
+      </c>
+      <c r="CM190" s="24" t="inlineStr">
+        <is>
+          <t>0.5256</t>
+        </is>
+      </c>
       <c r="CN190" s="24" t="n"/>
       <c r="CO190" s="24" t="n"/>
       <c r="CP190" s="24" t="n"/>
-      <c r="CQ190" s="24" t="inlineStr">
-        <is>
-          <t>0.542548</t>
-        </is>
-      </c>
+      <c r="CQ190" s="24" t="n"/>
       <c r="CR190" s="24" t="inlineStr">
+        <is>
+          <t>0.533882</t>
+        </is>
+      </c>
+      <c r="CS190" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -59057,12 +59261,12 @@
     <row r="191" ht="36" customHeight="1">
       <c r="A191" s="24" t="inlineStr">
         <is>
-          <t>526e6d62022e4594</t>
+          <t>7af08d52bd754f45</t>
         </is>
       </c>
       <c r="B191" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C191" s="24" t="inlineStr">
@@ -59107,30 +59311,30 @@
         </is>
       </c>
       <c r="L191" s="26" t="n">
-        <v>-138</v>
+        <v>-153</v>
       </c>
       <c r="M191" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.653595</v>
       </c>
       <c r="N191" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.604743</v>
       </c>
       <c r="O191" s="28" t="n">
-        <v>0.651997</v>
+        <v>0.61964</v>
       </c>
       <c r="P191" s="28" t="n"/>
       <c r="Q191" s="28" t="n">
-        <v>0.07216500000000001</v>
+        <v>0.014897</v>
       </c>
       <c r="R191" s="26" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="S191" s="29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="T191" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U191" s="24" t="inlineStr">
@@ -59149,7 +59353,7 @@
       <c r="AD191" s="24" t="n"/>
       <c r="AE191" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6242; executable ask 0.5800 (aec-mlb-tb-col-2026-08-04); model edge vs ask +0.0720.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.6050 (aec-mlb-tb-col-2026-08-04); model edge vs ask +0.0146.</t>
         </is>
       </c>
       <c r="AF191" s="31" t="inlineStr">
@@ -59167,7 +59371,7 @@
       <c r="AJ191" s="31" t="n"/>
       <c r="AK191" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL191" s="26" t="n">
@@ -59175,17 +59379,17 @@
       </c>
       <c r="AM191" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN191" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO191" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_BELOW_LEARNED_CONFIDENCE</t>
         </is>
       </c>
       <c r="AP191" s="24" t="inlineStr">
@@ -59233,7 +59437,7 @@
       </c>
       <c r="BA191" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB191" s="24" t="inlineStr">
@@ -59243,17 +59447,17 @@
       </c>
       <c r="BC191" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD191" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE191" s="24" t="inlineStr">
         <is>
-          <t>aa1550043d30dddf</t>
+          <t>16464949e4fc5515</t>
         </is>
       </c>
       <c r="BF191" s="24" t="inlineStr">
@@ -59263,12 +59467,12 @@
       </c>
       <c r="BG191" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH191" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:24.205568Z</t>
+          <t>2026-08-04T14:23:13.184791Z</t>
         </is>
       </c>
       <c r="BI191" s="24" t="inlineStr">
@@ -59278,16 +59482,16 @@
       </c>
       <c r="BJ191" s="25" t="n"/>
       <c r="BK191" s="26" t="n">
-        <v>-138</v>
+        <v>-153</v>
       </c>
       <c r="BL191" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.653595</v>
       </c>
       <c r="BM191" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.604743</v>
       </c>
       <c r="BN191" s="28" t="n">
-        <v>0.577114</v>
+        <v>0.60199</v>
       </c>
       <c r="BO191" s="28" t="n"/>
       <c r="BP191" s="25" t="n"/>
@@ -59320,14 +59524,10 @@
       </c>
       <c r="CF191" s="24" t="inlineStr">
         <is>
-          <t>1.0086</t>
-        </is>
-      </c>
-      <c r="CG191" s="24" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+          <t>1.0078</t>
+        </is>
+      </c>
+      <c r="CG191" s="24" t="n"/>
       <c r="CH191" s="24" t="n"/>
       <c r="CI191" s="24" t="n"/>
       <c r="CJ191" s="24" t="inlineStr">
@@ -59338,19 +59538,24 @@
       <c r="CK191" s="24" t="n"/>
       <c r="CL191" s="24" t="inlineStr">
         <is>
-          <t>0.056981</t>
-        </is>
-      </c>
-      <c r="CM191" s="24" t="n"/>
+          <t>0.044172</t>
+        </is>
+      </c>
+      <c r="CM191" s="24" t="inlineStr">
+        <is>
+          <t>-3.6232</t>
+        </is>
+      </c>
       <c r="CN191" s="24" t="n"/>
       <c r="CO191" s="24" t="n"/>
       <c r="CP191" s="24" t="n"/>
-      <c r="CQ191" s="24" t="inlineStr">
-        <is>
-          <t>0.651997</t>
-        </is>
-      </c>
+      <c r="CQ191" s="24" t="n"/>
       <c r="CR191" s="24" t="inlineStr">
+        <is>
+          <t>0.61964</t>
+        </is>
+      </c>
+      <c r="CS191" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -59359,12 +59564,12 @@
     <row r="192" ht="36" customHeight="1">
       <c r="A192" s="24" t="inlineStr">
         <is>
-          <t>483a1ee142774bb1</t>
+          <t>5b64872521b447b8</t>
         </is>
       </c>
       <c r="B192" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:24:46.511596Z</t>
         </is>
       </c>
       <c r="C192" s="24" t="inlineStr">
@@ -59409,30 +59614,30 @@
         </is>
       </c>
       <c r="L192" s="26" t="n">
-        <v>-122</v>
+        <v>-117</v>
       </c>
       <c r="M192" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.854701</v>
       </c>
       <c r="N192" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.539171</v>
       </c>
       <c r="O192" s="28" t="n">
-        <v>0.501668</v>
+        <v>0.503922</v>
       </c>
       <c r="P192" s="28" t="n"/>
       <c r="Q192" s="28" t="n">
-        <v>-0.047882</v>
+        <v>-0.035249</v>
       </c>
       <c r="R192" s="26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S192" s="29" t="n">
         <v>0</v>
       </c>
       <c r="T192" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U192" s="24" t="inlineStr">
@@ -59451,7 +59656,7 @@
       <c r="AD192" s="24" t="n"/>
       <c r="AE192" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6242; executable ask 0.5500 (aec-mlb-sd-az-2026-08-04); model edge vs ask -0.0483.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.5400 (aec-mlb-sd-az-2026-08-04); model edge vs ask -0.0361. NOTE: NO_CALL_STARTER_ERA_GAP_INSUFFICIENT_HISTORY unavailable for this game — defaulted to neutral, other features used normally.</t>
         </is>
       </c>
       <c r="AF192" s="31" t="inlineStr">
@@ -59535,7 +59740,7 @@
       </c>
       <c r="BA192" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB192" s="24" t="inlineStr">
@@ -59545,17 +59750,17 @@
       </c>
       <c r="BC192" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD192" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE192" s="24" t="inlineStr">
         <is>
-          <t>2f493ff6e1e8d90a</t>
+          <t>3a529a8e501822ee</t>
         </is>
       </c>
       <c r="BF192" s="24" t="inlineStr">
@@ -59565,12 +59770,12 @@
       </c>
       <c r="BG192" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH192" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:24.768428Z</t>
+          <t>2026-08-04T14:23:14.034829Z</t>
         </is>
       </c>
       <c r="BI192" s="24" t="inlineStr">
@@ -59580,16 +59785,16 @@
       </c>
       <c r="BJ192" s="25" t="n"/>
       <c r="BK192" s="26" t="n">
-        <v>-122</v>
+        <v>-117</v>
       </c>
       <c r="BL192" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.854701</v>
       </c>
       <c r="BM192" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.539171</v>
       </c>
       <c r="BN192" s="28" t="n">
-        <v>0.547264</v>
+        <v>0.537313</v>
       </c>
       <c r="BO192" s="28" t="n"/>
       <c r="BP192" s="25" t="n"/>
@@ -59625,13 +59830,13 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="CG192" s="24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="CG192" s="24" t="n"/>
       <c r="CH192" s="24" t="n"/>
-      <c r="CI192" s="24" t="n"/>
+      <c r="CI192" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_STARTER_ERA_GAP_INSUFFICIENT_HISTORY</t>
+        </is>
+      </c>
       <c r="CJ192" s="24" t="inlineStr">
         <is>
           <t>-0.127634</t>
@@ -59640,19 +59845,24 @@
       <c r="CK192" s="24" t="n"/>
       <c r="CL192" s="24" t="inlineStr">
         <is>
-          <t>-0.050453</t>
-        </is>
-      </c>
-      <c r="CM192" s="24" t="n"/>
+          <t>-0.132604</t>
+        </is>
+      </c>
+      <c r="CM192" s="24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="CN192" s="24" t="n"/>
       <c r="CO192" s="24" t="n"/>
       <c r="CP192" s="24" t="n"/>
-      <c r="CQ192" s="24" t="inlineStr">
-        <is>
-          <t>0.501668</t>
-        </is>
-      </c>
+      <c r="CQ192" s="24" t="n"/>
       <c r="CR192" s="24" t="inlineStr">
+        <is>
+          <t>0.503922</t>
+        </is>
+      </c>
+      <c r="CS192" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -59661,12 +59871,12 @@
     <row r="193" ht="36" customHeight="1">
       <c r="A193" s="24" t="inlineStr">
         <is>
-          <t>a63e8ea522ad47f1</t>
+          <t>a5061d0d39ad4a38</t>
         </is>
       </c>
       <c r="B193" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C193" s="24" t="inlineStr">
@@ -59722,13 +59932,13 @@
         <v>0.619772</v>
       </c>
       <c r="O193" s="28" t="n">
-        <v>0.559361</v>
+        <v>0.56005</v>
       </c>
       <c r="P193" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q193" s="28" t="n">
-        <v>-0.060411</v>
+        <v>-0.059722</v>
       </c>
       <c r="R193" s="26" t="n">
         <v>0</v>
@@ -59757,7 +59967,7 @@
       <c r="AD193" s="24" t="n"/>
       <c r="AE193" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.87-4.68; raw selected-side p=0.5904, calibrated p=0.5594.</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.87-4.68; raw selected-side p=0.5915, calibrated p=0.5601.</t>
         </is>
       </c>
       <c r="AF193" s="31" t="inlineStr">
@@ -59876,7 +60086,7 @@
       </c>
       <c r="BH193" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI193" s="24" t="inlineStr">
@@ -59928,7 +60138,8 @@
       <c r="CO193" s="24" t="n"/>
       <c r="CP193" s="24" t="n"/>
       <c r="CQ193" s="24" t="n"/>
-      <c r="CR193" s="24" t="inlineStr">
+      <c r="CR193" s="24" t="n"/>
+      <c r="CS193" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -59937,12 +60148,12 @@
     <row r="194" ht="36" customHeight="1">
       <c r="A194" s="24" t="inlineStr">
         <is>
-          <t>06af622abdde4b22</t>
+          <t>b7c4073b43b74821</t>
         </is>
       </c>
       <c r="B194" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C194" s="24" t="inlineStr">
@@ -59981,7 +60192,7 @@
         </is>
       </c>
       <c r="J194" s="25" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="K194" s="24" t="inlineStr">
         <is>
@@ -59989,25 +60200,25 @@
         </is>
       </c>
       <c r="L194" s="26" t="n">
-        <v>-113</v>
+        <v>122</v>
       </c>
       <c r="M194" s="27" t="n">
-        <v>1.884956</v>
+        <v>2.22</v>
       </c>
       <c r="N194" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.45045</v>
       </c>
       <c r="O194" s="28" t="n">
-        <v>0.5548650000000001</v>
+        <v>0.514254</v>
       </c>
       <c r="P194" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q194" s="28" t="n">
-        <v>0.024349</v>
+        <v>0.063804</v>
       </c>
       <c r="R194" s="26" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="S194" s="29" t="n">
         <v>1</v>
@@ -60033,7 +60244,7 @@
       <c r="AD194" s="24" t="n"/>
       <c r="AE194" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.87-4.68; raw selected-side p=0.6373, calibrated p=0.5549.</t>
+          <t>Measured Edge Totals: Trend Engine projected 3.87-4.68; raw selected-side p=0.5184, calibrated p=0.5143.</t>
         </is>
       </c>
       <c r="AF194" s="31" t="inlineStr">
@@ -60152,7 +60363,7 @@
       </c>
       <c r="BH194" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI194" s="24" t="inlineStr">
@@ -60161,19 +60372,19 @@
         </is>
       </c>
       <c r="BJ194" s="25" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK194" s="26" t="n">
-        <v>-113</v>
+        <v>122</v>
       </c>
       <c r="BL194" s="27" t="n">
-        <v>1.884956</v>
+        <v>2.22</v>
       </c>
       <c r="BM194" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.45045</v>
       </c>
       <c r="BN194" s="28" t="n">
-        <v>0.527363</v>
+        <v>0.447761</v>
       </c>
       <c r="BO194" s="28" t="n"/>
       <c r="BP194" s="25" t="n"/>
@@ -60204,7 +60415,8 @@
       <c r="CO194" s="24" t="n"/>
       <c r="CP194" s="24" t="n"/>
       <c r="CQ194" s="24" t="n"/>
-      <c r="CR194" s="24" t="inlineStr">
+      <c r="CR194" s="24" t="n"/>
+      <c r="CS194" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -60213,12 +60425,12 @@
     <row r="195" ht="36" customHeight="1">
       <c r="A195" s="24" t="inlineStr">
         <is>
-          <t>e7c5f25b4703405b</t>
+          <t>a5c045c8722b4b08</t>
         </is>
       </c>
       <c r="B195" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C195" s="24" t="inlineStr">
@@ -60274,16 +60486,16 @@
         <v>0.619772</v>
       </c>
       <c r="O195" s="28" t="n">
-        <v>0.602336</v>
+        <v>0.600007</v>
       </c>
       <c r="P195" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q195" s="28" t="n">
-        <v>-0.017436</v>
+        <v>-0.019765</v>
       </c>
       <c r="R195" s="26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S195" s="29" t="n">
         <v>1.5</v>
@@ -60309,7 +60521,7 @@
       <c r="AD195" s="24" t="n"/>
       <c r="AE195" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.10-4.32; raw selected-side p=0.6559, calibrated p=0.6023.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.10-4.32; raw selected-side p=0.6523, calibrated p=0.6000.</t>
         </is>
       </c>
       <c r="AF195" s="31" t="inlineStr">
@@ -60428,7 +60640,7 @@
       </c>
       <c r="BH195" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI195" s="24" t="inlineStr">
@@ -60480,7 +60692,8 @@
       <c r="CO195" s="24" t="n"/>
       <c r="CP195" s="24" t="n"/>
       <c r="CQ195" s="24" t="n"/>
-      <c r="CR195" s="24" t="inlineStr">
+      <c r="CR195" s="24" t="n"/>
+      <c r="CS195" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -60489,12 +60702,12 @@
     <row r="196" ht="36" customHeight="1">
       <c r="A196" s="24" t="inlineStr">
         <is>
-          <t>9eb4079d4c914a43</t>
+          <t>067a29588f3f461b</t>
         </is>
       </c>
       <c r="B196" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C196" s="24" t="inlineStr">
@@ -60541,25 +60754,25 @@
         </is>
       </c>
       <c r="L196" s="26" t="n">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="M196" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.943396</v>
       </c>
       <c r="N196" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.514563</v>
       </c>
       <c r="O196" s="28" t="n">
-        <v>0.523634</v>
+        <v>0.521567</v>
       </c>
       <c r="P196" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q196" s="28" t="n">
-        <v>0.01383</v>
+        <v>0.007004</v>
       </c>
       <c r="R196" s="26" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S196" s="29" t="n">
         <v>1</v>
@@ -60585,7 +60798,7 @@
       <c r="AD196" s="24" t="n"/>
       <c r="AE196" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.10-4.32; raw selected-side p=0.5459, calibrated p=0.5236.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.10-4.32; raw selected-side p=0.5399, calibrated p=0.5216.</t>
         </is>
       </c>
       <c r="AF196" s="31" t="inlineStr">
@@ -60704,7 +60917,7 @@
       </c>
       <c r="BH196" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI196" s="24" t="inlineStr">
@@ -60716,16 +60929,16 @@
         <v>7.5</v>
       </c>
       <c r="BK196" s="26" t="n">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="BL196" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.943396</v>
       </c>
       <c r="BM196" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.514563</v>
       </c>
       <c r="BN196" s="28" t="n">
-        <v>0.507463</v>
+        <v>0.5124379999999999</v>
       </c>
       <c r="BO196" s="28" t="n"/>
       <c r="BP196" s="25" t="n"/>
@@ -60756,7 +60969,8 @@
       <c r="CO196" s="24" t="n"/>
       <c r="CP196" s="24" t="n"/>
       <c r="CQ196" s="24" t="n"/>
-      <c r="CR196" s="24" t="inlineStr">
+      <c r="CR196" s="24" t="n"/>
+      <c r="CS196" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -60765,12 +60979,12 @@
     <row r="197" ht="36" customHeight="1">
       <c r="A197" s="24" t="inlineStr">
         <is>
-          <t>0327168d3b4b4358</t>
+          <t>55c227db771b4e23</t>
         </is>
       </c>
       <c r="B197" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C197" s="24" t="inlineStr">
@@ -60817,25 +61031,25 @@
         </is>
       </c>
       <c r="L197" s="26" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="M197" s="27" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="N197" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.460829</v>
       </c>
       <c r="O197" s="28" t="n">
-        <v>0.537481</v>
+        <v>0.540597</v>
       </c>
       <c r="P197" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q197" s="28" t="n">
-        <v>0.06354700000000001</v>
+        <v>0.07976800000000001</v>
       </c>
       <c r="R197" s="26" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="S197" s="29" t="n">
         <v>1</v>
@@ -60861,7 +61075,7 @@
       <c r="AD197" s="24" t="n"/>
       <c r="AE197" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.92-5.03; raw selected-side p=0.5571, calibrated p=0.5375.</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.92-5.03; raw selected-side p=0.5618, calibrated p=0.5406.</t>
         </is>
       </c>
       <c r="AF197" s="31" t="inlineStr">
@@ -60980,7 +61194,7 @@
       </c>
       <c r="BH197" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI197" s="24" t="inlineStr">
@@ -60992,16 +61206,16 @@
         <v>1.5</v>
       </c>
       <c r="BK197" s="26" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="BL197" s="27" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="BM197" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.460829</v>
       </c>
       <c r="BN197" s="28" t="n">
-        <v>0.472637</v>
+        <v>0.457711</v>
       </c>
       <c r="BO197" s="28" t="n"/>
       <c r="BP197" s="25" t="n"/>
@@ -61032,7 +61246,8 @@
       <c r="CO197" s="24" t="n"/>
       <c r="CP197" s="24" t="n"/>
       <c r="CQ197" s="24" t="n"/>
-      <c r="CR197" s="24" t="inlineStr">
+      <c r="CR197" s="24" t="n"/>
+      <c r="CS197" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -61041,12 +61256,12 @@
     <row r="198" ht="36" customHeight="1">
       <c r="A198" s="24" t="inlineStr">
         <is>
-          <t>ea28b607642a49de</t>
+          <t>524bb9401e074d18</t>
         </is>
       </c>
       <c r="B198" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C198" s="24" t="inlineStr">
@@ -61093,25 +61308,25 @@
         </is>
       </c>
       <c r="L198" s="26" t="n">
-        <v>-113</v>
+        <v>-117</v>
       </c>
       <c r="M198" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.854701</v>
       </c>
       <c r="N198" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.539171</v>
       </c>
       <c r="O198" s="28" t="n">
-        <v>0.511111</v>
+        <v>0.511059</v>
       </c>
       <c r="P198" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q198" s="28" t="n">
-        <v>-0.019405</v>
+        <v>-0.028112</v>
       </c>
       <c r="R198" s="26" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="S198" s="29" t="n">
         <v>1</v>
@@ -61137,7 +61352,7 @@
       <c r="AD198" s="24" t="n"/>
       <c r="AE198" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.92-5.03; raw selected-side p=0.5092, calibrated p=0.5111.</t>
+          <t>Measured Edge Totals: Trend Engine projected 3.92-5.03; raw selected-side p=0.5091, calibrated p=0.5111.</t>
         </is>
       </c>
       <c r="AF198" s="31" t="inlineStr">
@@ -61256,7 +61471,7 @@
       </c>
       <c r="BH198" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI198" s="24" t="inlineStr">
@@ -61268,16 +61483,16 @@
         <v>8.5</v>
       </c>
       <c r="BK198" s="26" t="n">
-        <v>-113</v>
+        <v>-117</v>
       </c>
       <c r="BL198" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.854701</v>
       </c>
       <c r="BM198" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.539171</v>
       </c>
       <c r="BN198" s="28" t="n">
-        <v>0.527363</v>
+        <v>0.537313</v>
       </c>
       <c r="BO198" s="28" t="n"/>
       <c r="BP198" s="25" t="n"/>
@@ -61308,7 +61523,8 @@
       <c r="CO198" s="24" t="n"/>
       <c r="CP198" s="24" t="n"/>
       <c r="CQ198" s="24" t="n"/>
-      <c r="CR198" s="24" t="inlineStr">
+      <c r="CR198" s="24" t="n"/>
+      <c r="CS198" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -61317,12 +61533,12 @@
     <row r="199" ht="36" customHeight="1">
       <c r="A199" s="24" t="inlineStr">
         <is>
-          <t>38ce62c228284f37</t>
+          <t>57528052036d4a88</t>
         </is>
       </c>
       <c r="B199" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C199" s="24" t="inlineStr">
@@ -61369,25 +61585,25 @@
         </is>
       </c>
       <c r="L199" s="26" t="n">
-        <v>-135</v>
+        <v>-120</v>
       </c>
       <c r="M199" s="27" t="n">
-        <v>1.740741</v>
+        <v>1.833333</v>
       </c>
       <c r="N199" s="28" t="n">
-        <v>0.574468</v>
+        <v>0.545455</v>
       </c>
       <c r="O199" s="28" t="n">
-        <v>0.611882</v>
+        <v>0.612998</v>
       </c>
       <c r="P199" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q199" s="28" t="n">
-        <v>0.037414</v>
+        <v>0.06754300000000001</v>
       </c>
       <c r="R199" s="26" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="S199" s="29" t="n">
         <v>1.5</v>
@@ -61413,7 +61629,7 @@
       <c r="AD199" s="24" t="n"/>
       <c r="AE199" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.35-4.35; raw selected-side p=0.6704, calibrated p=0.6119.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.35-4.35; raw selected-side p=0.6722, calibrated p=0.6130.</t>
         </is>
       </c>
       <c r="AF199" s="31" t="inlineStr">
@@ -61532,7 +61748,7 @@
       </c>
       <c r="BH199" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI199" s="24" t="inlineStr">
@@ -61544,16 +61760,16 @@
         <v>1.5</v>
       </c>
       <c r="BK199" s="26" t="n">
-        <v>-135</v>
+        <v>-120</v>
       </c>
       <c r="BL199" s="27" t="n">
-        <v>1.740741</v>
+        <v>1.833333</v>
       </c>
       <c r="BM199" s="28" t="n">
-        <v>0.574468</v>
+        <v>0.545455</v>
       </c>
       <c r="BN199" s="28" t="n">
-        <v>0.572139</v>
+        <v>0.542289</v>
       </c>
       <c r="BO199" s="28" t="n"/>
       <c r="BP199" s="25" t="n"/>
@@ -61584,7 +61800,8 @@
       <c r="CO199" s="24" t="n"/>
       <c r="CP199" s="24" t="n"/>
       <c r="CQ199" s="24" t="n"/>
-      <c r="CR199" s="24" t="inlineStr">
+      <c r="CR199" s="24" t="n"/>
+      <c r="CS199" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -61593,12 +61810,12 @@
     <row r="200" ht="36" customHeight="1">
       <c r="A200" s="24" t="inlineStr">
         <is>
-          <t>ca5fe66e272841d9</t>
+          <t>2159da02e71344f2</t>
         </is>
       </c>
       <c r="B200" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C200" s="24" t="inlineStr">
@@ -61645,25 +61862,25 @@
         </is>
       </c>
       <c r="L200" s="26" t="n">
-        <v>-108</v>
+        <v>-111</v>
       </c>
       <c r="M200" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.900901</v>
       </c>
       <c r="N200" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.526066</v>
       </c>
       <c r="O200" s="28" t="n">
-        <v>0.513093</v>
+        <v>0.510786</v>
       </c>
       <c r="P200" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q200" s="28" t="n">
-        <v>-0.006138</v>
+        <v>-0.01528</v>
       </c>
       <c r="R200" s="26" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="S200" s="29" t="n">
         <v>1</v>
@@ -61689,7 +61906,7 @@
       <c r="AD200" s="24" t="n"/>
       <c r="AE200" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.35-4.35; raw selected-side p=0.5151, calibrated p=0.5131.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.35-4.35; raw selected-side p=0.5083, calibrated p=0.5108.</t>
         </is>
       </c>
       <c r="AF200" s="31" t="inlineStr">
@@ -61808,7 +62025,7 @@
       </c>
       <c r="BH200" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI200" s="24" t="inlineStr">
@@ -61820,16 +62037,16 @@
         <v>8.5</v>
       </c>
       <c r="BK200" s="26" t="n">
-        <v>-108</v>
+        <v>-111</v>
       </c>
       <c r="BL200" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.900901</v>
       </c>
       <c r="BM200" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.526066</v>
       </c>
       <c r="BN200" s="28" t="n">
-        <v>0.517413</v>
+        <v>0.522388</v>
       </c>
       <c r="BO200" s="28" t="n"/>
       <c r="BP200" s="25" t="n"/>
@@ -61860,7 +62077,8 @@
       <c r="CO200" s="24" t="n"/>
       <c r="CP200" s="24" t="n"/>
       <c r="CQ200" s="24" t="n"/>
-      <c r="CR200" s="24" t="inlineStr">
+      <c r="CR200" s="24" t="n"/>
+      <c r="CS200" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -61869,12 +62087,12 @@
     <row r="201" ht="36" customHeight="1">
       <c r="A201" s="24" t="inlineStr">
         <is>
-          <t>7500acedd4784676</t>
+          <t>b89f05f334b14253</t>
         </is>
       </c>
       <c r="B201" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C201" s="24" t="inlineStr">
@@ -61921,22 +62139,22 @@
         </is>
       </c>
       <c r="L201" s="26" t="n">
-        <v>-178</v>
+        <v>-174</v>
       </c>
       <c r="M201" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.574713</v>
       </c>
       <c r="N201" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.635036</v>
       </c>
       <c r="O201" s="28" t="n">
-        <v>0.561067</v>
+        <v>0.558902</v>
       </c>
       <c r="P201" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q201" s="28" t="n">
-        <v>-0.079221</v>
+        <v>-0.07613399999999999</v>
       </c>
       <c r="R201" s="26" t="n">
         <v>0</v>
@@ -61965,7 +62183,7 @@
       <c r="AD201" s="24" t="n"/>
       <c r="AE201" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.37-5.16; raw selected-side p=0.5930, calibrated p=0.5611.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.37-5.16; raw selected-side p=0.5897, calibrated p=0.5589.</t>
         </is>
       </c>
       <c r="AF201" s="31" t="inlineStr">
@@ -62084,7 +62302,7 @@
       </c>
       <c r="BH201" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI201" s="24" t="inlineStr">
@@ -62096,16 +62314,16 @@
         <v>1.5</v>
       </c>
       <c r="BK201" s="26" t="n">
-        <v>-178</v>
+        <v>-174</v>
       </c>
       <c r="BL201" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.574713</v>
       </c>
       <c r="BM201" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.635036</v>
       </c>
       <c r="BN201" s="28" t="n">
-        <v>0.636816</v>
+        <v>0.631841</v>
       </c>
       <c r="BO201" s="28" t="n"/>
       <c r="BP201" s="25" t="n"/>
@@ -62136,7 +62354,8 @@
       <c r="CO201" s="24" t="n"/>
       <c r="CP201" s="24" t="n"/>
       <c r="CQ201" s="24" t="n"/>
-      <c r="CR201" s="24" t="inlineStr">
+      <c r="CR201" s="24" t="n"/>
+      <c r="CS201" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -62145,12 +62364,12 @@
     <row r="202" ht="36" customHeight="1">
       <c r="A202" s="24" t="inlineStr">
         <is>
-          <t>923a6ae1326f441e</t>
+          <t>cdbededbc14d4000</t>
         </is>
       </c>
       <c r="B202" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C202" s="24" t="inlineStr">
@@ -62197,25 +62416,25 @@
         </is>
       </c>
       <c r="L202" s="26" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="M202" s="27" t="n">
-        <v>1.8</v>
+        <v>1.819672</v>
       </c>
       <c r="N202" s="28" t="n">
-        <v>0.555556</v>
+        <v>0.54955</v>
       </c>
       <c r="O202" s="28" t="n">
-        <v>0.530246</v>
+        <v>0.529648</v>
       </c>
       <c r="P202" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q202" s="28" t="n">
-        <v>-0.02531</v>
+        <v>-0.019902</v>
       </c>
       <c r="R202" s="26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S202" s="29" t="n">
         <v>1</v>
@@ -62241,7 +62460,7 @@
       <c r="AD202" s="24" t="n"/>
       <c r="AE202" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.37-5.16; raw selected-side p=0.5653, calibrated p=0.5302.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.37-5.16; raw selected-side p=0.5635, calibrated p=0.5296.</t>
         </is>
       </c>
       <c r="AF202" s="31" t="inlineStr">
@@ -62360,7 +62579,7 @@
       </c>
       <c r="BH202" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI202" s="24" t="inlineStr">
@@ -62372,16 +62591,16 @@
         <v>8.5</v>
       </c>
       <c r="BK202" s="26" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="BL202" s="27" t="n">
-        <v>1.8</v>
+        <v>1.819672</v>
       </c>
       <c r="BM202" s="28" t="n">
-        <v>0.555556</v>
+        <v>0.54955</v>
       </c>
       <c r="BN202" s="28" t="n">
-        <v>0.552239</v>
+        <v>0.547264</v>
       </c>
       <c r="BO202" s="28" t="n"/>
       <c r="BP202" s="25" t="n"/>
@@ -62412,7 +62631,8 @@
       <c r="CO202" s="24" t="n"/>
       <c r="CP202" s="24" t="n"/>
       <c r="CQ202" s="24" t="n"/>
-      <c r="CR202" s="24" t="inlineStr">
+      <c r="CR202" s="24" t="n"/>
+      <c r="CS202" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -62421,12 +62641,12 @@
     <row r="203" ht="36" customHeight="1">
       <c r="A203" s="24" t="inlineStr">
         <is>
-          <t>601e003503bc4eda</t>
+          <t>e7b0e2bb23794399</t>
         </is>
       </c>
       <c r="B203" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C203" s="24" t="inlineStr">
@@ -62482,16 +62702,16 @@
         <v>0.6</v>
       </c>
       <c r="O203" s="28" t="n">
-        <v>0.563298</v>
+        <v>0.567661</v>
       </c>
       <c r="P203" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q203" s="28" t="n">
-        <v>-0.036702</v>
+        <v>-0.032339</v>
       </c>
       <c r="R203" s="26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S203" s="29" t="n">
         <v>1.25</v>
@@ -62517,7 +62737,7 @@
       <c r="AD203" s="24" t="n"/>
       <c r="AE203" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.10-4.82; raw selected-side p=0.5964, calibrated p=0.5633.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.10-4.82; raw selected-side p=0.6030, calibrated p=0.5677.</t>
         </is>
       </c>
       <c r="AF203" s="31" t="inlineStr">
@@ -62636,7 +62856,7 @@
       </c>
       <c r="BH203" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI203" s="24" t="inlineStr">
@@ -62688,7 +62908,8 @@
       <c r="CO203" s="24" t="n"/>
       <c r="CP203" s="24" t="n"/>
       <c r="CQ203" s="24" t="n"/>
-      <c r="CR203" s="24" t="inlineStr">
+      <c r="CR203" s="24" t="n"/>
+      <c r="CS203" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -62697,12 +62918,12 @@
     <row r="204" ht="36" customHeight="1">
       <c r="A204" s="24" t="inlineStr">
         <is>
-          <t>77e0f7ad0b6b4369</t>
+          <t>4c5441277aff4a8e</t>
         </is>
       </c>
       <c r="B204" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C204" s="24" t="inlineStr">
@@ -62749,25 +62970,25 @@
         </is>
       </c>
       <c r="L204" s="26" t="n">
-        <v>-120</v>
+        <v>-113</v>
       </c>
       <c r="M204" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.884956</v>
       </c>
       <c r="N204" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.530516</v>
       </c>
       <c r="O204" s="28" t="n">
-        <v>0.542496</v>
+        <v>0.54376</v>
       </c>
       <c r="P204" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q204" s="28" t="n">
-        <v>-0.002959</v>
+        <v>0.013244</v>
       </c>
       <c r="R204" s="26" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="S204" s="29" t="n">
         <v>1</v>
@@ -62793,7 +63014,7 @@
       <c r="AD204" s="24" t="n"/>
       <c r="AE204" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.10-4.82; raw selected-side p=0.6011, calibrated p=0.5425.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.10-4.82; raw selected-side p=0.6048, calibrated p=0.5438.</t>
         </is>
       </c>
       <c r="AF204" s="31" t="inlineStr">
@@ -62912,7 +63133,7 @@
       </c>
       <c r="BH204" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI204" s="24" t="inlineStr">
@@ -62924,16 +63145,16 @@
         <v>9.5</v>
       </c>
       <c r="BK204" s="26" t="n">
-        <v>-120</v>
+        <v>-113</v>
       </c>
       <c r="BL204" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.884956</v>
       </c>
       <c r="BM204" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.530516</v>
       </c>
       <c r="BN204" s="28" t="n">
-        <v>0.542289</v>
+        <v>0.527363</v>
       </c>
       <c r="BO204" s="28" t="n"/>
       <c r="BP204" s="25" t="n"/>
@@ -62964,21 +63185,22 @@
       <c r="CO204" s="24" t="n"/>
       <c r="CP204" s="24" t="n"/>
       <c r="CQ204" s="24" t="n"/>
-      <c r="CR204" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR204" s="24" t="n"/>
+      <c r="CS204" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="205" ht="36" customHeight="1">
       <c r="A205" s="24" t="inlineStr">
         <is>
-          <t>c383ac59b6c747f5</t>
+          <t>f284a96eb71d4942</t>
         </is>
       </c>
       <c r="B205" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C205" s="24" t="inlineStr">
@@ -63025,25 +63247,25 @@
         </is>
       </c>
       <c r="L205" s="26" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="M205" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.819672</v>
       </c>
       <c r="N205" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.54955</v>
       </c>
       <c r="O205" s="28" t="n">
-        <v>0.702982</v>
+        <v>0.700193</v>
       </c>
       <c r="P205" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q205" s="28" t="n">
-        <v>0.157527</v>
+        <v>0.150643</v>
       </c>
       <c r="R205" s="26" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="S205" s="29" t="n">
         <v>2</v>
@@ -63069,7 +63291,7 @@
       <c r="AD205" s="24" t="n"/>
       <c r="AE205" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.16-4.32; raw selected-side p=0.8093, calibrated p=0.7030.</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.16-4.32; raw selected-side p=0.8051, calibrated p=0.7002.</t>
         </is>
       </c>
       <c r="AF205" s="31" t="inlineStr">
@@ -63188,7 +63410,7 @@
       </c>
       <c r="BH205" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI205" s="24" t="inlineStr">
@@ -63200,16 +63422,16 @@
         <v>1.5</v>
       </c>
       <c r="BK205" s="26" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="BL205" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.819672</v>
       </c>
       <c r="BM205" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.54955</v>
       </c>
       <c r="BN205" s="28" t="n">
-        <v>0.542289</v>
+        <v>0.547264</v>
       </c>
       <c r="BO205" s="28" t="n"/>
       <c r="BP205" s="25" t="n"/>
@@ -63240,7 +63462,8 @@
       <c r="CO205" s="24" t="n"/>
       <c r="CP205" s="24" t="n"/>
       <c r="CQ205" s="24" t="n"/>
-      <c r="CR205" s="24" t="inlineStr">
+      <c r="CR205" s="24" t="n"/>
+      <c r="CS205" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -63249,12 +63472,12 @@
     <row r="206" ht="36" customHeight="1">
       <c r="A206" s="24" t="inlineStr">
         <is>
-          <t>76192f649d7f4595</t>
+          <t>5f61ad438f4e471d</t>
         </is>
       </c>
       <c r="B206" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C206" s="24" t="inlineStr">
@@ -63310,16 +63533,16 @@
         <v>0.545455</v>
       </c>
       <c r="O206" s="28" t="n">
-        <v>0.590214</v>
+        <v>0.587703</v>
       </c>
       <c r="P206" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q206" s="28" t="n">
-        <v>0.044759</v>
+        <v>0.042248</v>
       </c>
       <c r="R206" s="26" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S206" s="29" t="n">
         <v>1.25</v>
@@ -63345,7 +63568,7 @@
       <c r="AD206" s="24" t="n"/>
       <c r="AE206" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.16-4.32; raw selected-side p=0.7408, calibrated p=0.5902.</t>
+          <t>Measured Edge Totals: Trend Engine projected 3.16-4.32; raw selected-side p=0.7334, calibrated p=0.5877.</t>
         </is>
       </c>
       <c r="AF206" s="31" t="inlineStr">
@@ -63464,7 +63687,7 @@
       </c>
       <c r="BH206" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI206" s="24" t="inlineStr">
@@ -63516,7 +63739,8 @@
       <c r="CO206" s="24" t="n"/>
       <c r="CP206" s="24" t="n"/>
       <c r="CQ206" s="24" t="n"/>
-      <c r="CR206" s="24" t="inlineStr">
+      <c r="CR206" s="24" t="n"/>
+      <c r="CS206" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -63525,12 +63749,12 @@
     <row r="207" ht="36" customHeight="1">
       <c r="A207" s="24" t="inlineStr">
         <is>
-          <t>d908c8a36f45466c</t>
+          <t>49c4715d80c0469b</t>
         </is>
       </c>
       <c r="B207" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C207" s="24" t="inlineStr">
@@ -63577,25 +63801,25 @@
         </is>
       </c>
       <c r="L207" s="26" t="n">
-        <v>-150</v>
+        <v>-147</v>
       </c>
       <c r="M207" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.680272</v>
       </c>
       <c r="N207" s="28" t="n">
-        <v>0.6</v>
+        <v>0.5951419999999999</v>
       </c>
       <c r="O207" s="28" t="n">
-        <v>0.593511</v>
+        <v>0.597054</v>
       </c>
       <c r="P207" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q207" s="28" t="n">
-        <v>-0.006489</v>
+        <v>0.001912</v>
       </c>
       <c r="R207" s="26" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="S207" s="29" t="n">
         <v>1.25</v>
@@ -63621,7 +63845,7 @@
       <c r="AD207" s="24" t="n"/>
       <c r="AE207" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.58-4.00; raw selected-side p=0.6424, calibrated p=0.5935.</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.58-4.00; raw selected-side p=0.6479, calibrated p=0.5971.</t>
         </is>
       </c>
       <c r="AF207" s="31" t="inlineStr">
@@ -63740,7 +63964,7 @@
       </c>
       <c r="BH207" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI207" s="24" t="inlineStr">
@@ -63752,16 +63976,16 @@
         <v>1.5</v>
       </c>
       <c r="BK207" s="26" t="n">
-        <v>-150</v>
+        <v>-147</v>
       </c>
       <c r="BL207" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.680272</v>
       </c>
       <c r="BM207" s="28" t="n">
-        <v>0.6</v>
+        <v>0.5951419999999999</v>
       </c>
       <c r="BN207" s="28" t="n">
-        <v>0.597015</v>
+        <v>0.59204</v>
       </c>
       <c r="BO207" s="28" t="n"/>
       <c r="BP207" s="25" t="n"/>
@@ -63792,21 +64016,22 @@
       <c r="CO207" s="24" t="n"/>
       <c r="CP207" s="24" t="n"/>
       <c r="CQ207" s="24" t="n"/>
-      <c r="CR207" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR207" s="24" t="n"/>
+      <c r="CS207" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="208" ht="36" customHeight="1">
       <c r="A208" s="24" t="inlineStr">
         <is>
-          <t>5b1358e2f54c4a67</t>
+          <t>5635cb5568624ec0</t>
         </is>
       </c>
       <c r="B208" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C208" s="24" t="inlineStr">
@@ -63853,25 +64078,25 @@
         </is>
       </c>
       <c r="L208" s="26" t="n">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="M208" s="27" t="n">
-        <v>2</v>
+        <v>1.943396</v>
       </c>
       <c r="N208" s="28" t="n">
-        <v>0.5</v>
+        <v>0.514563</v>
       </c>
       <c r="O208" s="28" t="n">
-        <v>0.52237</v>
+        <v>0.523429</v>
       </c>
       <c r="P208" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q208" s="28" t="n">
-        <v>0.02237</v>
+        <v>0.008866000000000001</v>
       </c>
       <c r="R208" s="26" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="S208" s="29" t="n">
         <v>1</v>
@@ -63897,7 +64122,7 @@
       <c r="AD208" s="24" t="n"/>
       <c r="AE208" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.58-4.00; raw selected-side p=0.5422, calibrated p=0.5224.</t>
+          <t>Measured Edge Totals: Trend Engine projected 3.58-4.00; raw selected-side p=0.5453, calibrated p=0.5234.</t>
         </is>
       </c>
       <c r="AF208" s="31" t="inlineStr">
@@ -64016,7 +64241,7 @@
       </c>
       <c r="BH208" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI208" s="24" t="inlineStr">
@@ -64028,16 +64253,16 @@
         <v>7.5</v>
       </c>
       <c r="BK208" s="26" t="n">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="BL208" s="27" t="n">
-        <v>2</v>
+        <v>1.943396</v>
       </c>
       <c r="BM208" s="28" t="n">
-        <v>0.5</v>
+        <v>0.514563</v>
       </c>
       <c r="BN208" s="28" t="n">
-        <v>0.497512</v>
+        <v>0.509901</v>
       </c>
       <c r="BO208" s="28" t="n"/>
       <c r="BP208" s="25" t="n"/>
@@ -64068,7 +64293,8 @@
       <c r="CO208" s="24" t="n"/>
       <c r="CP208" s="24" t="n"/>
       <c r="CQ208" s="24" t="n"/>
-      <c r="CR208" s="24" t="inlineStr">
+      <c r="CR208" s="24" t="n"/>
+      <c r="CS208" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -64077,12 +64303,12 @@
     <row r="209" ht="36" customHeight="1">
       <c r="A209" s="24" t="inlineStr">
         <is>
-          <t>8b52316cb18e4e02</t>
+          <t>5f5a1531c272469f</t>
         </is>
       </c>
       <c r="B209" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C209" s="24" t="inlineStr">
@@ -64129,22 +64355,22 @@
         </is>
       </c>
       <c r="L209" s="26" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="M209" s="27" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="N209" s="28" t="n">
-        <v>0.454545</v>
+        <v>0.460829</v>
       </c>
       <c r="O209" s="28" t="n">
-        <v>0.626973</v>
+        <v>0.62835</v>
       </c>
       <c r="P209" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q209" s="28" t="n">
-        <v>0.172428</v>
+        <v>0.167521</v>
       </c>
       <c r="R209" s="26" t="n">
         <v>100</v>
@@ -64173,7 +64399,7 @@
       <c r="AD209" s="24" t="n"/>
       <c r="AE209" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.82-3.91; raw selected-side p=0.6935, calibrated p=0.6270.</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.82-3.91; raw selected-side p=0.6956, calibrated p=0.6284.</t>
         </is>
       </c>
       <c r="AF209" s="31" t="inlineStr">
@@ -64292,7 +64518,7 @@
       </c>
       <c r="BH209" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI209" s="24" t="inlineStr">
@@ -64304,16 +64530,16 @@
         <v>1.5</v>
       </c>
       <c r="BK209" s="26" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="BL209" s="27" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BM209" s="28" t="n">
-        <v>0.454545</v>
+        <v>0.460829</v>
       </c>
       <c r="BN209" s="28" t="n">
-        <v>0.452736</v>
+        <v>0.455446</v>
       </c>
       <c r="BO209" s="28" t="n"/>
       <c r="BP209" s="25" t="n"/>
@@ -64344,7 +64570,8 @@
       <c r="CO209" s="24" t="n"/>
       <c r="CP209" s="24" t="n"/>
       <c r="CQ209" s="24" t="n"/>
-      <c r="CR209" s="24" t="inlineStr">
+      <c r="CR209" s="24" t="n"/>
+      <c r="CS209" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -64353,12 +64580,12 @@
     <row r="210" ht="36" customHeight="1">
       <c r="A210" s="24" t="inlineStr">
         <is>
-          <t>a1c931f74b294499</t>
+          <t>0ad4a0f79bc647dd</t>
         </is>
       </c>
       <c r="B210" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C210" s="24" t="inlineStr">
@@ -64397,7 +64624,7 @@
         </is>
       </c>
       <c r="J210" s="25" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="K210" s="24" t="inlineStr">
         <is>
@@ -64405,28 +64632,28 @@
         </is>
       </c>
       <c r="L210" s="26" t="n">
-        <v>111</v>
+        <v>-122</v>
       </c>
       <c r="M210" s="27" t="n">
-        <v>2.11</v>
+        <v>1.819672</v>
       </c>
       <c r="N210" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.54955</v>
       </c>
       <c r="O210" s="28" t="n">
-        <v>0.546255</v>
+        <v>0.579434</v>
       </c>
       <c r="P210" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q210" s="28" t="n">
-        <v>0.072321</v>
+        <v>0.029884</v>
       </c>
       <c r="R210" s="26" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="S210" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T210" s="24" t="inlineStr">
         <is>
@@ -64449,7 +64676,7 @@
       <c r="AD210" s="24" t="n"/>
       <c r="AE210" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.82-3.91; raw selected-side p=0.6121, calibrated p=0.5463.</t>
+          <t>Measured Edge Totals: Trend Engine projected 3.82-3.91; raw selected-side p=0.7092, calibrated p=0.5794.</t>
         </is>
       </c>
       <c r="AF210" s="31" t="inlineStr">
@@ -64568,7 +64795,7 @@
       </c>
       <c r="BH210" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI210" s="24" t="inlineStr">
@@ -64577,19 +64804,19 @@
         </is>
       </c>
       <c r="BJ210" s="25" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="BK210" s="26" t="n">
-        <v>111</v>
+        <v>-122</v>
       </c>
       <c r="BL210" s="27" t="n">
-        <v>2.11</v>
+        <v>1.819672</v>
       </c>
       <c r="BM210" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.54955</v>
       </c>
       <c r="BN210" s="28" t="n">
-        <v>0.472637</v>
+        <v>0.547264</v>
       </c>
       <c r="BO210" s="28" t="n"/>
       <c r="BP210" s="25" t="n"/>
@@ -64620,7 +64847,8 @@
       <c r="CO210" s="24" t="n"/>
       <c r="CP210" s="24" t="n"/>
       <c r="CQ210" s="24" t="n"/>
-      <c r="CR210" s="24" t="inlineStr">
+      <c r="CR210" s="24" t="n"/>
+      <c r="CS210" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -64629,12 +64857,12 @@
     <row r="211" ht="36" customHeight="1">
       <c r="A211" s="24" t="inlineStr">
         <is>
-          <t>7c0eb143a06343b2</t>
+          <t>e7395971da7a4242</t>
         </is>
       </c>
       <c r="B211" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C211" s="24" t="inlineStr">
@@ -64681,25 +64909,25 @@
         </is>
       </c>
       <c r="L211" s="26" t="n">
-        <v>-122</v>
+        <v>-120</v>
       </c>
       <c r="M211" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.833333</v>
       </c>
       <c r="N211" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.545455</v>
       </c>
       <c r="O211" s="28" t="n">
-        <v>0.6599739999999999</v>
+        <v>0.657612</v>
       </c>
       <c r="P211" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q211" s="28" t="n">
-        <v>0.110424</v>
+        <v>0.112157</v>
       </c>
       <c r="R211" s="26" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="S211" s="29" t="n">
         <v>1.75</v>
@@ -64725,7 +64953,7 @@
       <c r="AD211" s="24" t="n"/>
       <c r="AE211" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.98-4.16; raw selected-side p=0.7438, calibrated p=0.6600.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.98-4.16; raw selected-side p=0.7401, calibrated p=0.6576.</t>
         </is>
       </c>
       <c r="AF211" s="31" t="inlineStr">
@@ -64844,7 +65072,7 @@
       </c>
       <c r="BH211" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI211" s="24" t="inlineStr">
@@ -64856,16 +65084,16 @@
         <v>1.5</v>
       </c>
       <c r="BK211" s="26" t="n">
-        <v>-122</v>
+        <v>-120</v>
       </c>
       <c r="BL211" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.833333</v>
       </c>
       <c r="BM211" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.545455</v>
       </c>
       <c r="BN211" s="28" t="n">
-        <v>0.547264</v>
+        <v>0.542289</v>
       </c>
       <c r="BO211" s="28" t="n"/>
       <c r="BP211" s="25" t="n"/>
@@ -64896,7 +65124,8 @@
       <c r="CO211" s="24" t="n"/>
       <c r="CP211" s="24" t="n"/>
       <c r="CQ211" s="24" t="n"/>
-      <c r="CR211" s="24" t="inlineStr">
+      <c r="CR211" s="24" t="n"/>
+      <c r="CS211" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -64905,12 +65134,12 @@
     <row r="212" ht="36" customHeight="1">
       <c r="A212" s="24" t="inlineStr">
         <is>
-          <t>ac0c244129e84c3d</t>
+          <t>cb0192769e5a4cee</t>
         </is>
       </c>
       <c r="B212" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C212" s="24" t="inlineStr">
@@ -64957,25 +65186,25 @@
         </is>
       </c>
       <c r="L212" s="26" t="n">
-        <v>-113</v>
+        <v>-115</v>
       </c>
       <c r="M212" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.869565</v>
       </c>
       <c r="N212" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.534884</v>
       </c>
       <c r="O212" s="28" t="n">
-        <v>0.544324</v>
+        <v>0.543008</v>
       </c>
       <c r="P212" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q212" s="28" t="n">
-        <v>0.013808</v>
+        <v>0.008123999999999999</v>
       </c>
       <c r="R212" s="26" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="S212" s="29" t="n">
         <v>1</v>
@@ -65001,7 +65230,7 @@
       <c r="AD212" s="24" t="n"/>
       <c r="AE212" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.98-4.16; raw selected-side p=0.6065, calibrated p=0.5443.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.98-4.16; raw selected-side p=0.6026, calibrated p=0.5430.</t>
         </is>
       </c>
       <c r="AF212" s="31" t="inlineStr">
@@ -65120,7 +65349,7 @@
       </c>
       <c r="BH212" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI212" s="24" t="inlineStr">
@@ -65132,16 +65361,16 @@
         <v>7.5</v>
       </c>
       <c r="BK212" s="26" t="n">
-        <v>-113</v>
+        <v>-115</v>
       </c>
       <c r="BL212" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.869565</v>
       </c>
       <c r="BM212" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.534884</v>
       </c>
       <c r="BN212" s="28" t="n">
-        <v>0.527363</v>
+        <v>0.532338</v>
       </c>
       <c r="BO212" s="28" t="n"/>
       <c r="BP212" s="25" t="n"/>
@@ -65172,7 +65401,8 @@
       <c r="CO212" s="24" t="n"/>
       <c r="CP212" s="24" t="n"/>
       <c r="CQ212" s="24" t="n"/>
-      <c r="CR212" s="24" t="inlineStr">
+      <c r="CR212" s="24" t="n"/>
+      <c r="CS212" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -65181,12 +65411,12 @@
     <row r="213" ht="36" customHeight="1">
       <c r="A213" s="24" t="inlineStr">
         <is>
-          <t>af65da97e3bb49f8</t>
+          <t>1ab8e11b08bf4246</t>
         </is>
       </c>
       <c r="B213" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C213" s="24" t="inlineStr">
@@ -65242,13 +65472,13 @@
         <v>0.640288</v>
       </c>
       <c r="O213" s="28" t="n">
-        <v>0.577995</v>
+        <v>0.577535</v>
       </c>
       <c r="P213" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q213" s="28" t="n">
-        <v>-0.062293</v>
+        <v>-0.062753</v>
       </c>
       <c r="R213" s="26" t="n">
         <v>0</v>
@@ -65277,7 +65507,7 @@
       <c r="AD213" s="24" t="n"/>
       <c r="AE213" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.31-4.86; raw selected-side p=0.6188, calibrated p=0.5780.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.31-4.86; raw selected-side p=0.6181, calibrated p=0.5775.</t>
         </is>
       </c>
       <c r="AF213" s="31" t="inlineStr">
@@ -65396,7 +65626,7 @@
       </c>
       <c r="BH213" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI213" s="24" t="inlineStr">
@@ -65448,7 +65678,8 @@
       <c r="CO213" s="24" t="n"/>
       <c r="CP213" s="24" t="n"/>
       <c r="CQ213" s="24" t="n"/>
-      <c r="CR213" s="24" t="inlineStr">
+      <c r="CR213" s="24" t="n"/>
+      <c r="CS213" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -65457,12 +65688,12 @@
     <row r="214" ht="36" customHeight="1">
       <c r="A214" s="24" t="inlineStr">
         <is>
-          <t>ef3a681efff84e09</t>
+          <t>6aa689583a734862</t>
         </is>
       </c>
       <c r="B214" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C214" s="24" t="inlineStr">
@@ -65518,16 +65749,16 @@
         <v>0.490196</v>
       </c>
       <c r="O214" s="28" t="n">
-        <v>0.515724</v>
+        <v>0.516834</v>
       </c>
       <c r="P214" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q214" s="28" t="n">
-        <v>0.025528</v>
+        <v>0.026638</v>
       </c>
       <c r="R214" s="26" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S214" s="29" t="n">
         <v>1</v>
@@ -65553,7 +65784,7 @@
       <c r="AD214" s="24" t="n"/>
       <c r="AE214" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.31-4.86; raw selected-side p=0.5228, calibrated p=0.5157.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.31-4.86; raw selected-side p=0.5260, calibrated p=0.5168.</t>
         </is>
       </c>
       <c r="AF214" s="31" t="inlineStr">
@@ -65672,7 +65903,7 @@
       </c>
       <c r="BH214" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI214" s="24" t="inlineStr">
@@ -65724,7 +65955,8 @@
       <c r="CO214" s="24" t="n"/>
       <c r="CP214" s="24" t="n"/>
       <c r="CQ214" s="24" t="n"/>
-      <c r="CR214" s="24" t="inlineStr">
+      <c r="CR214" s="24" t="n"/>
+      <c r="CS214" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -65733,12 +65965,12 @@
     <row r="215" ht="36" customHeight="1">
       <c r="A215" s="24" t="inlineStr">
         <is>
-          <t>9d72b13af2b44f3c</t>
+          <t>7076bff2302649bd</t>
         </is>
       </c>
       <c r="B215" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C215" s="24" t="inlineStr">
@@ -65785,25 +66017,25 @@
         </is>
       </c>
       <c r="L215" s="26" t="n">
-        <v>-120</v>
+        <v>-104</v>
       </c>
       <c r="M215" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.961538</v>
       </c>
       <c r="N215" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.509804</v>
       </c>
       <c r="O215" s="28" t="n">
-        <v>0.687662</v>
+        <v>0.6912700000000001</v>
       </c>
       <c r="P215" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q215" s="28" t="n">
-        <v>0.142207</v>
+        <v>0.181466</v>
       </c>
       <c r="R215" s="26" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="S215" s="29" t="n">
         <v>2</v>
@@ -65829,7 +66061,7 @@
       <c r="AD215" s="24" t="n"/>
       <c r="AE215" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.49-6.29; raw selected-side p=0.7860, calibrated p=0.6877.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.49-6.29; raw selected-side p=0.7914, calibrated p=0.6913.</t>
         </is>
       </c>
       <c r="AF215" s="31" t="inlineStr">
@@ -65948,7 +66180,7 @@
       </c>
       <c r="BH215" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI215" s="24" t="inlineStr">
@@ -65960,16 +66192,16 @@
         <v>1.5</v>
       </c>
       <c r="BK215" s="26" t="n">
-        <v>-120</v>
+        <v>-104</v>
       </c>
       <c r="BL215" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.961538</v>
       </c>
       <c r="BM215" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.509804</v>
       </c>
       <c r="BN215" s="28" t="n">
-        <v>0.542289</v>
+        <v>0.507463</v>
       </c>
       <c r="BO215" s="28" t="n"/>
       <c r="BP215" s="25" t="n"/>
@@ -66000,7 +66232,8 @@
       <c r="CO215" s="24" t="n"/>
       <c r="CP215" s="24" t="n"/>
       <c r="CQ215" s="24" t="n"/>
-      <c r="CR215" s="24" t="inlineStr">
+      <c r="CR215" s="24" t="n"/>
+      <c r="CS215" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -66009,12 +66242,12 @@
     <row r="216" ht="36" customHeight="1">
       <c r="A216" s="24" t="inlineStr">
         <is>
-          <t>fca6d01866b74032</t>
+          <t>3f2c709c8b734a2c</t>
         </is>
       </c>
       <c r="B216" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C216" s="24" t="inlineStr">
@@ -66061,25 +66294,25 @@
         </is>
       </c>
       <c r="L216" s="26" t="n">
-        <v>-120</v>
+        <v>-117</v>
       </c>
       <c r="M216" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.854701</v>
       </c>
       <c r="N216" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.539171</v>
       </c>
       <c r="O216" s="28" t="n">
-        <v>0.544956</v>
+        <v>0.544905</v>
       </c>
       <c r="P216" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q216" s="28" t="n">
-        <v>-0.000499</v>
+        <v>0.005734</v>
       </c>
       <c r="R216" s="26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S216" s="29" t="n">
         <v>1</v>
@@ -66105,7 +66338,7 @@
       <c r="AD216" s="24" t="n"/>
       <c r="AE216" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.49-6.29; raw selected-side p=0.6083, calibrated p=0.5450.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.49-6.29; raw selected-side p=0.6081, calibrated p=0.5449.</t>
         </is>
       </c>
       <c r="AF216" s="31" t="inlineStr">
@@ -66224,7 +66457,7 @@
       </c>
       <c r="BH216" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI216" s="24" t="inlineStr">
@@ -66236,16 +66469,16 @@
         <v>11.5</v>
       </c>
       <c r="BK216" s="26" t="n">
-        <v>-120</v>
+        <v>-117</v>
       </c>
       <c r="BL216" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.854701</v>
       </c>
       <c r="BM216" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.539171</v>
       </c>
       <c r="BN216" s="28" t="n">
-        <v>0.542289</v>
+        <v>0.537313</v>
       </c>
       <c r="BO216" s="28" t="n"/>
       <c r="BP216" s="25" t="n"/>
@@ -66276,21 +66509,22 @@
       <c r="CO216" s="24" t="n"/>
       <c r="CP216" s="24" t="n"/>
       <c r="CQ216" s="24" t="n"/>
-      <c r="CR216" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR216" s="24" t="n"/>
+      <c r="CS216" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="217" ht="36" customHeight="1">
       <c r="A217" s="24" t="inlineStr">
         <is>
-          <t>375805bbaab94810</t>
+          <t>bff984f3f67c40ee</t>
         </is>
       </c>
       <c r="B217" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C217" s="24" t="inlineStr">
@@ -66346,13 +66580,13 @@
         <v>0.640288</v>
       </c>
       <c r="O217" s="28" t="n">
-        <v>0.5404330000000001</v>
+        <v>0.543418</v>
       </c>
       <c r="P217" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q217" s="28" t="n">
-        <v>-0.099855</v>
+        <v>-0.09687</v>
       </c>
       <c r="R217" s="26" t="n">
         <v>0</v>
@@ -66381,7 +66615,7 @@
       <c r="AD217" s="24" t="n"/>
       <c r="AE217" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.09-5.16; raw selected-side p=0.5615, calibrated p=0.5404.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.09-5.16; raw selected-side p=0.5661, calibrated p=0.5434.</t>
         </is>
       </c>
       <c r="AF217" s="31" t="inlineStr">
@@ -66500,7 +66734,7 @@
       </c>
       <c r="BH217" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI217" s="24" t="inlineStr">
@@ -66552,7 +66786,8 @@
       <c r="CO217" s="24" t="n"/>
       <c r="CP217" s="24" t="n"/>
       <c r="CQ217" s="24" t="n"/>
-      <c r="CR217" s="24" t="inlineStr">
+      <c r="CR217" s="24" t="n"/>
+      <c r="CS217" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -66561,12 +66796,12 @@
     <row r="218" ht="36" customHeight="1">
       <c r="A218" s="24" t="inlineStr">
         <is>
-          <t>9a580d93ed664173</t>
+          <t>84ba76f89a674e31</t>
         </is>
       </c>
       <c r="B218" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C218" s="24" t="inlineStr">
@@ -66613,25 +66848,25 @@
         </is>
       </c>
       <c r="L218" s="26" t="n">
-        <v>-104</v>
+        <v>-125</v>
       </c>
       <c r="M218" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.8</v>
       </c>
       <c r="N218" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.555556</v>
       </c>
       <c r="O218" s="28" t="n">
-        <v>0.520815</v>
+        <v>0.520781</v>
       </c>
       <c r="P218" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q218" s="28" t="n">
-        <v>0.011011</v>
+        <v>-0.034775</v>
       </c>
       <c r="R218" s="26" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="S218" s="29" t="n">
         <v>1</v>
@@ -66657,7 +66892,7 @@
       <c r="AD218" s="24" t="n"/>
       <c r="AE218" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.09-5.16; raw selected-side p=0.5376, calibrated p=0.5208.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.09-5.16; raw selected-side p=0.5375, calibrated p=0.5208.</t>
         </is>
       </c>
       <c r="AF218" s="31" t="inlineStr">
@@ -66776,7 +67011,7 @@
       </c>
       <c r="BH218" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI218" s="24" t="inlineStr">
@@ -66788,16 +67023,16 @@
         <v>8.5</v>
       </c>
       <c r="BK218" s="26" t="n">
-        <v>-104</v>
+        <v>-125</v>
       </c>
       <c r="BL218" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.8</v>
       </c>
       <c r="BM218" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.555556</v>
       </c>
       <c r="BN218" s="28" t="n">
-        <v>0.507463</v>
+        <v>0.552239</v>
       </c>
       <c r="BO218" s="28" t="n"/>
       <c r="BP218" s="25" t="n"/>
@@ -66828,9 +67063,10 @@
       <c r="CO218" s="24" t="n"/>
       <c r="CP218" s="24" t="n"/>
       <c r="CQ218" s="24" t="n"/>
-      <c r="CR218" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR218" s="24" t="n"/>
+      <c r="CS218" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/data/flat/mlb.xlsx
+++ b/data/flat/mlb.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -57790,12 +57790,12 @@
     <row r="186" ht="36" customHeight="1">
       <c r="A186" s="24" t="inlineStr">
         <is>
-          <t>6ff3540567964bef</t>
+          <t>5f545bf126614044</t>
         </is>
       </c>
       <c r="B186" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C186" s="24" t="inlineStr">
@@ -57840,20 +57840,20 @@
         </is>
       </c>
       <c r="L186" s="26" t="n">
-        <v>-156</v>
+        <v>-174</v>
       </c>
       <c r="M186" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.574713</v>
       </c>
       <c r="N186" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.635036</v>
       </c>
       <c r="O186" s="28" t="n">
         <v>0.543314</v>
       </c>
       <c r="P186" s="28" t="n"/>
       <c r="Q186" s="28" t="n">
-        <v>-0.06606099999999999</v>
+        <v>-0.091722</v>
       </c>
       <c r="R186" s="26" t="n">
         <v>0</v>
@@ -57882,7 +57882,7 @@
       <c r="AD186" s="24" t="n"/>
       <c r="AE186" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.6100 (aec-mlb-tor-hou-2026-08-05); model edge vs ask -0.0667.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.6350 (aec-mlb-tor-hou-2026-08-05); model edge vs ask -0.0917.</t>
         </is>
       </c>
       <c r="AF186" s="31" t="inlineStr">
@@ -58001,7 +58001,7 @@
       </c>
       <c r="BH186" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:50.122845Z</t>
+          <t>2026-08-05T13:52:24.506232Z</t>
         </is>
       </c>
       <c r="BI186" s="24" t="inlineStr">
@@ -58011,16 +58011,16 @@
       </c>
       <c r="BJ186" s="25" t="n"/>
       <c r="BK186" s="26" t="n">
-        <v>-156</v>
+        <v>-174</v>
       </c>
       <c r="BL186" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.574713</v>
       </c>
       <c r="BM186" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.635036</v>
       </c>
       <c r="BN186" s="28" t="n">
-        <v>0.606965</v>
+        <v>0.631841</v>
       </c>
       <c r="BO186" s="28" t="n"/>
       <c r="BP186" s="25" t="n"/>
@@ -58093,12 +58093,12 @@
     <row r="187" ht="36" customHeight="1">
       <c r="A187" s="24" t="inlineStr">
         <is>
-          <t>7bfbbb9e10304374</t>
+          <t>2533a73a6e144c45</t>
         </is>
       </c>
       <c r="B187" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C187" s="24" t="inlineStr">
@@ -58152,11 +58152,11 @@
         <v>0.534884</v>
       </c>
       <c r="O187" s="28" t="n">
-        <v>0.522292</v>
+        <v>0.522352</v>
       </c>
       <c r="P187" s="28" t="n"/>
       <c r="Q187" s="28" t="n">
-        <v>-0.012592</v>
+        <v>-0.012532</v>
       </c>
       <c r="R187" s="26" t="n">
         <v>15</v>
@@ -58185,7 +58185,7 @@
       <c r="AD187" s="24" t="n"/>
       <c r="AE187" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5350 (aec-mlb-lad-chc-2026-08-05); model edge vs ask -0.0127.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5350 (aec-mlb-lad-chc-2026-08-05); model edge vs ask -0.0126.</t>
         </is>
       </c>
       <c r="AF187" s="31" t="inlineStr">
@@ -58289,7 +58289,7 @@
       </c>
       <c r="BE187" s="24" t="inlineStr">
         <is>
-          <t>cd121ba990e73d6d</t>
+          <t>7d69706ac5e95086</t>
         </is>
       </c>
       <c r="BF187" s="24" t="inlineStr">
@@ -58304,7 +58304,7 @@
       </c>
       <c r="BH187" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:50.628303Z</t>
+          <t>2026-08-05T13:52:24.994220Z</t>
         </is>
       </c>
       <c r="BI187" s="24" t="inlineStr">
@@ -58356,7 +58356,7 @@
       </c>
       <c r="CF187" s="24" t="inlineStr">
         <is>
-          <t>1.0097</t>
+          <t>1.0089</t>
         </is>
       </c>
       <c r="CG187" s="24" t="n"/>
@@ -58384,7 +58384,7 @@
       <c r="CQ187" s="24" t="n"/>
       <c r="CR187" s="24" t="inlineStr">
         <is>
-          <t>0.522292</t>
+          <t>0.522352</t>
         </is>
       </c>
       <c r="CS187" s="24" t="inlineStr">
@@ -58396,12 +58396,12 @@
     <row r="188" ht="36" customHeight="1">
       <c r="A188" s="24" t="inlineStr">
         <is>
-          <t>213b1d6df73b46a3</t>
+          <t>ae2fc2d9c7c44ae0</t>
         </is>
       </c>
       <c r="B188" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C188" s="24" t="inlineStr">
@@ -58446,23 +58446,23 @@
         </is>
       </c>
       <c r="L188" s="26" t="n">
-        <v>-167</v>
+        <v>-163</v>
       </c>
       <c r="M188" s="27" t="n">
-        <v>1.598802</v>
+        <v>1.613497</v>
       </c>
       <c r="N188" s="28" t="n">
-        <v>0.625468</v>
+        <v>0.619772</v>
       </c>
       <c r="O188" s="28" t="n">
         <v>0.585182</v>
       </c>
       <c r="P188" s="28" t="n"/>
       <c r="Q188" s="28" t="n">
-        <v>-0.040286</v>
+        <v>-0.03459</v>
       </c>
       <c r="R188" s="26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S188" s="29" t="n">
         <v>0</v>
@@ -58488,7 +58488,7 @@
       <c r="AD188" s="24" t="n"/>
       <c r="AE188" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.6250 (aec-mlb-sf-tex-2026-08-05); model edge vs ask -0.0398.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.6200 (aec-mlb-sf-tex-2026-08-05); model edge vs ask -0.0348.</t>
         </is>
       </c>
       <c r="AF188" s="31" t="inlineStr">
@@ -58607,7 +58607,7 @@
       </c>
       <c r="BH188" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:51.533440Z</t>
+          <t>2026-08-05T13:52:25.614756Z</t>
         </is>
       </c>
       <c r="BI188" s="24" t="inlineStr">
@@ -58617,16 +58617,16 @@
       </c>
       <c r="BJ188" s="25" t="n"/>
       <c r="BK188" s="26" t="n">
-        <v>-167</v>
+        <v>-163</v>
       </c>
       <c r="BL188" s="27" t="n">
-        <v>1.598802</v>
+        <v>1.613497</v>
       </c>
       <c r="BM188" s="28" t="n">
-        <v>0.625468</v>
+        <v>0.619772</v>
       </c>
       <c r="BN188" s="28" t="n">
-        <v>0.621891</v>
+        <v>0.616915</v>
       </c>
       <c r="BO188" s="28" t="n"/>
       <c r="BP188" s="25" t="n"/>
@@ -58699,12 +58699,12 @@
     <row r="189" ht="36" customHeight="1">
       <c r="A189" s="24" t="inlineStr">
         <is>
-          <t>1ecfa20ee3cd46f5</t>
+          <t>51149c5ad9e34fb7</t>
         </is>
       </c>
       <c r="B189" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C189" s="24" t="inlineStr">
@@ -58749,23 +58749,23 @@
         </is>
       </c>
       <c r="L189" s="26" t="n">
-        <v>-147</v>
+        <v>-153</v>
       </c>
       <c r="M189" s="27" t="n">
-        <v>1.680272</v>
+        <v>1.653595</v>
       </c>
       <c r="N189" s="28" t="n">
-        <v>0.5951419999999999</v>
+        <v>0.604743</v>
       </c>
       <c r="O189" s="28" t="n">
-        <v>0.651419</v>
+        <v>0.651358</v>
       </c>
       <c r="P189" s="28" t="n"/>
       <c r="Q189" s="28" t="n">
-        <v>0.056277</v>
+        <v>0.046615</v>
       </c>
       <c r="R189" s="26" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="S189" s="29" t="n">
         <v>1.75</v>
@@ -58791,7 +58791,7 @@
       <c r="AD189" s="24" t="n"/>
       <c r="AE189" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5950 (aec-mlb-tb-col-2026-08-05); model edge vs ask +0.0564.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.6050 (aec-mlb-tb-col-2026-08-05); model edge vs ask +0.0464.</t>
         </is>
       </c>
       <c r="AF189" s="31" t="inlineStr">
@@ -58895,7 +58895,7 @@
       </c>
       <c r="BE189" s="24" t="inlineStr">
         <is>
-          <t>afbdfea2d660f7f9</t>
+          <t>133a0f8d2d67fce5</t>
         </is>
       </c>
       <c r="BF189" s="24" t="inlineStr">
@@ -58910,7 +58910,7 @@
       </c>
       <c r="BH189" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:52.558033Z</t>
+          <t>2026-08-05T13:52:26.086277Z</t>
         </is>
       </c>
       <c r="BI189" s="24" t="inlineStr">
@@ -58920,16 +58920,16 @@
       </c>
       <c r="BJ189" s="25" t="n"/>
       <c r="BK189" s="26" t="n">
-        <v>-147</v>
+        <v>-153</v>
       </c>
       <c r="BL189" s="27" t="n">
-        <v>1.680272</v>
+        <v>1.653595</v>
       </c>
       <c r="BM189" s="28" t="n">
-        <v>0.5951419999999999</v>
+        <v>0.604743</v>
       </c>
       <c r="BN189" s="28" t="n">
-        <v>0.59204</v>
+        <v>0.60199</v>
       </c>
       <c r="BO189" s="28" t="n"/>
       <c r="BP189" s="25" t="n"/>
@@ -58962,7 +58962,7 @@
       </c>
       <c r="CF189" s="24" t="inlineStr">
         <is>
-          <t>1.0105</t>
+          <t>1.0096</t>
         </is>
       </c>
       <c r="CG189" s="24" t="n"/>
@@ -58990,7 +58990,7 @@
       <c r="CQ189" s="24" t="n"/>
       <c r="CR189" s="24" t="inlineStr">
         <is>
-          <t>0.651419</t>
+          <t>0.651358</t>
         </is>
       </c>
       <c r="CS189" s="24" t="inlineStr">
@@ -59002,12 +59002,12 @@
     <row r="190" ht="36" customHeight="1">
       <c r="A190" s="24" t="inlineStr">
         <is>
-          <t>834fa6cfaa72498f</t>
+          <t>dc6ca6079a734a5f</t>
         </is>
       </c>
       <c r="B190" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C190" s="24" t="inlineStr">
@@ -59052,23 +59052,23 @@
         </is>
       </c>
       <c r="L190" s="26" t="n">
-        <v>-130</v>
+        <v>-117</v>
       </c>
       <c r="M190" s="27" t="n">
-        <v>1.769231</v>
+        <v>1.854701</v>
       </c>
       <c r="N190" s="28" t="n">
-        <v>0.565217</v>
+        <v>0.539171</v>
       </c>
       <c r="O190" s="28" t="n">
-        <v>0.620283</v>
+        <v>0.620156</v>
       </c>
       <c r="P190" s="28" t="n"/>
       <c r="Q190" s="28" t="n">
-        <v>0.055066</v>
+        <v>0.080985</v>
       </c>
       <c r="R190" s="26" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="S190" s="29" t="n">
         <v>1.5</v>
@@ -59094,7 +59094,7 @@
       <c r="AD190" s="24" t="n"/>
       <c r="AE190" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5650 (aec-mlb-laa-bal-2026-08-05); model edge vs ask +0.0553.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5400 (aec-mlb-laa-bal-2026-08-05); model edge vs ask +0.0802.</t>
         </is>
       </c>
       <c r="AF190" s="31" t="inlineStr">
@@ -59198,7 +59198,7 @@
       </c>
       <c r="BE190" s="24" t="inlineStr">
         <is>
-          <t>0c5ef877e6b12160</t>
+          <t>90250452b4135146</t>
         </is>
       </c>
       <c r="BF190" s="24" t="inlineStr">
@@ -59213,7 +59213,7 @@
       </c>
       <c r="BH190" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:53.451157Z</t>
+          <t>2026-08-05T13:52:26.546603Z</t>
         </is>
       </c>
       <c r="BI190" s="24" t="inlineStr">
@@ -59223,16 +59223,16 @@
       </c>
       <c r="BJ190" s="25" t="n"/>
       <c r="BK190" s="26" t="n">
-        <v>-130</v>
+        <v>-117</v>
       </c>
       <c r="BL190" s="27" t="n">
-        <v>1.769231</v>
+        <v>1.854701</v>
       </c>
       <c r="BM190" s="28" t="n">
-        <v>0.565217</v>
+        <v>0.539171</v>
       </c>
       <c r="BN190" s="28" t="n">
-        <v>0.562189</v>
+        <v>0.537313</v>
       </c>
       <c r="BO190" s="28" t="n"/>
       <c r="BP190" s="25" t="n"/>
@@ -59265,7 +59265,7 @@
       </c>
       <c r="CF190" s="24" t="inlineStr">
         <is>
-          <t>1.0102</t>
+          <t>1.012</t>
         </is>
       </c>
       <c r="CG190" s="24" t="n"/>
@@ -59293,7 +59293,7 @@
       <c r="CQ190" s="24" t="n"/>
       <c r="CR190" s="24" t="inlineStr">
         <is>
-          <t>0.620283</t>
+          <t>0.620156</t>
         </is>
       </c>
       <c r="CS190" s="24" t="inlineStr">
@@ -59305,12 +59305,12 @@
     <row r="191" ht="36" customHeight="1">
       <c r="A191" s="24" t="inlineStr">
         <is>
-          <t>b3c6b3cca4c3426f</t>
+          <t>e3a6b3fee6d14874</t>
         </is>
       </c>
       <c r="B191" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C191" s="24" t="inlineStr">
@@ -59355,23 +59355,23 @@
         </is>
       </c>
       <c r="L191" s="26" t="n">
-        <v>-127</v>
+        <v>-135</v>
       </c>
       <c r="M191" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.740741</v>
       </c>
       <c r="N191" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.574468</v>
       </c>
       <c r="O191" s="28" t="n">
-        <v>0.531988</v>
+        <v>0.531981</v>
       </c>
       <c r="P191" s="28" t="n"/>
       <c r="Q191" s="28" t="n">
-        <v>-0.027483</v>
+        <v>-0.042487</v>
       </c>
       <c r="R191" s="26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S191" s="29" t="n">
         <v>0</v>
@@ -59397,7 +59397,7 @@
       <c r="AD191" s="24" t="n"/>
       <c r="AE191" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5600 (aec-mlb-ath-cin-2026-08-05); model edge vs ask -0.0280.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5750 (aec-mlb-ath-cin-2026-08-05); model edge vs ask -0.0430.</t>
         </is>
       </c>
       <c r="AF191" s="31" t="inlineStr">
@@ -59501,7 +59501,7 @@
       </c>
       <c r="BE191" s="24" t="inlineStr">
         <is>
-          <t>117cc3945a0a3429</t>
+          <t>b37c86ce3baa60b2</t>
         </is>
       </c>
       <c r="BF191" s="24" t="inlineStr">
@@ -59516,7 +59516,7 @@
       </c>
       <c r="BH191" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:56.201811Z</t>
+          <t>2026-08-05T13:52:28.221956Z</t>
         </is>
       </c>
       <c r="BI191" s="24" t="inlineStr">
@@ -59526,16 +59526,16 @@
       </c>
       <c r="BJ191" s="25" t="n"/>
       <c r="BK191" s="26" t="n">
-        <v>-127</v>
+        <v>-135</v>
       </c>
       <c r="BL191" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.740741</v>
       </c>
       <c r="BM191" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.574468</v>
       </c>
       <c r="BN191" s="28" t="n">
-        <v>0.557214</v>
+        <v>0.572139</v>
       </c>
       <c r="BO191" s="28" t="n"/>
       <c r="BP191" s="25" t="n"/>
@@ -59568,7 +59568,7 @@
       </c>
       <c r="CF191" s="24" t="inlineStr">
         <is>
-          <t>1.0202</t>
+          <t>1.0203</t>
         </is>
       </c>
       <c r="CG191" s="24" t="n"/>
@@ -59596,7 +59596,7 @@
       <c r="CQ191" s="24" t="n"/>
       <c r="CR191" s="24" t="inlineStr">
         <is>
-          <t>0.531988</t>
+          <t>0.531981</t>
         </is>
       </c>
       <c r="CS191" s="24" t="inlineStr">
@@ -59608,12 +59608,12 @@
     <row r="192" ht="36" customHeight="1">
       <c r="A192" s="24" t="inlineStr">
         <is>
-          <t>ea183039e65241a5</t>
+          <t>2b50414866bd4838</t>
         </is>
       </c>
       <c r="B192" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C192" s="24" t="inlineStr">
@@ -59658,23 +59658,23 @@
         </is>
       </c>
       <c r="L192" s="26" t="n">
-        <v>106</v>
+        <v>-104</v>
       </c>
       <c r="M192" s="27" t="n">
-        <v>2.06</v>
+        <v>1.961538</v>
       </c>
       <c r="N192" s="28" t="n">
-        <v>0.485437</v>
+        <v>0.509804</v>
       </c>
       <c r="O192" s="28" t="n">
-        <v>0.570001</v>
+        <v>0.570059</v>
       </c>
       <c r="P192" s="28" t="n"/>
       <c r="Q192" s="28" t="n">
-        <v>0.084564</v>
+        <v>0.060255</v>
       </c>
       <c r="R192" s="26" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="S192" s="29" t="n">
         <v>0</v>
@@ -59700,7 +59700,7 @@
       <c r="AD192" s="24" t="n"/>
       <c r="AE192" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.4850 (aec-mlb-nym-cle-2026-08-05); model edge vs ask +0.0850.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5100 (aec-mlb-nym-cle-2026-08-05); model edge vs ask +0.0601.</t>
         </is>
       </c>
       <c r="AF192" s="31" t="inlineStr">
@@ -59804,7 +59804,7 @@
       </c>
       <c r="BE192" s="24" t="inlineStr">
         <is>
-          <t>e56570441b5f5cf2</t>
+          <t>a8496f0544fb49ff</t>
         </is>
       </c>
       <c r="BF192" s="24" t="inlineStr">
@@ -59819,7 +59819,7 @@
       </c>
       <c r="BH192" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:55.141566Z</t>
+          <t>2026-08-05T13:52:27.503942Z</t>
         </is>
       </c>
       <c r="BI192" s="24" t="inlineStr">
@@ -59829,16 +59829,16 @@
       </c>
       <c r="BJ192" s="25" t="n"/>
       <c r="BK192" s="26" t="n">
-        <v>106</v>
+        <v>-104</v>
       </c>
       <c r="BL192" s="27" t="n">
-        <v>2.06</v>
+        <v>1.961538</v>
       </c>
       <c r="BM192" s="28" t="n">
-        <v>0.485437</v>
+        <v>0.509804</v>
       </c>
       <c r="BN192" s="28" t="n">
-        <v>0.482587</v>
+        <v>0.507463</v>
       </c>
       <c r="BO192" s="28" t="n"/>
       <c r="BP192" s="25" t="n"/>
@@ -59871,7 +59871,7 @@
       </c>
       <c r="CF192" s="24" t="inlineStr">
         <is>
-          <t>1.0127</t>
+          <t>1.0119</t>
         </is>
       </c>
       <c r="CG192" s="24" t="n"/>
@@ -59899,7 +59899,7 @@
       <c r="CQ192" s="24" t="n"/>
       <c r="CR192" s="24" t="inlineStr">
         <is>
-          <t>0.570001</t>
+          <t>0.570059</t>
         </is>
       </c>
       <c r="CS192" s="24" t="inlineStr">
@@ -59911,12 +59911,12 @@
     <row r="193" ht="36" customHeight="1">
       <c r="A193" s="24" t="inlineStr">
         <is>
-          <t>554772c4dc254e8d</t>
+          <t>0707206819d14a7d</t>
         </is>
       </c>
       <c r="B193" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C193" s="24" t="inlineStr">
@@ -59961,20 +59961,20 @@
         </is>
       </c>
       <c r="L193" s="26" t="n">
-        <v>-160</v>
+        <v>-174</v>
       </c>
       <c r="M193" s="27" t="n">
-        <v>1.625</v>
+        <v>1.574713</v>
       </c>
       <c r="N193" s="28" t="n">
-        <v>0.615385</v>
+        <v>0.635036</v>
       </c>
       <c r="O193" s="28" t="n">
-        <v>0.568075</v>
+        <v>0.568112</v>
       </c>
       <c r="P193" s="28" t="n"/>
       <c r="Q193" s="28" t="n">
-        <v>-0.04731</v>
+        <v>-0.066924</v>
       </c>
       <c r="R193" s="26" t="n">
         <v>0</v>
@@ -60003,7 +60003,7 @@
       <c r="AD193" s="24" t="n"/>
       <c r="AE193" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.6150 (aec-mlb-wsh-phi-2026-08-05); model edge vs ask -0.0469.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.6350 (aec-mlb-wsh-phi-2026-08-05); model edge vs ask -0.0669.</t>
         </is>
       </c>
       <c r="AF193" s="31" t="inlineStr">
@@ -60107,7 +60107,7 @@
       </c>
       <c r="BE193" s="24" t="inlineStr">
         <is>
-          <t>cc0cc1936c4cd2d0</t>
+          <t>28c4190bf888aff9</t>
         </is>
       </c>
       <c r="BF193" s="24" t="inlineStr">
@@ -60122,7 +60122,7 @@
       </c>
       <c r="BH193" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:54.460834Z</t>
+          <t>2026-08-05T13:52:27.109583Z</t>
         </is>
       </c>
       <c r="BI193" s="24" t="inlineStr">
@@ -60132,16 +60132,16 @@
       </c>
       <c r="BJ193" s="25" t="n"/>
       <c r="BK193" s="26" t="n">
-        <v>-160</v>
+        <v>-174</v>
       </c>
       <c r="BL193" s="27" t="n">
-        <v>1.625</v>
+        <v>1.574713</v>
       </c>
       <c r="BM193" s="28" t="n">
-        <v>0.615385</v>
+        <v>0.635036</v>
       </c>
       <c r="BN193" s="28" t="n">
-        <v>0.61194</v>
+        <v>0.631841</v>
       </c>
       <c r="BO193" s="28" t="n"/>
       <c r="BP193" s="25" t="n"/>
@@ -60174,7 +60174,7 @@
       </c>
       <c r="CF193" s="24" t="inlineStr">
         <is>
-          <t>1.0112</t>
+          <t>1.0107</t>
         </is>
       </c>
       <c r="CG193" s="24" t="n"/>
@@ -60202,7 +60202,7 @@
       <c r="CQ193" s="24" t="n"/>
       <c r="CR193" s="24" t="inlineStr">
         <is>
-          <t>0.568075</t>
+          <t>0.568112</t>
         </is>
       </c>
       <c r="CS193" s="24" t="inlineStr">
@@ -60214,12 +60214,12 @@
     <row r="194" ht="36" customHeight="1">
       <c r="A194" s="24" t="inlineStr">
         <is>
-          <t>6173832403c34386</t>
+          <t>0e57b7e2b084476b</t>
         </is>
       </c>
       <c r="B194" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C194" s="24" t="inlineStr">
@@ -60273,11 +60273,11 @@
         <v>0.590164</v>
       </c>
       <c r="O194" s="28" t="n">
-        <v>0.585723</v>
+        <v>0.5858100000000001</v>
       </c>
       <c r="P194" s="28" t="n"/>
       <c r="Q194" s="28" t="n">
-        <v>-0.004441</v>
+        <v>-0.004354</v>
       </c>
       <c r="R194" s="26" t="n">
         <v>19</v>
@@ -60306,7 +60306,7 @@
       <c r="AD194" s="24" t="n"/>
       <c r="AE194" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5900 (aec-mlb-stl-nyy-2026-08-05); model edge vs ask -0.0043.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5900 (aec-mlb-stl-nyy-2026-08-05); model edge vs ask -0.0042.</t>
         </is>
       </c>
       <c r="AF194" s="31" t="inlineStr">
@@ -60410,7 +60410,7 @@
       </c>
       <c r="BE194" s="24" t="inlineStr">
         <is>
-          <t>5e4023ab8bd19cc5</t>
+          <t>f16100c8dde61330</t>
         </is>
       </c>
       <c r="BF194" s="24" t="inlineStr">
@@ -60425,7 +60425,7 @@
       </c>
       <c r="BH194" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:57.037353Z</t>
+          <t>2026-08-05T13:52:28.745980Z</t>
         </is>
       </c>
       <c r="BI194" s="24" t="inlineStr">
@@ -60477,7 +60477,7 @@
       </c>
       <c r="CF194" s="24" t="inlineStr">
         <is>
-          <t>1.0089</t>
+          <t>1.0077</t>
         </is>
       </c>
       <c r="CG194" s="24" t="n"/>
@@ -60505,7 +60505,7 @@
       <c r="CQ194" s="24" t="n"/>
       <c r="CR194" s="24" t="inlineStr">
         <is>
-          <t>0.585723</t>
+          <t>0.58581</t>
         </is>
       </c>
       <c r="CS194" s="24" t="inlineStr">
@@ -60517,12 +60517,12 @@
     <row r="195" ht="36" customHeight="1">
       <c r="A195" s="24" t="inlineStr">
         <is>
-          <t>74cff5906ad44224</t>
+          <t>5e79dc4004814e2f</t>
         </is>
       </c>
       <c r="B195" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C195" s="24" t="inlineStr">
@@ -60567,23 +60567,23 @@
         </is>
       </c>
       <c r="L195" s="26" t="n">
-        <v>-115</v>
+        <v>-125</v>
       </c>
       <c r="M195" s="27" t="n">
-        <v>1.869565</v>
+        <v>1.8</v>
       </c>
       <c r="N195" s="28" t="n">
-        <v>0.534884</v>
+        <v>0.555556</v>
       </c>
       <c r="O195" s="28" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.576188</v>
       </c>
       <c r="P195" s="28" t="n"/>
       <c r="Q195" s="28" t="n">
-        <v>0.041216</v>
+        <v>0.020632</v>
       </c>
       <c r="R195" s="26" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="S195" s="29" t="n">
         <v>0</v>
@@ -60609,7 +60609,7 @@
       <c r="AD195" s="24" t="n"/>
       <c r="AE195" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5350 (aec-mlb-cws-bos-2026-08-05); model edge vs ask +0.0411.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5550 (aec-mlb-cws-bos-2026-08-05); model edge vs ask +0.0212.</t>
         </is>
       </c>
       <c r="AF195" s="31" t="inlineStr">
@@ -60713,7 +60713,7 @@
       </c>
       <c r="BE195" s="24" t="inlineStr">
         <is>
-          <t>b747944f91650fd4</t>
+          <t>10f5b05f22dccd69</t>
         </is>
       </c>
       <c r="BF195" s="24" t="inlineStr">
@@ -60728,7 +60728,7 @@
       </c>
       <c r="BH195" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:57.825385Z</t>
+          <t>2026-08-05T13:52:29.150568Z</t>
         </is>
       </c>
       <c r="BI195" s="24" t="inlineStr">
@@ -60738,16 +60738,16 @@
       </c>
       <c r="BJ195" s="25" t="n"/>
       <c r="BK195" s="26" t="n">
-        <v>-115</v>
+        <v>-125</v>
       </c>
       <c r="BL195" s="27" t="n">
-        <v>1.869565</v>
+        <v>1.8</v>
       </c>
       <c r="BM195" s="28" t="n">
-        <v>0.534884</v>
+        <v>0.555556</v>
       </c>
       <c r="BN195" s="28" t="n">
-        <v>0.532338</v>
+        <v>0.552239</v>
       </c>
       <c r="BO195" s="28" t="n"/>
       <c r="BP195" s="25" t="n"/>
@@ -60780,7 +60780,7 @@
       </c>
       <c r="CF195" s="24" t="inlineStr">
         <is>
-          <t>1.0141</t>
+          <t>1.0129</t>
         </is>
       </c>
       <c r="CG195" s="24" t="n"/>
@@ -60808,7 +60808,7 @@
       <c r="CQ195" s="24" t="n"/>
       <c r="CR195" s="24" t="inlineStr">
         <is>
-          <t>0.5761</t>
+          <t>0.576188</t>
         </is>
       </c>
       <c r="CS195" s="24" t="inlineStr">
@@ -60820,12 +60820,12 @@
     <row r="196" ht="36" customHeight="1">
       <c r="A196" s="24" t="inlineStr">
         <is>
-          <t>e54060cb42344aa5</t>
+          <t>d1e30ef4ff0b4aa1</t>
         </is>
       </c>
       <c r="B196" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C196" s="24" t="inlineStr">
@@ -60879,11 +60879,11 @@
         <v>0.545455</v>
       </c>
       <c r="O196" s="28" t="n">
-        <v>0.59089</v>
+        <v>0.590933</v>
       </c>
       <c r="P196" s="28" t="n"/>
       <c r="Q196" s="28" t="n">
-        <v>0.045435</v>
+        <v>0.045478</v>
       </c>
       <c r="R196" s="26" t="n">
         <v>44</v>
@@ -61016,7 +61016,7 @@
       </c>
       <c r="BE196" s="24" t="inlineStr">
         <is>
-          <t>bb6f41cb5975b5bb</t>
+          <t>06a32b1aa50e018d</t>
         </is>
       </c>
       <c r="BF196" s="24" t="inlineStr">
@@ -61031,7 +61031,7 @@
       </c>
       <c r="BH196" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:58.789026Z</t>
+          <t>2026-08-05T13:52:29.624655Z</t>
         </is>
       </c>
       <c r="BI196" s="24" t="inlineStr">
@@ -61083,7 +61083,7 @@
       </c>
       <c r="CF196" s="24" t="inlineStr">
         <is>
-          <t>1.0072</t>
+          <t>1.0066</t>
         </is>
       </c>
       <c r="CG196" s="24" t="n"/>
@@ -61115,7 +61115,7 @@
       <c r="CQ196" s="24" t="n"/>
       <c r="CR196" s="24" t="inlineStr">
         <is>
-          <t>0.59089</t>
+          <t>0.590933</t>
         </is>
       </c>
       <c r="CS196" s="24" t="inlineStr">
@@ -61127,12 +61127,12 @@
     <row r="197" ht="36" customHeight="1">
       <c r="A197" s="24" t="inlineStr">
         <is>
-          <t>1f14ba2d3f6a4999</t>
+          <t>33f2e3a8a1e74278</t>
         </is>
       </c>
       <c r="B197" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C197" s="24" t="inlineStr">
@@ -61177,23 +61177,23 @@
         </is>
       </c>
       <c r="L197" s="26" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="M197" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.8</v>
       </c>
       <c r="N197" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.555556</v>
       </c>
       <c r="O197" s="28" t="n">
         <v>0.6155080000000001</v>
       </c>
       <c r="P197" s="28" t="n"/>
       <c r="Q197" s="28" t="n">
-        <v>0.065958</v>
+        <v>0.059952</v>
       </c>
       <c r="R197" s="26" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S197" s="29" t="n">
         <v>1.5</v>
@@ -61219,7 +61219,7 @@
       <c r="AD197" s="24" t="n"/>
       <c r="AE197" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5500 (aec-mlb-pit-mil-2026-08-05); model edge vs ask +0.0655.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5550 (aec-mlb-pit-mil-2026-08-05); model edge vs ask +0.0605.</t>
         </is>
       </c>
       <c r="AF197" s="31" t="inlineStr">
@@ -61338,7 +61338,7 @@
       </c>
       <c r="BH197" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:59.358107Z</t>
+          <t>2026-08-05T13:52:30.079092Z</t>
         </is>
       </c>
       <c r="BI197" s="24" t="inlineStr">
@@ -61348,16 +61348,16 @@
       </c>
       <c r="BJ197" s="25" t="n"/>
       <c r="BK197" s="26" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="BL197" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.8</v>
       </c>
       <c r="BM197" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.555556</v>
       </c>
       <c r="BN197" s="28" t="n">
-        <v>0.547264</v>
+        <v>0.552239</v>
       </c>
       <c r="BO197" s="28" t="n"/>
       <c r="BP197" s="25" t="n"/>
@@ -61430,12 +61430,12 @@
     <row r="198" ht="36" customHeight="1">
       <c r="A198" s="24" t="inlineStr">
         <is>
-          <t>ac481a548c2d4c55</t>
+          <t>d43a3520d7d3492b</t>
         </is>
       </c>
       <c r="B198" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C198" s="24" t="inlineStr">
@@ -61480,23 +61480,23 @@
         </is>
       </c>
       <c r="L198" s="26" t="n">
-        <v>-108</v>
+        <v>-113</v>
       </c>
       <c r="M198" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.884956</v>
       </c>
       <c r="N198" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.530516</v>
       </c>
       <c r="O198" s="28" t="n">
-        <v>0.5251209999999999</v>
+        <v>0.524802</v>
       </c>
       <c r="P198" s="28" t="n"/>
       <c r="Q198" s="28" t="n">
-        <v>0.00589</v>
+        <v>-0.005714</v>
       </c>
       <c r="R198" s="26" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="S198" s="29" t="n">
         <v>0</v>
@@ -61522,7 +61522,7 @@
       <c r="AD198" s="24" t="n"/>
       <c r="AE198" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5200 (aec-mlb-min-kc-2026-08-05); model edge vs ask +0.0051.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5300 (aec-mlb-min-kc-2026-08-05); model edge vs ask -0.0052.</t>
         </is>
       </c>
       <c r="AF198" s="31" t="inlineStr">
@@ -61626,7 +61626,7 @@
       </c>
       <c r="BE198" s="24" t="inlineStr">
         <is>
-          <t>f8ae77f69b137e22</t>
+          <t>420793a043fef772</t>
         </is>
       </c>
       <c r="BF198" s="24" t="inlineStr">
@@ -61641,7 +61641,7 @@
       </c>
       <c r="BH198" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:00.271972Z</t>
+          <t>2026-08-05T13:52:30.727273Z</t>
         </is>
       </c>
       <c r="BI198" s="24" t="inlineStr">
@@ -61651,16 +61651,16 @@
       </c>
       <c r="BJ198" s="25" t="n"/>
       <c r="BK198" s="26" t="n">
-        <v>-108</v>
+        <v>-113</v>
       </c>
       <c r="BL198" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.884956</v>
       </c>
       <c r="BM198" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.530516</v>
       </c>
       <c r="BN198" s="28" t="n">
-        <v>0.5148509999999999</v>
+        <v>0.527363</v>
       </c>
       <c r="BO198" s="28" t="n"/>
       <c r="BP198" s="25" t="n"/>
@@ -61693,7 +61693,7 @@
       </c>
       <c r="CF198" s="24" t="inlineStr">
         <is>
-          <t>1.0128</t>
+          <t>1.0171</t>
         </is>
       </c>
       <c r="CG198" s="24" t="n"/>
@@ -61721,24 +61721,24 @@
       <c r="CQ198" s="24" t="n"/>
       <c r="CR198" s="24" t="inlineStr">
         <is>
-          <t>0.525121</t>
+          <t>0.524802</t>
         </is>
       </c>
       <c r="CS198" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="199" ht="36" customHeight="1">
       <c r="A199" s="24" t="inlineStr">
         <is>
-          <t>360f9b23ece34b85</t>
+          <t>50fddafac55b4f3c</t>
         </is>
       </c>
       <c r="B199" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C199" s="24" t="inlineStr">
@@ -61783,23 +61783,23 @@
         </is>
       </c>
       <c r="L199" s="26" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="M199" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.694444</v>
       </c>
       <c r="N199" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.590164</v>
       </c>
       <c r="O199" s="28" t="n">
         <v>0.550053</v>
       </c>
       <c r="P199" s="28" t="n"/>
       <c r="Q199" s="28" t="n">
-        <v>-0.029779</v>
+        <v>-0.040111</v>
       </c>
       <c r="R199" s="26" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S199" s="29" t="n">
         <v>0</v>
@@ -61825,7 +61825,7 @@
       <c r="AD199" s="24" t="n"/>
       <c r="AE199" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5800 (aec-mlb-det-sea-2026-08-05); model edge vs ask -0.0299.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5900 (aec-mlb-det-sea-2026-08-05); model edge vs ask -0.0399.</t>
         </is>
       </c>
       <c r="AF199" s="31" t="inlineStr">
@@ -61944,7 +61944,7 @@
       </c>
       <c r="BH199" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:01.074140Z</t>
+          <t>2026-08-05T13:52:31.897237Z</t>
         </is>
       </c>
       <c r="BI199" s="24" t="inlineStr">
@@ -61954,16 +61954,16 @@
       </c>
       <c r="BJ199" s="25" t="n"/>
       <c r="BK199" s="26" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="BL199" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.694444</v>
       </c>
       <c r="BM199" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.590164</v>
       </c>
       <c r="BN199" s="28" t="n">
-        <v>0.577114</v>
+        <v>0.5870649999999999</v>
       </c>
       <c r="BO199" s="28" t="n"/>
       <c r="BP199" s="25" t="n"/>
@@ -62036,12 +62036,12 @@
     <row r="200" ht="36" customHeight="1">
       <c r="A200" s="24" t="inlineStr">
         <is>
-          <t>b5bac8a287c347f5</t>
+          <t>4304c4a91d1145b1</t>
         </is>
       </c>
       <c r="B200" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C200" s="24" t="inlineStr">
@@ -62086,23 +62086,23 @@
         </is>
       </c>
       <c r="L200" s="26" t="n">
-        <v>-111</v>
+        <v>-115</v>
       </c>
       <c r="M200" s="27" t="n">
-        <v>1.900901</v>
+        <v>1.869565</v>
       </c>
       <c r="N200" s="28" t="n">
-        <v>0.526066</v>
+        <v>0.534884</v>
       </c>
       <c r="O200" s="28" t="n">
         <v>0.512293</v>
       </c>
       <c r="P200" s="28" t="n"/>
       <c r="Q200" s="28" t="n">
-        <v>-0.013773</v>
+        <v>-0.022591</v>
       </c>
       <c r="R200" s="26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="S200" s="29" t="n">
         <v>0</v>
@@ -62128,7 +62128,7 @@
       <c r="AD200" s="24" t="n"/>
       <c r="AE200" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5250 (aec-mlb-sd-az-2026-08-05); model edge vs ask -0.0127.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5350 (aec-mlb-sd-az-2026-08-05); model edge vs ask -0.0227.</t>
         </is>
       </c>
       <c r="AF200" s="31" t="inlineStr">
@@ -62247,7 +62247,7 @@
       </c>
       <c r="BH200" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:01.895512Z</t>
+          <t>2026-08-05T13:52:33.047392Z</t>
         </is>
       </c>
       <c r="BI200" s="24" t="inlineStr">
@@ -62257,16 +62257,16 @@
       </c>
       <c r="BJ200" s="25" t="n"/>
       <c r="BK200" s="26" t="n">
-        <v>-111</v>
+        <v>-115</v>
       </c>
       <c r="BL200" s="27" t="n">
-        <v>1.900901</v>
+        <v>1.869565</v>
       </c>
       <c r="BM200" s="28" t="n">
-        <v>0.526066</v>
+        <v>0.534884</v>
       </c>
       <c r="BN200" s="28" t="n">
-        <v>0.522388</v>
+        <v>0.532338</v>
       </c>
       <c r="BO200" s="28" t="n"/>
       <c r="BP200" s="25" t="n"/>
@@ -62339,12 +62339,12 @@
     <row r="201" ht="36" customHeight="1">
       <c r="A201" s="24" t="inlineStr">
         <is>
-          <t>2af2f4dcab2b4c21</t>
+          <t>b7732472266842a3</t>
         </is>
       </c>
       <c r="B201" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C201" s="24" t="inlineStr">
@@ -62391,25 +62391,25 @@
         </is>
       </c>
       <c r="L201" s="26" t="n">
-        <v>-135</v>
+        <v>-122</v>
       </c>
       <c r="M201" s="27" t="n">
-        <v>1.740741</v>
+        <v>1.819672</v>
       </c>
       <c r="N201" s="28" t="n">
-        <v>0.574468</v>
+        <v>0.54955</v>
       </c>
       <c r="O201" s="28" t="n">
-        <v>0.556045</v>
+        <v>0.554069</v>
       </c>
       <c r="P201" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q201" s="28" t="n">
-        <v>-0.018423</v>
+        <v>0.004519</v>
       </c>
       <c r="R201" s="26" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="S201" s="29" t="n">
         <v>1</v>
@@ -62435,7 +62435,7 @@
       <c r="AD201" s="24" t="n"/>
       <c r="AE201" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.45-5.29; raw selected-side p=0.5823, calibrated p=0.5560.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.45-5.29; raw selected-side p=0.5794, calibrated p=0.5541.</t>
         </is>
       </c>
       <c r="AF201" s="31" t="inlineStr">
@@ -62554,7 +62554,7 @@
       </c>
       <c r="BH201" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI201" s="24" t="inlineStr">
@@ -62566,16 +62566,16 @@
         <v>1.5</v>
       </c>
       <c r="BK201" s="26" t="n">
-        <v>-135</v>
+        <v>-122</v>
       </c>
       <c r="BL201" s="27" t="n">
-        <v>1.740741</v>
+        <v>1.819672</v>
       </c>
       <c r="BM201" s="28" t="n">
-        <v>0.574468</v>
+        <v>0.54955</v>
       </c>
       <c r="BN201" s="28" t="n">
-        <v>0.572139</v>
+        <v>0.547264</v>
       </c>
       <c r="BO201" s="28" t="n"/>
       <c r="BP201" s="25" t="n"/>
@@ -62609,19 +62609,19 @@
       <c r="CR201" s="24" t="n"/>
       <c r="CS201" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="202" ht="36" customHeight="1">
       <c r="A202" s="24" t="inlineStr">
         <is>
-          <t>2e28c6f185954677</t>
+          <t>d6db2f4b521b400d</t>
         </is>
       </c>
       <c r="B202" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C202" s="24" t="inlineStr">
@@ -62677,13 +62677,13 @@
         <v>0.473934</v>
       </c>
       <c r="O202" s="28" t="n">
-        <v>0.524815</v>
+        <v>0.525275</v>
       </c>
       <c r="P202" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q202" s="28" t="n">
-        <v>0.050881</v>
+        <v>0.051341</v>
       </c>
       <c r="R202" s="26" t="n">
         <v>51</v>
@@ -62712,7 +62712,7 @@
       <c r="AD202" s="24" t="n"/>
       <c r="AE202" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.45-5.29; raw selected-side p=0.5766, calibrated p=0.5248.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.45-5.29; raw selected-side p=0.5784, calibrated p=0.5253.</t>
         </is>
       </c>
       <c r="AF202" s="31" t="inlineStr">
@@ -62831,7 +62831,7 @@
       </c>
       <c r="BH202" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI202" s="24" t="inlineStr">
@@ -62893,12 +62893,12 @@
     <row r="203" ht="36" customHeight="1">
       <c r="A203" s="24" t="inlineStr">
         <is>
-          <t>f2a4bd8da10e45d5</t>
+          <t>433e220b206847ba</t>
         </is>
       </c>
       <c r="B203" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C203" s="24" t="inlineStr">
@@ -62933,7 +62933,7 @@
       </c>
       <c r="I203" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J203" s="25" t="n">
@@ -62954,19 +62954,19 @@
         <v>0.635036</v>
       </c>
       <c r="O203" s="28" t="n">
-        <v>0.6607420000000001</v>
+        <v>0.576862</v>
       </c>
       <c r="P203" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q203" s="28" t="n">
-        <v>0.025706</v>
+        <v>-0.058174</v>
       </c>
       <c r="R203" s="26" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="S203" s="29" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="T203" s="24" t="inlineStr">
         <is>
@@ -62989,7 +62989,7 @@
       <c r="AD203" s="24" t="n"/>
       <c r="AE203" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.96-4.59; raw selected-side p=0.7359, calibrated p=0.6607.</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.96-4.59; raw selected-side p=0.6128, calibrated p=0.5769.</t>
         </is>
       </c>
       <c r="AF203" s="31" t="inlineStr">
@@ -63108,7 +63108,7 @@
       </c>
       <c r="BH203" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI203" s="24" t="inlineStr">
@@ -63163,19 +63163,19 @@
       <c r="CR203" s="24" t="n"/>
       <c r="CS203" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="204" ht="36" customHeight="1">
       <c r="A204" s="24" t="inlineStr">
         <is>
-          <t>3bc0a1dfe50a4d9e</t>
+          <t>10263ec937d04c88</t>
         </is>
       </c>
       <c r="B204" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C204" s="24" t="inlineStr">
@@ -63222,25 +63222,25 @@
         </is>
       </c>
       <c r="L204" s="26" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="M204" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.961538</v>
       </c>
       <c r="N204" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.509804</v>
       </c>
       <c r="O204" s="28" t="n">
-        <v>0.539558</v>
+        <v>0.540166</v>
       </c>
       <c r="P204" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q204" s="28" t="n">
-        <v>0.020327</v>
+        <v>0.030362</v>
       </c>
       <c r="R204" s="26" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="S204" s="29" t="n">
         <v>1</v>
@@ -63266,7 +63266,7 @@
       <c r="AD204" s="24" t="n"/>
       <c r="AE204" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.96-4.59; raw selected-side p=0.6359, calibrated p=0.5396.</t>
+          <t>Measured Edge Totals: Trend Engine projected 3.96-4.59; raw selected-side p=0.6383, calibrated p=0.5402.</t>
         </is>
       </c>
       <c r="AF204" s="31" t="inlineStr">
@@ -63385,7 +63385,7 @@
       </c>
       <c r="BH204" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI204" s="24" t="inlineStr">
@@ -63397,16 +63397,16 @@
         <v>9.5</v>
       </c>
       <c r="BK204" s="26" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="BL204" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.961538</v>
       </c>
       <c r="BM204" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.509804</v>
       </c>
       <c r="BN204" s="28" t="n">
-        <v>0.517413</v>
+        <v>0.507463</v>
       </c>
       <c r="BO204" s="28" t="n"/>
       <c r="BP204" s="25" t="n"/>
@@ -63447,12 +63447,12 @@
     <row r="205" ht="36" customHeight="1">
       <c r="A205" s="24" t="inlineStr">
         <is>
-          <t>0d24c94754b64c63</t>
+          <t>21ae370f36684ead</t>
         </is>
       </c>
       <c r="B205" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C205" s="24" t="inlineStr">
@@ -63508,13 +63508,13 @@
         <v>0.565217</v>
       </c>
       <c r="O205" s="28" t="n">
-        <v>0.588514</v>
+        <v>0.587935</v>
       </c>
       <c r="P205" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q205" s="28" t="n">
-        <v>0.023297</v>
+        <v>0.022718</v>
       </c>
       <c r="R205" s="26" t="n">
         <v>32</v>
@@ -63543,7 +63543,7 @@
       <c r="AD205" s="24" t="n"/>
       <c r="AE205" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.57-4.92; raw selected-side p=0.6299, calibrated p=0.5885.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.57-4.92; raw selected-side p=0.6290, calibrated p=0.5879.</t>
         </is>
       </c>
       <c r="AF205" s="31" t="inlineStr">
@@ -63662,7 +63662,7 @@
       </c>
       <c r="BH205" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI205" s="24" t="inlineStr">
@@ -63724,12 +63724,12 @@
     <row r="206" ht="36" customHeight="1">
       <c r="A206" s="24" t="inlineStr">
         <is>
-          <t>76748dfba8094a58</t>
+          <t>5ddca6a6a2a64ce9</t>
         </is>
       </c>
       <c r="B206" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C206" s="24" t="inlineStr">
@@ -63785,16 +63785,16 @@
         <v>0.480769</v>
       </c>
       <c r="O206" s="28" t="n">
-        <v>0.522257</v>
+        <v>0.519176</v>
       </c>
       <c r="P206" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q206" s="28" t="n">
-        <v>0.041488</v>
+        <v>0.038407</v>
       </c>
       <c r="R206" s="26" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S206" s="29" t="n">
         <v>1</v>
@@ -63820,7 +63820,7 @@
       <c r="AD206" s="24" t="n"/>
       <c r="AE206" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.57-4.92; raw selected-side p=0.5663, calibrated p=0.5223.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.57-4.92; raw selected-side p=0.5538, calibrated p=0.5192.</t>
         </is>
       </c>
       <c r="AF206" s="31" t="inlineStr">
@@ -63939,7 +63939,7 @@
       </c>
       <c r="BH206" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI206" s="24" t="inlineStr">
@@ -64001,12 +64001,12 @@
     <row r="207" ht="36" customHeight="1">
       <c r="A207" s="24" t="inlineStr">
         <is>
-          <t>0cd90ea61a734a0b</t>
+          <t>011175b8945c4b41</t>
         </is>
       </c>
       <c r="B207" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C207" s="24" t="inlineStr">
@@ -64053,25 +64053,25 @@
         </is>
       </c>
       <c r="L207" s="26" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="M207" s="27" t="n">
-        <v>1.961538</v>
+        <v>2</v>
       </c>
       <c r="N207" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.5</v>
       </c>
       <c r="O207" s="28" t="n">
-        <v>0.602278</v>
+        <v>0.600915</v>
       </c>
       <c r="P207" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q207" s="28" t="n">
-        <v>0.092474</v>
+        <v>0.100915</v>
       </c>
       <c r="R207" s="26" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="S207" s="29" t="n">
         <v>1.5</v>
@@ -64097,7 +64097,7 @@
       <c r="AD207" s="24" t="n"/>
       <c r="AE207" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.81-4.67; raw selected-side p=0.6501, calibrated p=0.6023.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.81-4.66; raw selected-side p=0.6481, calibrated p=0.6009.</t>
         </is>
       </c>
       <c r="AF207" s="31" t="inlineStr">
@@ -64216,7 +64216,7 @@
       </c>
       <c r="BH207" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI207" s="24" t="inlineStr">
@@ -64228,16 +64228,16 @@
         <v>1.5</v>
       </c>
       <c r="BK207" s="26" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="BL207" s="27" t="n">
-        <v>1.961538</v>
+        <v>2</v>
       </c>
       <c r="BM207" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.5</v>
       </c>
       <c r="BN207" s="28" t="n">
-        <v>0.507463</v>
+        <v>0.497512</v>
       </c>
       <c r="BO207" s="28" t="n"/>
       <c r="BP207" s="25" t="n"/>
@@ -64278,12 +64278,12 @@
     <row r="208" ht="36" customHeight="1">
       <c r="A208" s="24" t="inlineStr">
         <is>
-          <t>14659c36acee4d5f</t>
+          <t>b0eee51cd3b44422</t>
         </is>
       </c>
       <c r="B208" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C208" s="24" t="inlineStr">
@@ -64330,25 +64330,25 @@
         </is>
       </c>
       <c r="L208" s="26" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M208" s="27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="N208" s="28" t="n">
-        <v>0.5</v>
+        <v>0.49505</v>
       </c>
       <c r="O208" s="28" t="n">
-        <v>0.557989</v>
+        <v>0.558548</v>
       </c>
       <c r="P208" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q208" s="28" t="n">
-        <v>0.057989</v>
+        <v>0.063498</v>
       </c>
       <c r="R208" s="26" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="S208" s="29" t="n">
         <v>1</v>
@@ -64374,7 +64374,7 @@
       <c r="AD208" s="24" t="n"/>
       <c r="AE208" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.81-4.67; raw selected-side p=0.7101, calibrated p=0.5580.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.81-4.66; raw selected-side p=0.7124, calibrated p=0.5585.</t>
         </is>
       </c>
       <c r="AF208" s="31" t="inlineStr">
@@ -64493,7 +64493,7 @@
       </c>
       <c r="BH208" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI208" s="24" t="inlineStr">
@@ -64505,16 +64505,16 @@
         <v>11.5</v>
       </c>
       <c r="BK208" s="26" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BL208" s="27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BM208" s="28" t="n">
-        <v>0.5</v>
+        <v>0.49505</v>
       </c>
       <c r="BN208" s="28" t="n">
-        <v>0.49505</v>
+        <v>0.492537</v>
       </c>
       <c r="BO208" s="28" t="n"/>
       <c r="BP208" s="25" t="n"/>
@@ -64555,12 +64555,12 @@
     <row r="209" ht="36" customHeight="1">
       <c r="A209" s="24" t="inlineStr">
         <is>
-          <t>c84c5e3ee91443f5</t>
+          <t>087961e2f0c74b71</t>
         </is>
       </c>
       <c r="B209" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C209" s="24" t="inlineStr">
@@ -64607,25 +64607,25 @@
         </is>
       </c>
       <c r="L209" s="26" t="n">
-        <v>-167</v>
+        <v>-174</v>
       </c>
       <c r="M209" s="27" t="n">
-        <v>1.598802</v>
+        <v>1.574713</v>
       </c>
       <c r="N209" s="28" t="n">
-        <v>0.625468</v>
+        <v>0.635036</v>
       </c>
       <c r="O209" s="28" t="n">
-        <v>0.585379</v>
+        <v>0.590183</v>
       </c>
       <c r="P209" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q209" s="28" t="n">
-        <v>-0.040089</v>
+        <v>-0.044853</v>
       </c>
       <c r="R209" s="26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S209" s="29" t="n">
         <v>1.25</v>
@@ -64651,7 +64651,7 @@
       <c r="AD209" s="24" t="n"/>
       <c r="AE209" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.25-4.70; raw selected-side p=0.6253, calibrated p=0.5854.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.25-4.70; raw selected-side p=0.6323, calibrated p=0.5902.</t>
         </is>
       </c>
       <c r="AF209" s="31" t="inlineStr">
@@ -64770,7 +64770,7 @@
       </c>
       <c r="BH209" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI209" s="24" t="inlineStr">
@@ -64782,16 +64782,16 @@
         <v>1.5</v>
       </c>
       <c r="BK209" s="26" t="n">
-        <v>-167</v>
+        <v>-174</v>
       </c>
       <c r="BL209" s="27" t="n">
-        <v>1.598802</v>
+        <v>1.574713</v>
       </c>
       <c r="BM209" s="28" t="n">
-        <v>0.625468</v>
+        <v>0.635036</v>
       </c>
       <c r="BN209" s="28" t="n">
-        <v>0.621891</v>
+        <v>0.631841</v>
       </c>
       <c r="BO209" s="28" t="n"/>
       <c r="BP209" s="25" t="n"/>
@@ -64832,12 +64832,12 @@
     <row r="210" ht="36" customHeight="1">
       <c r="A210" s="24" t="inlineStr">
         <is>
-          <t>276c399a45f44a14</t>
+          <t>535a08003a8a4c2d</t>
         </is>
       </c>
       <c r="B210" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C210" s="24" t="inlineStr">
@@ -64876,7 +64876,7 @@
         </is>
       </c>
       <c r="J210" s="25" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="K210" s="24" t="inlineStr">
         <is>
@@ -64884,25 +64884,25 @@
         </is>
       </c>
       <c r="L210" s="26" t="n">
-        <v>111</v>
+        <v>-115</v>
       </c>
       <c r="M210" s="27" t="n">
-        <v>2.11</v>
+        <v>1.869565</v>
       </c>
       <c r="N210" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.534884</v>
       </c>
       <c r="O210" s="28" t="n">
-        <v>0.5089669999999999</v>
+        <v>0.527597</v>
       </c>
       <c r="P210" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q210" s="28" t="n">
-        <v>0.035033</v>
+        <v>-0.007287</v>
       </c>
       <c r="R210" s="26" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="S210" s="29" t="n">
         <v>1</v>
@@ -64928,7 +64928,7 @@
       <c r="AD210" s="24" t="n"/>
       <c r="AE210" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.25-4.70; raw selected-side p=0.5128, calibrated p=0.5090.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.25-4.70; raw selected-side p=0.5877, calibrated p=0.5276.</t>
         </is>
       </c>
       <c r="AF210" s="31" t="inlineStr">
@@ -65047,7 +65047,7 @@
       </c>
       <c r="BH210" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI210" s="24" t="inlineStr">
@@ -65056,19 +65056,19 @@
         </is>
       </c>
       <c r="BJ210" s="25" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BK210" s="26" t="n">
-        <v>111</v>
+        <v>-115</v>
       </c>
       <c r="BL210" s="27" t="n">
-        <v>2.11</v>
+        <v>1.869565</v>
       </c>
       <c r="BM210" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.534884</v>
       </c>
       <c r="BN210" s="28" t="n">
-        <v>0.472637</v>
+        <v>0.532338</v>
       </c>
       <c r="BO210" s="28" t="n"/>
       <c r="BP210" s="25" t="n"/>
@@ -65102,19 +65102,19 @@
       <c r="CR210" s="24" t="n"/>
       <c r="CS210" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="211" ht="36" customHeight="1">
       <c r="A211" s="24" t="inlineStr">
         <is>
-          <t>09e9149787ed47e4</t>
+          <t>ed818bf10f91467f</t>
         </is>
       </c>
       <c r="B211" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C211" s="24" t="inlineStr">
@@ -65170,16 +65170,16 @@
         <v>0.604743</v>
       </c>
       <c r="O211" s="28" t="n">
-        <v>0.590797</v>
+        <v>0.594067</v>
       </c>
       <c r="P211" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q211" s="28" t="n">
-        <v>-0.013946</v>
+        <v>-0.010676</v>
       </c>
       <c r="R211" s="26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S211" s="29" t="n">
         <v>1.25</v>
@@ -65205,7 +65205,7 @@
       <c r="AD211" s="24" t="n"/>
       <c r="AE211" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.90-5.09; raw selected-side p=0.6332, calibrated p=0.5908.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.90-5.09; raw selected-side p=0.6381, calibrated p=0.5941.</t>
         </is>
       </c>
       <c r="AF211" s="31" t="inlineStr">
@@ -65324,7 +65324,7 @@
       </c>
       <c r="BH211" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI211" s="24" t="inlineStr">
@@ -65386,12 +65386,12 @@
     <row r="212" ht="36" customHeight="1">
       <c r="A212" s="24" t="inlineStr">
         <is>
-          <t>c5aaf24102e945be</t>
+          <t>b1ad3a4710984315</t>
         </is>
       </c>
       <c r="B212" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C212" s="24" t="inlineStr">
@@ -65447,16 +65447,16 @@
         <v>0.490196</v>
       </c>
       <c r="O212" s="28" t="n">
-        <v>0.509116</v>
+        <v>0.509961</v>
       </c>
       <c r="P212" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q212" s="28" t="n">
-        <v>0.01892</v>
+        <v>0.019765</v>
       </c>
       <c r="R212" s="26" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S212" s="29" t="n">
         <v>1</v>
@@ -65482,7 +65482,7 @@
       <c r="AD212" s="24" t="n"/>
       <c r="AE212" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.90-5.09; raw selected-side p=0.5133, calibrated p=0.5091.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.90-5.09; raw selected-side p=0.5168, calibrated p=0.5100.</t>
         </is>
       </c>
       <c r="AF212" s="31" t="inlineStr">
@@ -65601,7 +65601,7 @@
       </c>
       <c r="BH212" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI212" s="24" t="inlineStr">
@@ -65663,12 +65663,12 @@
     <row r="213" ht="36" customHeight="1">
       <c r="A213" s="24" t="inlineStr">
         <is>
-          <t>066b2518b950478a</t>
+          <t>09d22d46c62d4d23</t>
         </is>
       </c>
       <c r="B213" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C213" s="24" t="inlineStr">
@@ -65715,25 +65715,25 @@
         </is>
       </c>
       <c r="L213" s="26" t="n">
-        <v>-153</v>
+        <v>-170</v>
       </c>
       <c r="M213" s="27" t="n">
-        <v>1.653595</v>
+        <v>1.588235</v>
       </c>
       <c r="N213" s="28" t="n">
-        <v>0.604743</v>
+        <v>0.62963</v>
       </c>
       <c r="O213" s="28" t="n">
-        <v>0.60221</v>
+        <v>0.611375</v>
       </c>
       <c r="P213" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q213" s="28" t="n">
-        <v>-0.002533</v>
+        <v>-0.018255</v>
       </c>
       <c r="R213" s="26" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="S213" s="29" t="n">
         <v>1.5</v>
@@ -65759,7 +65759,7 @@
       <c r="AD213" s="24" t="n"/>
       <c r="AE213" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.46-4.24; raw selected-side p=0.6500, calibrated p=0.6022.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.46-4.24; raw selected-side p=0.6634, calibrated p=0.6114.</t>
         </is>
       </c>
       <c r="AF213" s="31" t="inlineStr">
@@ -65878,7 +65878,7 @@
       </c>
       <c r="BH213" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI213" s="24" t="inlineStr">
@@ -65890,16 +65890,16 @@
         <v>1.5</v>
       </c>
       <c r="BK213" s="26" t="n">
-        <v>-153</v>
+        <v>-170</v>
       </c>
       <c r="BL213" s="27" t="n">
-        <v>1.653595</v>
+        <v>1.588235</v>
       </c>
       <c r="BM213" s="28" t="n">
-        <v>0.604743</v>
+        <v>0.62963</v>
       </c>
       <c r="BN213" s="28" t="n">
-        <v>0.60199</v>
+        <v>0.626866</v>
       </c>
       <c r="BO213" s="28" t="n"/>
       <c r="BP213" s="25" t="n"/>
@@ -65940,12 +65940,12 @@
     <row r="214" ht="36" customHeight="1">
       <c r="A214" s="24" t="inlineStr">
         <is>
-          <t>c8fc1ee12e1f422d</t>
+          <t>e753f321748a4b0a</t>
         </is>
       </c>
       <c r="B214" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C214" s="24" t="inlineStr">
@@ -65980,11 +65980,11 @@
       </c>
       <c r="I214" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J214" s="25" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="K214" s="24" t="inlineStr">
         <is>
@@ -65992,25 +65992,25 @@
         </is>
       </c>
       <c r="L214" s="26" t="n">
-        <v>-102</v>
+        <v>-111</v>
       </c>
       <c r="M214" s="27" t="n">
-        <v>1.980392</v>
+        <v>1.900901</v>
       </c>
       <c r="N214" s="28" t="n">
-        <v>0.50495</v>
+        <v>0.526066</v>
       </c>
       <c r="O214" s="28" t="n">
-        <v>0.50934</v>
+        <v>0.522244</v>
       </c>
       <c r="P214" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q214" s="28" t="n">
-        <v>0.00439</v>
+        <v>-0.003822</v>
       </c>
       <c r="R214" s="26" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S214" s="29" t="n">
         <v>1</v>
@@ -66036,7 +66036,7 @@
       <c r="AD214" s="24" t="n"/>
       <c r="AE214" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.46-4.24; raw selected-side p=0.5142, calibrated p=0.5093.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.46-4.24; raw selected-side p=0.5662, calibrated p=0.5222.</t>
         </is>
       </c>
       <c r="AF214" s="31" t="inlineStr">
@@ -66155,7 +66155,7 @@
       </c>
       <c r="BH214" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI214" s="24" t="inlineStr">
@@ -66164,19 +66164,19 @@
         </is>
       </c>
       <c r="BJ214" s="25" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BK214" s="26" t="n">
-        <v>-102</v>
+        <v>-111</v>
       </c>
       <c r="BL214" s="27" t="n">
-        <v>1.980392</v>
+        <v>1.900901</v>
       </c>
       <c r="BM214" s="28" t="n">
-        <v>0.50495</v>
+        <v>0.526066</v>
       </c>
       <c r="BN214" s="28" t="n">
-        <v>0.502488</v>
+        <v>0.522388</v>
       </c>
       <c r="BO214" s="28" t="n"/>
       <c r="BP214" s="25" t="n"/>
@@ -66210,19 +66210,19 @@
       <c r="CR214" s="24" t="n"/>
       <c r="CS214" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="215" ht="36" customHeight="1">
       <c r="A215" s="24" t="inlineStr">
         <is>
-          <t>752d0681afe84a29</t>
+          <t>3d42118f96554a28</t>
         </is>
       </c>
       <c r="B215" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C215" s="24" t="inlineStr">
@@ -66269,25 +66269,25 @@
         </is>
       </c>
       <c r="L215" s="26" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="M215" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.819672</v>
       </c>
       <c r="N215" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.54955</v>
       </c>
       <c r="O215" s="28" t="n">
-        <v>0.60238</v>
+        <v>0.603096</v>
       </c>
       <c r="P215" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q215" s="28" t="n">
-        <v>0.042909</v>
+        <v>0.053546</v>
       </c>
       <c r="R215" s="26" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="S215" s="29" t="n">
         <v>1.5</v>
@@ -66313,7 +66313,7 @@
       <c r="AD215" s="24" t="n"/>
       <c r="AE215" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 5.21-5.30; raw selected-side p=0.6502, calibrated p=0.6024.</t>
+          <t>Measured Edge Margin: Trend Engine projected 5.21-5.30; raw selected-side p=0.6513, calibrated p=0.6031.</t>
         </is>
       </c>
       <c r="AF215" s="31" t="inlineStr">
@@ -66432,7 +66432,7 @@
       </c>
       <c r="BH215" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI215" s="24" t="inlineStr">
@@ -66444,16 +66444,16 @@
         <v>1.5</v>
       </c>
       <c r="BK215" s="26" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="BL215" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.819672</v>
       </c>
       <c r="BM215" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.54955</v>
       </c>
       <c r="BN215" s="28" t="n">
-        <v>0.554455</v>
+        <v>0.547264</v>
       </c>
       <c r="BO215" s="28" t="n"/>
       <c r="BP215" s="25" t="n"/>
@@ -66494,12 +66494,12 @@
     <row r="216" ht="36" customHeight="1">
       <c r="A216" s="24" t="inlineStr">
         <is>
-          <t>aef861b91af148b0</t>
+          <t>5bd846da30024e77</t>
         </is>
       </c>
       <c r="B216" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C216" s="24" t="inlineStr">
@@ -66546,22 +66546,22 @@
         </is>
       </c>
       <c r="L216" s="26" t="n">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="M216" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.980392</v>
       </c>
       <c r="N216" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.50495</v>
       </c>
       <c r="O216" s="28" t="n">
-        <v>0.5154879999999999</v>
+        <v>0.511737</v>
       </c>
       <c r="P216" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q216" s="28" t="n">
-        <v>0.005684</v>
+        <v>0.006787</v>
       </c>
       <c r="R216" s="26" t="n">
         <v>29</v>
@@ -66590,7 +66590,7 @@
       <c r="AD216" s="24" t="n"/>
       <c r="AE216" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 5.21-5.30; raw selected-side p=0.5390, calibrated p=0.5155.</t>
+          <t>Measured Edge Totals: Trend Engine projected 5.21-5.30; raw selected-side p=0.5239, calibrated p=0.5117.</t>
         </is>
       </c>
       <c r="AF216" s="31" t="inlineStr">
@@ -66709,7 +66709,7 @@
       </c>
       <c r="BH216" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI216" s="24" t="inlineStr">
@@ -66721,16 +66721,16 @@
         <v>9.5</v>
       </c>
       <c r="BK216" s="26" t="n">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="BL216" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.980392</v>
       </c>
       <c r="BM216" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.50495</v>
       </c>
       <c r="BN216" s="28" t="n">
-        <v>0.507463</v>
+        <v>0.502488</v>
       </c>
       <c r="BO216" s="28" t="n"/>
       <c r="BP216" s="25" t="n"/>
@@ -66771,12 +66771,12 @@
     <row r="217" ht="36" customHeight="1">
       <c r="A217" s="24" t="inlineStr">
         <is>
-          <t>52aaeb284bef4334</t>
+          <t>a08d34f0b56a4205</t>
         </is>
       </c>
       <c r="B217" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C217" s="24" t="inlineStr">
@@ -66823,25 +66823,25 @@
         </is>
       </c>
       <c r="L217" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="M217" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="N217" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="O217" s="28" t="n">
-        <v>0.6248320000000001</v>
+        <v>0.624219</v>
       </c>
       <c r="P217" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q217" s="28" t="n">
-        <v>0.024832</v>
+        <v>0.034055</v>
       </c>
       <c r="R217" s="26" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="S217" s="29" t="n">
         <v>1.5</v>
@@ -66867,7 +66867,7 @@
       <c r="AD217" s="24" t="n"/>
       <c r="AE217" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.74-4.57; raw selected-side p=0.6832, calibrated p=0.6248.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.74-4.57; raw selected-side p=0.6823, calibrated p=0.6242.</t>
         </is>
       </c>
       <c r="AF217" s="31" t="inlineStr">
@@ -66986,7 +66986,7 @@
       </c>
       <c r="BH217" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI217" s="24" t="inlineStr">
@@ -66998,16 +66998,16 @@
         <v>1.5</v>
       </c>
       <c r="BK217" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="BL217" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="BM217" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="BN217" s="28" t="n">
-        <v>0.597015</v>
+        <v>0.5870649999999999</v>
       </c>
       <c r="BO217" s="28" t="n"/>
       <c r="BP217" s="25" t="n"/>
@@ -67048,12 +67048,12 @@
     <row r="218" ht="36" customHeight="1">
       <c r="A218" s="24" t="inlineStr">
         <is>
-          <t>f40f762a1ba74bba</t>
+          <t>44d845a6727d4325</t>
         </is>
       </c>
       <c r="B218" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C218" s="24" t="inlineStr">
@@ -67100,25 +67100,25 @@
         </is>
       </c>
       <c r="L218" s="26" t="n">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="M218" s="27" t="n">
-        <v>1.900901</v>
+        <v>1.925926</v>
       </c>
       <c r="N218" s="28" t="n">
-        <v>0.526066</v>
+        <v>0.519231</v>
       </c>
       <c r="O218" s="28" t="n">
-        <v>0.516866</v>
+        <v>0.515997</v>
       </c>
       <c r="P218" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q218" s="28" t="n">
-        <v>-0.0092</v>
+        <v>-0.003234</v>
       </c>
       <c r="R218" s="26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="S218" s="29" t="n">
         <v>1</v>
@@ -67144,7 +67144,7 @@
       <c r="AD218" s="24" t="n"/>
       <c r="AE218" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.74-4.57; raw selected-side p=0.5445, calibrated p=0.5169.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.74-4.57; raw selected-side p=0.5411, calibrated p=0.5160.</t>
         </is>
       </c>
       <c r="AF218" s="31" t="inlineStr">
@@ -67263,7 +67263,7 @@
       </c>
       <c r="BH218" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI218" s="24" t="inlineStr">
@@ -67275,16 +67275,16 @@
         <v>8.5</v>
       </c>
       <c r="BK218" s="26" t="n">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="BL218" s="27" t="n">
-        <v>1.900901</v>
+        <v>1.925926</v>
       </c>
       <c r="BM218" s="28" t="n">
-        <v>0.526066</v>
+        <v>0.519231</v>
       </c>
       <c r="BN218" s="28" t="n">
-        <v>0.522388</v>
+        <v>0.517413</v>
       </c>
       <c r="BO218" s="28" t="n"/>
       <c r="BP218" s="25" t="n"/>
@@ -67325,12 +67325,12 @@
     <row r="219" ht="36" customHeight="1">
       <c r="A219" s="24" t="inlineStr">
         <is>
-          <t>bb089dab22964210</t>
+          <t>05636342c84641d7</t>
         </is>
       </c>
       <c r="B219" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C219" s="24" t="inlineStr">
@@ -67377,25 +67377,25 @@
         </is>
       </c>
       <c r="L219" s="26" t="n">
-        <v>-182</v>
+        <v>-167</v>
       </c>
       <c r="M219" s="27" t="n">
-        <v>1.549451</v>
+        <v>1.598802</v>
       </c>
       <c r="N219" s="28" t="n">
-        <v>0.64539</v>
+        <v>0.625468</v>
       </c>
       <c r="O219" s="28" t="n">
-        <v>0.6332140000000001</v>
+        <v>0.633248</v>
       </c>
       <c r="P219" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q219" s="28" t="n">
-        <v>-0.012176</v>
+        <v>0.00778</v>
       </c>
       <c r="R219" s="26" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="S219" s="29" t="n">
         <v>1.5</v>
@@ -67421,7 +67421,7 @@
       <c r="AD219" s="24" t="n"/>
       <c r="AE219" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.13-3.98; raw selected-side p=0.6955, calibrated p=0.6332.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.13-3.98; raw selected-side p=0.6956, calibrated p=0.6332.</t>
         </is>
       </c>
       <c r="AF219" s="31" t="inlineStr">
@@ -67540,7 +67540,7 @@
       </c>
       <c r="BH219" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI219" s="24" t="inlineStr">
@@ -67552,16 +67552,16 @@
         <v>1.5</v>
       </c>
       <c r="BK219" s="26" t="n">
-        <v>-182</v>
+        <v>-167</v>
       </c>
       <c r="BL219" s="27" t="n">
-        <v>1.549451</v>
+        <v>1.598802</v>
       </c>
       <c r="BM219" s="28" t="n">
-        <v>0.64539</v>
+        <v>0.625468</v>
       </c>
       <c r="BN219" s="28" t="n">
-        <v>0.641791</v>
+        <v>0.621891</v>
       </c>
       <c r="BO219" s="28" t="n"/>
       <c r="BP219" s="25" t="n"/>
@@ -67595,19 +67595,19 @@
       <c r="CR219" s="24" t="n"/>
       <c r="CS219" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="220" ht="36" customHeight="1">
       <c r="A220" s="24" t="inlineStr">
         <is>
-          <t>c4dda4d6947e4af2</t>
+          <t>0862f28e8fcd401c</t>
         </is>
       </c>
       <c r="B220" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C220" s="24" t="inlineStr">
@@ -67654,25 +67654,25 @@
         </is>
       </c>
       <c r="L220" s="26" t="n">
-        <v>100</v>
+        <v>-111</v>
       </c>
       <c r="M220" s="27" t="n">
-        <v>2</v>
+        <v>1.900901</v>
       </c>
       <c r="N220" s="28" t="n">
-        <v>0.5</v>
+        <v>0.526066</v>
       </c>
       <c r="O220" s="28" t="n">
-        <v>0.52325</v>
+        <v>0.522381</v>
       </c>
       <c r="P220" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q220" s="28" t="n">
-        <v>0.02325</v>
+        <v>-0.003685</v>
       </c>
       <c r="R220" s="26" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="S220" s="29" t="n">
         <v>1</v>
@@ -67698,7 +67698,7 @@
       <c r="AD220" s="24" t="n"/>
       <c r="AE220" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.13-3.98; raw selected-side p=0.5703, calibrated p=0.5233.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.13-3.98; raw selected-side p=0.5667, calibrated p=0.5224.</t>
         </is>
       </c>
       <c r="AF220" s="31" t="inlineStr">
@@ -67817,7 +67817,7 @@
       </c>
       <c r="BH220" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI220" s="24" t="inlineStr">
@@ -67829,16 +67829,16 @@
         <v>8.5</v>
       </c>
       <c r="BK220" s="26" t="n">
-        <v>100</v>
+        <v>-111</v>
       </c>
       <c r="BL220" s="27" t="n">
-        <v>2</v>
+        <v>1.900901</v>
       </c>
       <c r="BM220" s="28" t="n">
-        <v>0.5</v>
+        <v>0.526066</v>
       </c>
       <c r="BN220" s="28" t="n">
-        <v>0.497512</v>
+        <v>0.522388</v>
       </c>
       <c r="BO220" s="28" t="n"/>
       <c r="BP220" s="25" t="n"/>
@@ -67872,19 +67872,19 @@
       <c r="CR220" s="24" t="n"/>
       <c r="CS220" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="221" ht="36" customHeight="1">
       <c r="A221" s="24" t="inlineStr">
         <is>
-          <t>ba991f0b9ea64ab9</t>
+          <t>6c7fdfd427e540ad</t>
         </is>
       </c>
       <c r="B221" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C221" s="24" t="inlineStr">
@@ -67940,16 +67940,16 @@
         <v>0.635036</v>
       </c>
       <c r="O221" s="28" t="n">
-        <v>0.639346</v>
+        <v>0.639551</v>
       </c>
       <c r="P221" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q221" s="28" t="n">
-        <v>0.00431</v>
+        <v>0.004515</v>
       </c>
       <c r="R221" s="26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S221" s="29" t="n">
         <v>1.75</v>
@@ -67975,7 +67975,7 @@
       <c r="AD221" s="24" t="n"/>
       <c r="AE221" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.38-4.11; raw selected-side p=0.7045, calibrated p=0.6393.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.38-4.11; raw selected-side p=0.7048, calibrated p=0.6396.</t>
         </is>
       </c>
       <c r="AF221" s="31" t="inlineStr">
@@ -68094,7 +68094,7 @@
       </c>
       <c r="BH221" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI221" s="24" t="inlineStr">
@@ -68156,12 +68156,12 @@
     <row r="222" ht="36" customHeight="1">
       <c r="A222" s="24" t="inlineStr">
         <is>
-          <t>f0a23255eaaa4207</t>
+          <t>fbf4b19abd124423</t>
         </is>
       </c>
       <c r="B222" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C222" s="24" t="inlineStr">
@@ -68208,25 +68208,25 @@
         </is>
       </c>
       <c r="L222" s="26" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M222" s="27" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="N222" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.480769</v>
       </c>
       <c r="O222" s="28" t="n">
-        <v>0.51201</v>
+        <v>0.513637</v>
       </c>
       <c r="P222" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q222" s="28" t="n">
-        <v>0.038076</v>
+        <v>0.032868</v>
       </c>
       <c r="R222" s="26" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S222" s="29" t="n">
         <v>1</v>
@@ -68252,7 +68252,7 @@
       <c r="AD222" s="24" t="n"/>
       <c r="AE222" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.38-4.11; raw selected-side p=0.5250, calibrated p=0.5120.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.38-4.11; raw selected-side p=0.5315, calibrated p=0.5136.</t>
         </is>
       </c>
       <c r="AF222" s="31" t="inlineStr">
@@ -68371,7 +68371,7 @@
       </c>
       <c r="BH222" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI222" s="24" t="inlineStr">
@@ -68383,16 +68383,16 @@
         <v>8.5</v>
       </c>
       <c r="BK222" s="26" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BL222" s="27" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="BM222" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.480769</v>
       </c>
       <c r="BN222" s="28" t="n">
-        <v>0.472637</v>
+        <v>0.477612</v>
       </c>
       <c r="BO222" s="28" t="n"/>
       <c r="BP222" s="25" t="n"/>
@@ -68433,12 +68433,12 @@
     <row r="223" ht="36" customHeight="1">
       <c r="A223" s="24" t="inlineStr">
         <is>
-          <t>fa3e2c85412847c3</t>
+          <t>cb88912e18744f3e</t>
         </is>
       </c>
       <c r="B223" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C223" s="24" t="inlineStr">
@@ -68494,16 +68494,16 @@
         <v>0.640288</v>
       </c>
       <c r="O223" s="28" t="n">
-        <v>0.590354</v>
+        <v>0.586402</v>
       </c>
       <c r="P223" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q223" s="28" t="n">
-        <v>-0.049934</v>
+        <v>-0.053886</v>
       </c>
       <c r="R223" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S223" s="29" t="n">
         <v>1.25</v>
@@ -68529,7 +68529,7 @@
       <c r="AD223" s="24" t="n"/>
       <c r="AE223" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.27-4.68; raw selected-side p=0.6326, calibrated p=0.5904.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.27-4.68; raw selected-side p=0.6268, calibrated p=0.5864.</t>
         </is>
       </c>
       <c r="AF223" s="31" t="inlineStr">
@@ -68648,7 +68648,7 @@
       </c>
       <c r="BH223" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI223" s="24" t="inlineStr">
@@ -68710,12 +68710,12 @@
     <row r="224" ht="36" customHeight="1">
       <c r="A224" s="24" t="inlineStr">
         <is>
-          <t>38e7ec7e31dd40c3</t>
+          <t>f776c4b504a54715</t>
         </is>
       </c>
       <c r="B224" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C224" s="24" t="inlineStr">
@@ -68762,25 +68762,25 @@
         </is>
       </c>
       <c r="L224" s="26" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="M224" s="27" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="N224" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.460829</v>
       </c>
       <c r="O224" s="28" t="n">
-        <v>0.527448</v>
+        <v>0.527398</v>
       </c>
       <c r="P224" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q224" s="28" t="n">
-        <v>0.053514</v>
+        <v>0.066569</v>
       </c>
       <c r="R224" s="26" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="S224" s="29" t="n">
         <v>1</v>
@@ -68806,7 +68806,7 @@
       <c r="AD224" s="24" t="n"/>
       <c r="AE224" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.27-4.68; raw selected-side p=0.5871, calibrated p=0.5274.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.27-4.68; raw selected-side p=0.5869, calibrated p=0.5274.</t>
         </is>
       </c>
       <c r="AF224" s="31" t="inlineStr">
@@ -68925,7 +68925,7 @@
       </c>
       <c r="BH224" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI224" s="24" t="inlineStr">
@@ -68937,16 +68937,16 @@
         <v>7.5</v>
       </c>
       <c r="BK224" s="26" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="BL224" s="27" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="BM224" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.460829</v>
       </c>
       <c r="BN224" s="28" t="n">
-        <v>0.472637</v>
+        <v>0.457711</v>
       </c>
       <c r="BO224" s="28" t="n"/>
       <c r="BP224" s="25" t="n"/>
@@ -68987,12 +68987,12 @@
     <row r="225" ht="36" customHeight="1">
       <c r="A225" s="24" t="inlineStr">
         <is>
-          <t>b58820a536ec4f82</t>
+          <t>7847dc728e3644d6</t>
         </is>
       </c>
       <c r="B225" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C225" s="24" t="inlineStr">
@@ -69039,25 +69039,25 @@
         </is>
       </c>
       <c r="L225" s="26" t="n">
-        <v>-174</v>
+        <v>-178</v>
       </c>
       <c r="M225" s="27" t="n">
-        <v>1.574713</v>
+        <v>1.561798</v>
       </c>
       <c r="N225" s="28" t="n">
-        <v>0.635036</v>
+        <v>0.640288</v>
       </c>
       <c r="O225" s="28" t="n">
-        <v>0.647353</v>
+        <v>0.648545</v>
       </c>
       <c r="P225" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q225" s="28" t="n">
-        <v>0.012317</v>
+        <v>0.008257</v>
       </c>
       <c r="R225" s="26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S225" s="29" t="n">
         <v>1.75</v>
@@ -69083,7 +69083,7 @@
       <c r="AD225" s="24" t="n"/>
       <c r="AE225" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.58-5.19; raw selected-side p=0.7163, calibrated p=0.6474.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.58-5.19; raw selected-side p=0.7180, calibrated p=0.6485.</t>
         </is>
       </c>
       <c r="AF225" s="31" t="inlineStr">
@@ -69202,7 +69202,7 @@
       </c>
       <c r="BH225" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI225" s="24" t="inlineStr">
@@ -69214,16 +69214,16 @@
         <v>1.5</v>
       </c>
       <c r="BK225" s="26" t="n">
-        <v>-174</v>
+        <v>-178</v>
       </c>
       <c r="BL225" s="27" t="n">
-        <v>1.574713</v>
+        <v>1.561798</v>
       </c>
       <c r="BM225" s="28" t="n">
-        <v>0.635036</v>
+        <v>0.640288</v>
       </c>
       <c r="BN225" s="28" t="n">
-        <v>0.631841</v>
+        <v>0.636816</v>
       </c>
       <c r="BO225" s="28" t="n"/>
       <c r="BP225" s="25" t="n"/>
@@ -69264,12 +69264,12 @@
     <row r="226" ht="36" customHeight="1">
       <c r="A226" s="24" t="inlineStr">
         <is>
-          <t>bd50730c4fab42bb</t>
+          <t>3a3a3a079e0b4ac3</t>
         </is>
       </c>
       <c r="B226" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C226" s="24" t="inlineStr">
@@ -69304,11 +69304,11 @@
       </c>
       <c r="I226" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J226" s="25" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="K226" s="24" t="inlineStr">
         <is>
@@ -69316,25 +69316,25 @@
         </is>
       </c>
       <c r="L226" s="26" t="n">
-        <v>-122</v>
+        <v>-111</v>
       </c>
       <c r="M226" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.900901</v>
       </c>
       <c r="N226" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.526066</v>
       </c>
       <c r="O226" s="28" t="n">
-        <v>0.51355</v>
+        <v>0.524778</v>
       </c>
       <c r="P226" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q226" s="28" t="n">
-        <v>-0.036</v>
+        <v>-0.001288</v>
       </c>
       <c r="R226" s="26" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="S226" s="29" t="n">
         <v>1</v>
@@ -69360,7 +69360,7 @@
       <c r="AD226" s="24" t="n"/>
       <c r="AE226" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.58-5.19; raw selected-side p=0.5312, calibrated p=0.5136.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.58-5.19; raw selected-side p=0.5764, calibrated p=0.5248.</t>
         </is>
       </c>
       <c r="AF226" s="31" t="inlineStr">
@@ -69479,7 +69479,7 @@
       </c>
       <c r="BH226" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI226" s="24" t="inlineStr">
@@ -69488,19 +69488,19 @@
         </is>
       </c>
       <c r="BJ226" s="25" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK226" s="26" t="n">
-        <v>-122</v>
+        <v>-111</v>
       </c>
       <c r="BL226" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.900901</v>
       </c>
       <c r="BM226" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.526066</v>
       </c>
       <c r="BN226" s="28" t="n">
-        <v>0.547264</v>
+        <v>0.522388</v>
       </c>
       <c r="BO226" s="28" t="n"/>
       <c r="BP226" s="25" t="n"/>
@@ -69541,12 +69541,12 @@
     <row r="227" ht="36" customHeight="1">
       <c r="A227" s="24" t="inlineStr">
         <is>
-          <t>bcc44891645f4282</t>
+          <t>a7a64cb2e98c4d4c</t>
         </is>
       </c>
       <c r="B227" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C227" s="24" t="inlineStr">
@@ -69593,25 +69593,25 @@
         </is>
       </c>
       <c r="L227" s="26" t="n">
-        <v>-156</v>
+        <v>-153</v>
       </c>
       <c r="M227" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.653595</v>
       </c>
       <c r="N227" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.604743</v>
       </c>
       <c r="O227" s="28" t="n">
-        <v>0.631715</v>
+        <v>0.633554</v>
       </c>
       <c r="P227" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q227" s="28" t="n">
-        <v>0.02234</v>
+        <v>0.028811</v>
       </c>
       <c r="R227" s="26" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="S227" s="29" t="n">
         <v>1.5</v>
@@ -69637,7 +69637,7 @@
       <c r="AD227" s="24" t="n"/>
       <c r="AE227" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.87-4.56; raw selected-side p=0.6933, calibrated p=0.6317.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.87-4.56; raw selected-side p=0.6960, calibrated p=0.6336.</t>
         </is>
       </c>
       <c r="AF227" s="31" t="inlineStr">
@@ -69756,7 +69756,7 @@
       </c>
       <c r="BH227" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI227" s="24" t="inlineStr">
@@ -69768,16 +69768,16 @@
         <v>1.5</v>
       </c>
       <c r="BK227" s="26" t="n">
-        <v>-156</v>
+        <v>-153</v>
       </c>
       <c r="BL227" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.653595</v>
       </c>
       <c r="BM227" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.604743</v>
       </c>
       <c r="BN227" s="28" t="n">
-        <v>0.606965</v>
+        <v>0.60199</v>
       </c>
       <c r="BO227" s="28" t="n"/>
       <c r="BP227" s="25" t="n"/>
@@ -69818,12 +69818,12 @@
     <row r="228" ht="36" customHeight="1">
       <c r="A228" s="24" t="inlineStr">
         <is>
-          <t>ad2ee23048d3470b</t>
+          <t>4cff1e5dcda04b4c</t>
         </is>
       </c>
       <c r="B228" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C228" s="24" t="inlineStr">
@@ -69870,25 +69870,25 @@
         </is>
       </c>
       <c r="L228" s="26" t="n">
-        <v>-113</v>
+        <v>-102</v>
       </c>
       <c r="M228" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.980392</v>
       </c>
       <c r="N228" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.50495</v>
       </c>
       <c r="O228" s="28" t="n">
-        <v>0.537198</v>
+        <v>0.537173</v>
       </c>
       <c r="P228" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q228" s="28" t="n">
-        <v>0.006682</v>
+        <v>0.032223</v>
       </c>
       <c r="R228" s="26" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="S228" s="29" t="n">
         <v>1</v>
@@ -69914,7 +69914,7 @@
       <c r="AD228" s="24" t="n"/>
       <c r="AE228" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.87-4.56; raw selected-side p=0.6264, calibrated p=0.5372.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.87-4.56; raw selected-side p=0.6263, calibrated p=0.5372.</t>
         </is>
       </c>
       <c r="AF228" s="31" t="inlineStr">
@@ -70033,7 +70033,7 @@
       </c>
       <c r="BH228" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI228" s="24" t="inlineStr">
@@ -70045,16 +70045,16 @@
         <v>7.5</v>
       </c>
       <c r="BK228" s="26" t="n">
-        <v>-113</v>
+        <v>-102</v>
       </c>
       <c r="BL228" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.980392</v>
       </c>
       <c r="BM228" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.50495</v>
       </c>
       <c r="BN228" s="28" t="n">
-        <v>0.527363</v>
+        <v>0.502488</v>
       </c>
       <c r="BO228" s="28" t="n"/>
       <c r="BP228" s="25" t="n"/>
@@ -70095,12 +70095,12 @@
     <row r="229" ht="36" customHeight="1">
       <c r="A229" s="24" t="inlineStr">
         <is>
-          <t>d1c934f6d02e4c3f</t>
+          <t>3b8fce910aa54bd0</t>
         </is>
       </c>
       <c r="B229" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C229" s="24" t="inlineStr">
@@ -70147,25 +70147,25 @@
         </is>
       </c>
       <c r="L229" s="26" t="n">
-        <v>-150</v>
+        <v>-141</v>
       </c>
       <c r="M229" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.70922</v>
       </c>
       <c r="N229" s="28" t="n">
-        <v>0.6</v>
+        <v>0.585062</v>
       </c>
       <c r="O229" s="28" t="n">
-        <v>0.580303</v>
+        <v>0.5781230000000001</v>
       </c>
       <c r="P229" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q229" s="28" t="n">
-        <v>-0.019697</v>
+        <v>-0.006939</v>
       </c>
       <c r="R229" s="26" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="S229" s="29" t="n">
         <v>1.25</v>
@@ -70191,7 +70191,7 @@
       <c r="AD229" s="24" t="n"/>
       <c r="AE229" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.83-4.33; raw selected-side p=0.6179, calibrated p=0.5803.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.83-4.33; raw selected-side p=0.6147, calibrated p=0.5781.</t>
         </is>
       </c>
       <c r="AF229" s="31" t="inlineStr">
@@ -70310,7 +70310,7 @@
       </c>
       <c r="BH229" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI229" s="24" t="inlineStr">
@@ -70322,16 +70322,16 @@
         <v>1.5</v>
       </c>
       <c r="BK229" s="26" t="n">
-        <v>-150</v>
+        <v>-141</v>
       </c>
       <c r="BL229" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.70922</v>
       </c>
       <c r="BM229" s="28" t="n">
-        <v>0.6</v>
+        <v>0.585062</v>
       </c>
       <c r="BN229" s="28" t="n">
-        <v>0.597015</v>
+        <v>0.58209</v>
       </c>
       <c r="BO229" s="28" t="n"/>
       <c r="BP229" s="25" t="n"/>
@@ -70372,12 +70372,12 @@
     <row r="230" ht="36" customHeight="1">
       <c r="A230" s="24" t="inlineStr">
         <is>
-          <t>2cf016d817bc4758</t>
+          <t>1c707594d7d54d7c</t>
         </is>
       </c>
       <c r="B230" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C230" s="24" t="inlineStr">
@@ -70424,25 +70424,25 @@
         </is>
       </c>
       <c r="L230" s="26" t="n">
-        <v>-113</v>
+        <v>-120</v>
       </c>
       <c r="M230" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.833333</v>
       </c>
       <c r="N230" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.545455</v>
       </c>
       <c r="O230" s="28" t="n">
-        <v>0.527374</v>
+        <v>0.526914</v>
       </c>
       <c r="P230" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q230" s="28" t="n">
-        <v>-0.003142</v>
+        <v>-0.018541</v>
       </c>
       <c r="R230" s="26" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="S230" s="29" t="n">
         <v>1</v>
@@ -70468,7 +70468,7 @@
       <c r="AD230" s="24" t="n"/>
       <c r="AE230" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.83-4.33; raw selected-side p=0.5868, calibrated p=0.5274.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.83-4.33; raw selected-side p=0.5850, calibrated p=0.5269.</t>
         </is>
       </c>
       <c r="AF230" s="31" t="inlineStr">
@@ -70587,7 +70587,7 @@
       </c>
       <c r="BH230" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI230" s="24" t="inlineStr">
@@ -70599,16 +70599,16 @@
         <v>9.5</v>
       </c>
       <c r="BK230" s="26" t="n">
-        <v>-113</v>
+        <v>-120</v>
       </c>
       <c r="BL230" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.833333</v>
       </c>
       <c r="BM230" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.545455</v>
       </c>
       <c r="BN230" s="28" t="n">
-        <v>0.527363</v>
+        <v>0.542289</v>
       </c>
       <c r="BO230" s="28" t="n"/>
       <c r="BP230" s="25" t="n"/>
